--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -815,7 +815,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -895,7 +899,7 @@
         <v>46277</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -929,7 +933,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1135,7 +1143,7 @@
         <v>46273</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1261,7 +1269,7 @@
         <v>46273</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -4675,7 +4683,7 @@
         <v>46254</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -4801,7 +4809,7 @@
         <v>46254</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
@@ -7497,7 +7505,7 @@
         <v>46246</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -10835,7 +10843,7 @@
         <v>46234</v>
       </c>
       <c r="AA83" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
@@ -10957,7 +10965,7 @@
         <v>46238</v>
       </c>
       <c r="AA84" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
@@ -11083,7 +11091,7 @@
         <v>46238</v>
       </c>
       <c r="AA85" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
@@ -11861,7 +11869,7 @@
         <v>46254</v>
       </c>
       <c r="AA91" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
@@ -12377,7 +12385,7 @@
         <v>46229</v>
       </c>
       <c r="AA95" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
@@ -12503,7 +12511,7 @@
         <v>46229</v>
       </c>
       <c r="AA96" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
@@ -17435,7 +17443,7 @@
         <v>46258</v>
       </c>
       <c r="AA135" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
@@ -17577,7 +17585,7 @@
         <v>46254</v>
       </c>
       <c r="AA136" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
@@ -18519,7 +18527,7 @@
         <v>46258</v>
       </c>
       <c r="AA143" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB143" s="2" t="inlineStr">
         <is>
@@ -22120,7 +22128,7 @@
         <v>46234</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -25208,7 +25216,7 @@
         <v>46258</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -25350,7 +25358,7 @@
         <v>46254</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -26174,7 +26182,7 @@
         <v>46258</v>
       </c>
       <c r="AA50" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
@@ -27294,7 +27302,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -27374,7 +27386,7 @@
         <v>46277</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -27408,7 +27420,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -27492,7 +27508,7 @@
         <v>46273</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -27618,7 +27634,7 @@
         <v>46273</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -30534,7 +30550,7 @@
         <v>46254</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -30660,7 +30676,7 @@
         <v>46254</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
@@ -33098,7 +33114,7 @@
         <v>46246</v>
       </c>
       <c r="AA50" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
@@ -34944,7 +34960,7 @@
         <v>46238</v>
       </c>
       <c r="AA65" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
@@ -35070,7 +35086,7 @@
         <v>46238</v>
       </c>
       <c r="AA66" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
@@ -35426,7 +35442,7 @@
         <v>46254</v>
       </c>
       <c r="AA69" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
@@ -35670,7 +35686,7 @@
         <v>46229</v>
       </c>
       <c r="AA71" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
@@ -35796,7 +35812,7 @@
         <v>46229</v>
       </c>
       <c r="AA72" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
@@ -38968,7 +38984,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -39094,7 +39110,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -40241,7 +40257,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -40367,7 +40383,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -40564,7 +40580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M126"/>
+  <dimension ref="A1:M127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -46826,8 +46842,57 @@
         </is>
       </c>
     </row>
+    <row r="127" ht="54" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T17:27:56+08:00</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 至 2026-09-13</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问74页，访问失败215页，持久化待复核208个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M126"/>
+  <autoFilter ref="A1:M127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -16541,7 +16541,7 @@
         <v>46229</v>
       </c>
       <c r="AA128" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB128" s="2" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>46254</v>
       </c>
       <c r="AA134" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB134" s="2" t="inlineStr">
         <is>
@@ -37988,7 +37988,7 @@
         <v>46229</v>
       </c>
       <c r="AA90" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>46254</v>
       </c>
       <c r="AA93" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -46891,8 +46891,57 @@
         </is>
       </c>
     </row>
+    <row r="128" ht="54" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T17:46:59+08:00</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 至 2026-09-13</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: RetryError: HTTPConnectionPool(host='qinghai.chinatax.gov.cn', port=80): Max retries exceeded with url: /hxz/sjtzgg/ (Caused by ResponseError('too many 502 error responses')) | discover_official_index: https://fujian.chinatax.go...</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问70页，访问失败212页，持久化待复核205个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M127"/>
+  <autoFilter ref="A1:M128"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$130</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -821,7 +821,7 @@
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1409,7 +1413,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -27662,7 +27670,7 @@
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -28014,7 +28022,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -28128,7 +28140,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -41288,7 +41304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -47701,8 +47717,57 @@
         </is>
       </c>
     </row>
+    <row r="130" ht="54" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T18:05:09+08:00</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 至 2026-09-14</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问71页，访问失败219页，持久化待复核212个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M129"/>
+  <autoFilter ref="A1:M130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -781,7 +781,7 @@
         <v>46279</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>46273</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>46273</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>46254</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>46254</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>46246</v>
       </c>
       <c r="AA60" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>46234</v>
       </c>
       <c r="AA86" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>46238</v>
       </c>
       <c r="AA87" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>46238</v>
       </c>
       <c r="AA88" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>46254</v>
       </c>
       <c r="AA94" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>46229</v>
       </c>
       <c r="AA98" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>46229</v>
       </c>
       <c r="AA99" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>46229</v>
       </c>
       <c r="AA131" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>46254</v>
       </c>
       <c r="AA137" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>46258</v>
       </c>
       <c r="AA138" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>46254</v>
       </c>
       <c r="AA139" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB139" s="2" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>46258</v>
       </c>
       <c r="AA146" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB146" s="2" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>46234</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>46258</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46254</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>46258</v>
       </c>
       <c r="AA50" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>46279</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>46273</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>46273</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>46254</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>46254</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>46246</v>
       </c>
       <c r="AA53" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>46238</v>
       </c>
       <c r="AA68" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>46238</v>
       </c>
       <c r="AA69" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>46254</v>
       </c>
       <c r="AA72" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>46229</v>
       </c>
       <c r="AA74" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>46229</v>
       </c>
       <c r="AA75" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>46229</v>
       </c>
       <c r="AA93" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>46254</v>
       </c>
       <c r="AA96" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -47766,8 +47766,57 @@
         </is>
       </c>
     </row>
+    <row r="131" ht="54" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15T17:22:30+08:00</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 至 2026-09-15</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问71页，访问失败218页，持久化待复核211个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M130"/>
+  <autoFilter ref="A1:M131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -781,7 +781,7 @@
         <v>46280</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -815,7 +815,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -895,7 +899,7 @@
         <v>46280</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -929,7 +933,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1009,7 +1017,7 @@
         <v>46280</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1043,7 +1051,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1119,7 +1131,7 @@
         <v>46280</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1153,7 +1165,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1233,7 +1249,7 @@
         <v>46280</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1267,7 +1283,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1347,7 +1367,7 @@
         <v>46280</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1381,7 +1401,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1461,7 +1485,7 @@
         <v>46279</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -5721,7 +5745,7 @@
         <v>46254</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -5847,7 +5871,7 @@
         <v>46254</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -8543,7 +8567,7 @@
         <v>46246</v>
       </c>
       <c r="AA66" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
@@ -11881,7 +11905,7 @@
         <v>46234</v>
       </c>
       <c r="AA92" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
@@ -12003,7 +12027,7 @@
         <v>46238</v>
       </c>
       <c r="AA93" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
@@ -12129,7 +12153,7 @@
         <v>46238</v>
       </c>
       <c r="AA94" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
@@ -12907,7 +12931,7 @@
         <v>46254</v>
       </c>
       <c r="AA100" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
@@ -13423,7 +13447,7 @@
         <v>46229</v>
       </c>
       <c r="AA104" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
@@ -13549,7 +13573,7 @@
         <v>46229</v>
       </c>
       <c r="AA105" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
@@ -18481,7 +18505,7 @@
         <v>46258</v>
       </c>
       <c r="AA144" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
@@ -18623,7 +18647,7 @@
         <v>46254</v>
       </c>
       <c r="AA145" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB145" s="2" t="inlineStr">
         <is>
@@ -19565,7 +19589,7 @@
         <v>46258</v>
       </c>
       <c r="AA152" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB152" s="2" t="inlineStr">
         <is>
@@ -23176,7 +23200,7 @@
         <v>46234</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -26264,7 +26288,7 @@
         <v>46258</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -26406,7 +26430,7 @@
         <v>46254</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -27230,7 +27254,7 @@
         <v>46258</v>
       </c>
       <c r="AA50" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
@@ -28316,7 +28340,7 @@
         <v>46280</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -28350,7 +28374,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -28430,7 +28458,7 @@
         <v>46280</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -28464,7 +28492,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -28544,7 +28576,7 @@
         <v>46280</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -28578,7 +28610,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -28654,7 +28690,7 @@
         <v>46280</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -28688,7 +28724,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -28768,7 +28808,7 @@
         <v>46280</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -28802,7 +28842,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -28882,7 +28926,7 @@
         <v>46280</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -28916,7 +28960,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -28996,7 +29044,7 @@
         <v>46279</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -32636,7 +32684,7 @@
         <v>46254</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -32762,7 +32810,7 @@
         <v>46254</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
@@ -35200,7 +35248,7 @@
         <v>46246</v>
       </c>
       <c r="AA59" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
@@ -37046,7 +37094,7 @@
         <v>46238</v>
       </c>
       <c r="AA74" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
@@ -37172,7 +37220,7 @@
         <v>46238</v>
       </c>
       <c r="AA75" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
@@ -37528,7 +37576,7 @@
         <v>46254</v>
       </c>
       <c r="AA78" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
@@ -37772,7 +37820,7 @@
         <v>46229</v>
       </c>
       <c r="AA80" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
@@ -37898,7 +37946,7 @@
         <v>46229</v>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
@@ -41080,7 +41128,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -41206,7 +41254,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -42353,7 +42401,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -42479,7 +42527,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -42676,7 +42724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M132"/>
+  <dimension ref="A1:M133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -49240,8 +49288,57 @@
         </is>
       </c>
     </row>
+    <row r="133" ht="54" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T17:15:18+08:00</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 至 2026-09-16</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问69页，访问失败225页，持久化待复核218个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M132"/>
+  <autoFilter ref="A1:M133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$106</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -29573,7 +29573,7 @@
       </c>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -29699,7 +29699,7 @@
       </c>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -43466,7 +43466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M135"/>
+  <dimension ref="A1:M136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -50185,8 +50185,57 @@
         </is>
       </c>
     </row>
+    <row r="136" ht="54" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T17:42:42+08:00</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 至 2026-09-17</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问67页，访问失败230页，持久化待复核223个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M135"/>
+  <autoFilter ref="A1:M136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$138</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -825,7 +825,7 @@
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         <v>46280</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>46280</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>46280</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>46280</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>46280</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>46280</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -29137,7 +29137,7 @@
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -29219,7 +29219,7 @@
         <v>46280</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>46280</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>46280</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>46280</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>46280</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>46280</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -50799,8 +50799,57 @@
         </is>
       </c>
     </row>
+    <row r="138" ht="54" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T17:16:42+08:00</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 至 2026-09-18</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问74页，访问失败234页，持久化待复核226个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M137"/>
+  <autoFilter ref="A1:M138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -785,7 +785,7 @@
         <v>46283</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46283</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46280</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>46280</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>46280</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>46280</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>46280</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>46280</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>46282</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>46282</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>46279</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>46254</v>
       </c>
       <c r="AA48" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>46254</v>
       </c>
       <c r="AA49" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>46246</v>
       </c>
       <c r="AA71" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>46234</v>
       </c>
       <c r="AA97" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>46238</v>
       </c>
       <c r="AA98" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>46238</v>
       </c>
       <c r="AA99" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>46254</v>
       </c>
       <c r="AA105" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46229</v>
       </c>
       <c r="AA142" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46254</v>
       </c>
       <c r="AA148" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB148" s="2" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>46258</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>46254</v>
       </c>
       <c r="AA150" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>46258</v>
       </c>
       <c r="AA157" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>46234</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>46258</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>46254</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>46258</v>
       </c>
       <c r="AA50" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>46283</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>46283</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>46280</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>46280</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>46280</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>46280</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>46280</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>46280</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>46282</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>46282</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>46279</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>46254</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>46254</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>46246</v>
       </c>
       <c r="AA64" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>46238</v>
       </c>
       <c r="AA79" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>46238</v>
       </c>
       <c r="AA80" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>46254</v>
       </c>
       <c r="AA83" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>46229</v>
       </c>
       <c r="AA104" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>46254</v>
       </c>
       <c r="AA107" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -43655,7 +43655,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M138"/>
+  <dimension ref="A1:M139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -50848,8 +50848,57 @@
         </is>
       </c>
     </row>
+    <row r="139" ht="54" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T16:45:44+08:00</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12 至 2026-09-19</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问67页，访问失败236页，持久化待复核228个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M138"/>
+  <autoFilter ref="A1:M139"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1087,7 +1087,11 @@
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -21889,7 +21893,11 @@
           <t>附件正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -44742,7 +44750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:M142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -51767,8 +51775,57 @@
         </is>
       </c>
     </row>
+    <row r="142" ht="54" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T17:33:46+08:00</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 至 2026-09-20</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/pingtanswj/zfxxgkzl/zfxxgkml/qtgg/: ConnectionError: HTTPSConnectionPool(host='...</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问70页，访问失败245页，持久化待复核237个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M141"/>
+  <autoFilter ref="A1:M142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$143</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -785,7 +785,7 @@
         <v>46283</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46283</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>46285</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46280</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46280</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>46280</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>46280</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>46280</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>46280</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>46282</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>46282</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46279</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>46254</v>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>46254</v>
       </c>
       <c r="AA52" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>46246</v>
       </c>
       <c r="AA74" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>46234</v>
       </c>
       <c r="AA100" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>46238</v>
       </c>
       <c r="AA101" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>46238</v>
       </c>
       <c r="AA102" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>46254</v>
       </c>
       <c r="AA108" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>46229</v>
       </c>
       <c r="AA145" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB145" s="2" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>46254</v>
       </c>
       <c r="AA151" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB151" s="2" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>46258</v>
       </c>
       <c r="AA152" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB152" s="2" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>46254</v>
       </c>
       <c r="AA153" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB153" s="2" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>46258</v>
       </c>
       <c r="AA160" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>46285</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>46234</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>46258</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>46254</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>46258</v>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>46283</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>46283</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>46280</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>46280</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>46280</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>46280</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>46280</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>46280</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>46282</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>46282</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>46279</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>46254</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>46254</v>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>46246</v>
       </c>
       <c r="AA66" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>46238</v>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>46238</v>
       </c>
       <c r="AA82" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>46254</v>
       </c>
       <c r="AA85" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>46229</v>
       </c>
       <c r="AA106" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
         <v>46254</v>
       </c>
       <c r="AA109" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -51824,8 +51824,57 @@
         </is>
       </c>
     </row>
+    <row r="143" ht="54" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:52:03+08:00</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 至 2026-09-21</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问81页，访问失败246页，持久化待复核238个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M142"/>
+  <autoFilter ref="A1:M143"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -833,7 +833,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -961,7 +965,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -23955,7 +23963,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -24083,7 +24095,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -48878,7 +48894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -56107,8 +56123,57 @@
         </is>
       </c>
     </row>
+    <row r="146" ht="54" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22T17:35:50+08:00</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 至 2026-09-22</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>334</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/pingtanswj/zfxxgkzl/zfxxgkml/qtgg/: ConnectionError: HTTPSConnectionPool(host='...</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问76页，访问失败253页，持久化待复核242个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M145"/>
+  <autoFilter ref="A1:M146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -799,7 +799,7 @@
         <v>46287</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46287</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>46286</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46286</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>46286</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>46286</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>46283</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>46283</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>46285</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46280</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>46280</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>46280</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>46280</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>46280</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>46280</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>46254</v>
       </c>
       <c r="AA61" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>46254</v>
       </c>
       <c r="AA62" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>46246</v>
       </c>
       <c r="AA84" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>46234</v>
       </c>
       <c r="AA110" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>46238</v>
       </c>
       <c r="AA111" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>46238</v>
       </c>
       <c r="AA112" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>46254</v>
       </c>
       <c r="AA118" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46229</v>
       </c>
       <c r="AA157" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         <v>46254</v>
       </c>
       <c r="AA165" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>46258</v>
       </c>
       <c r="AA166" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB166" s="2" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>46254</v>
       </c>
       <c r="AA167" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB167" s="2" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>46258</v>
       </c>
       <c r="AA176" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>46287</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>46287</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>46285</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>46234</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>46258</v>
       </c>
       <c r="AA48" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>46254</v>
       </c>
       <c r="AA49" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>46258</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>46286</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>46286</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>46286</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>46286</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>46283</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>46283</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -33081,7 +33081,7 @@
         <v>46280</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>46280</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>46280</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>46280</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46280</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46280</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>46254</v>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>46254</v>
       </c>
       <c r="AA52" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>46246</v>
       </c>
       <c r="AA72" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>46238</v>
       </c>
       <c r="AA87" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>46238</v>
       </c>
       <c r="AA88" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
@@ -42943,7 +42943,7 @@
         <v>46254</v>
       </c>
       <c r="AA91" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>46229</v>
       </c>
       <c r="AA114" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>46254</v>
       </c>
       <c r="AA119" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -48815,7 +48815,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M146"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -56172,8 +56172,57 @@
         </is>
       </c>
     </row>
+    <row r="147" ht="54" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23T17:15:54+08:00</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 至 2026-09-23</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问79页，访问失败258页，持久化待复核247个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M146"/>
+  <autoFilter ref="A1:M147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$148</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -48894,7 +48894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -56221,8 +56221,57 @@
         </is>
       </c>
     </row>
+    <row r="148" ht="54" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23T17:36:44+08:00</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 至 2026-09-23</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问77页，访问失败259页，持久化待复核248个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M147"/>
+  <autoFilter ref="A1:M148"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -799,7 +799,7 @@
         <v>46287</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46287</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>46286</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>46286</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>46286</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>46286</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>46283</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>46283</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>46285</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46280</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>46280</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>46280</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>46280</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>46280</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>46280</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>46254</v>
       </c>
       <c r="AA61" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>46254</v>
       </c>
       <c r="AA62" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>46246</v>
       </c>
       <c r="AA84" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>46234</v>
       </c>
       <c r="AA110" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>46238</v>
       </c>
       <c r="AA111" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>46238</v>
       </c>
       <c r="AA112" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>46254</v>
       </c>
       <c r="AA118" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46229</v>
       </c>
       <c r="AA157" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         <v>46254</v>
       </c>
       <c r="AA165" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>46258</v>
       </c>
       <c r="AA166" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB166" s="2" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>46254</v>
       </c>
       <c r="AA167" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB167" s="2" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>46258</v>
       </c>
       <c r="AA176" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>46287</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>46287</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>46285</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>46234</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>46258</v>
       </c>
       <c r="AA48" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>46254</v>
       </c>
       <c r="AA49" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>46258</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>46286</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>46286</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>46286</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>46286</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>46283</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>46283</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -33081,7 +33081,7 @@
         <v>46280</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>46280</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>46280</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>46280</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46280</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46280</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>46254</v>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>46254</v>
       </c>
       <c r="AA52" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>46246</v>
       </c>
       <c r="AA72" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>46238</v>
       </c>
       <c r="AA87" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>46238</v>
       </c>
       <c r="AA88" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
@@ -42943,7 +42943,7 @@
         <v>46254</v>
       </c>
       <c r="AA91" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>46229</v>
       </c>
       <c r="AA114" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>46254</v>
       </c>
       <c r="AA119" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -48815,7 +48815,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M148"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -56270,8 +56270,57 @@
         </is>
       </c>
     </row>
+    <row r="149" ht="54" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24T17:15:13+08:00</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 至 2026-09-24</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>347</v>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/: ConnectionError: HTTPSConnectionPool(host='fuji...</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问82页，访问失败260页，持久化待复核249个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M148"/>
+  <autoFilter ref="A1:M149"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$127</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -821,7 +821,7 @@
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -32763,7 +32763,7 @@
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -32885,7 +32885,7 @@
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -50130,7 +50130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -57661,8 +57661,57 @@
         </is>
       </c>
     </row>
+    <row r="152" ht="54" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25T17:55:12+08:00</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 至 2026-09-25</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问78页，访问失败278页，持久化待复核267个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M151"/>
+  <autoFilter ref="A1:M152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$127</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$153</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -781,7 +781,7 @@
         <v>46290</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>46290</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46289</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>46289</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>46287</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>46287</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46289</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>46286</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>46286</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>46286</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>46286</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>46280</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>46280</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>46280</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>46280</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>46280</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>46280</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>46254</v>
       </c>
       <c r="AA66" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>46254</v>
       </c>
       <c r="AA67" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>46246</v>
       </c>
       <c r="AA89" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>46234</v>
       </c>
       <c r="AA115" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>46238</v>
       </c>
       <c r="AA116" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB116" s="2" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>46238</v>
       </c>
       <c r="AA117" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>46254</v>
       </c>
       <c r="AA123" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>46229</v>
       </c>
       <c r="AA162" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB162" s="2" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>46254</v>
       </c>
       <c r="AA170" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>46258</v>
       </c>
       <c r="AA171" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>46254</v>
       </c>
       <c r="AA172" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>46258</v>
       </c>
       <c r="AA181" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB181" s="2" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>46287</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>46287</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>46234</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>46258</v>
       </c>
       <c r="AA48" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>46254</v>
       </c>
       <c r="AA49" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>46258</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>46290</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>46290</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>46289</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>46289</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>46289</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>46286</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>46286</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>46286</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>46286</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>46280</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>46280</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>46280</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>46280</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>46280</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>46280</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>46254</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>46254</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>46246</v>
       </c>
       <c r="AA77" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>46238</v>
       </c>
       <c r="AA92" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>46238</v>
       </c>
       <c r="AA93" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>46254</v>
       </c>
       <c r="AA96" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>46229</v>
       </c>
       <c r="AA119" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>46254</v>
       </c>
       <c r="AA124" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB124" s="2" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -48660,7 +48660,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -49807,7 +49807,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -57710,8 +57710,57 @@
         </is>
       </c>
     </row>
+    <row r="153" ht="54" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26T17:18:42+08:00</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 至 2026-09-26</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问77页，访问失败281页，持久化待复核270个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M152"/>
+  <autoFilter ref="A1:M153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$127</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -50130,7 +50130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M153"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -57759,8 +57759,57 @@
         </is>
       </c>
     </row>
+    <row r="154" ht="54" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26T17:39:02+08:00</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 至 2026-09-26</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/: ConnectionError: HTTPSConnectionPool(host='fuji...</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问78页，访问失败280页，持久化待复核269个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M153"/>
+  <autoFilter ref="A1:M154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$161</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -795,7 +795,7 @@
         <v>46294</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46294</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>46294</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>46294</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>46293</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>46293</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>46294</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1597,7 +1597,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1677,7 +1681,7 @@
         <v>46294</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1713,7 +1717,7 @@
       </c>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>字段“官方原文链接”存在冲突:保留原值“https://gtm-cn-2r42yzjvn0s.jiangsu.chinatax.gov.cn/art/2026/9/28/art_9193_1788059.html”,新值“https://jiangsu.chinatax.gov.cn/art/2026/9/28/art_9193_1788059.html”未静默覆盖。</t>
+          <t>字段“官方原文链接”存在冲突:保留原值“https://gtm-cn-2r42yzjvn0s.jiangsu.chinatax.gov.cn/art/2026/9/28/art_9193_1788059.html”,新值“https://jiangsu.chinatax.gov.cn/art/2026/9/28/art_9193_1788059.html”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1803,7 @@
         <v>46293</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1929,7 @@
         <v>46293</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2047,7 +2051,7 @@
         <v>46290</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2169,7 +2173,7 @@
         <v>46290</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -3663,7 +3667,7 @@
         <v>46286</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3785,7 +3789,7 @@
         <v>46286</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -4805,7 +4809,7 @@
         <v>46280</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -5037,7 +5041,7 @@
         <v>46280</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
@@ -5155,7 +5159,7 @@
         <v>46280</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
@@ -5269,7 +5273,7 @@
         <v>46280</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -5387,7 +5391,7 @@
         <v>46280</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
@@ -5505,7 +5509,7 @@
         <v>46280</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -10395,7 +10399,7 @@
         <v>46254</v>
       </c>
       <c r="AA80" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
@@ -10521,7 +10525,7 @@
         <v>46254</v>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
@@ -13217,7 +13221,7 @@
         <v>46246</v>
       </c>
       <c r="AA103" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
@@ -16555,7 +16559,7 @@
         <v>46234</v>
       </c>
       <c r="AA129" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB129" s="2" t="inlineStr">
         <is>
@@ -16677,7 +16681,7 @@
         <v>46238</v>
       </c>
       <c r="AA130" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB130" s="2" t="inlineStr">
         <is>
@@ -16803,7 +16807,7 @@
         <v>46238</v>
       </c>
       <c r="AA131" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
@@ -17581,7 +17585,7 @@
         <v>46254</v>
       </c>
       <c r="AA137" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
@@ -22505,7 +22509,7 @@
         <v>46229</v>
       </c>
       <c r="AA176" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
@@ -23533,7 +23537,7 @@
         <v>46254</v>
       </c>
       <c r="AA184" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB184" s="2" t="inlineStr">
         <is>
@@ -23667,7 +23671,7 @@
         <v>46258</v>
       </c>
       <c r="AA185" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
@@ -23809,7 +23813,7 @@
         <v>46254</v>
       </c>
       <c r="AA186" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB186" s="2" t="inlineStr">
         <is>
@@ -25011,7 +25015,7 @@
         <v>46258</v>
       </c>
       <c r="AA195" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
@@ -26330,7 +26334,7 @@
         <v>46294</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -26472,7 +26476,7 @@
         <v>46294</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -26594,7 +26598,7 @@
         <v>46294</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -26628,7 +26632,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -30136,7 +30144,7 @@
         <v>46234</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
@@ -33224,7 +33232,7 @@
         <v>46258</v>
       </c>
       <c r="AA54" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
@@ -33366,7 +33374,7 @@
         <v>46254</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -34190,7 +34198,7 @@
         <v>46258</v>
       </c>
       <c r="AA61" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
@@ -35295,7 +35303,7 @@
         <v>46294</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -35421,7 +35429,7 @@
         <v>46294</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -35547,7 +35555,7 @@
         <v>46293</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -35673,7 +35681,7 @@
         <v>46293</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -35795,7 +35803,7 @@
         <v>46294</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -35831,7 +35839,7 @@
       </c>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>字段“官方原文链接”存在冲突:保留原值“https://gtm-cn-2r42yzjvn0s.jiangsu.chinatax.gov.cn/art/2026/9/28/art_9193_1788059.html”,新值“https://jiangsu.chinatax.gov.cn/art/2026/9/28/art_9193_1788059.html”未静默覆盖。</t>
+          <t>字段“官方原文链接”存在冲突:保留原值“https://gtm-cn-2r42yzjvn0s.jiangsu.chinatax.gov.cn/art/2026/9/28/art_9193_1788059.html”,新值“https://jiangsu.chinatax.gov.cn/art/2026/9/28/art_9193_1788059.html”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -35917,7 +35925,7 @@
         <v>46293</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -36043,7 +36051,7 @@
         <v>46293</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -36165,7 +36173,7 @@
         <v>46290</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -36287,7 +36295,7 @@
         <v>46290</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -37133,7 +37141,7 @@
         <v>46286</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -37255,7 +37263,7 @@
         <v>46286</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -37869,7 +37877,7 @@
         <v>46280</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -38101,7 +38109,7 @@
         <v>46280</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -38219,7 +38227,7 @@
         <v>46280</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -38333,7 +38341,7 @@
         <v>46280</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -38451,7 +38459,7 @@
         <v>46280</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -38569,7 +38577,7 @@
         <v>46280</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -42839,7 +42847,7 @@
         <v>46254</v>
       </c>
       <c r="AA64" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
@@ -42965,7 +42973,7 @@
         <v>46254</v>
       </c>
       <c r="AA65" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
@@ -45403,7 +45411,7 @@
         <v>46246</v>
       </c>
       <c r="AA85" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
@@ -47249,7 +47257,7 @@
         <v>46238</v>
       </c>
       <c r="AA100" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
@@ -47375,7 +47383,7 @@
         <v>46238</v>
       </c>
       <c r="AA101" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
@@ -47731,7 +47739,7 @@
         <v>46254</v>
       </c>
       <c r="AA104" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
@@ -50529,7 +50537,7 @@
         <v>46229</v>
       </c>
       <c r="AA127" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
@@ -51151,7 +51159,7 @@
         <v>46254</v>
       </c>
       <c r="AA132" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB132" s="2" t="inlineStr">
         <is>
@@ -52108,7 +52116,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -52234,7 +52242,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -52352,7 +52360,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -53381,7 +53389,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -53507,7 +53515,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -53625,7 +53633,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -53704,7 +53712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M160"/>
+  <dimension ref="A1:M161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -61700,8 +61708,57 @@
         </is>
       </c>
     </row>
+    <row r="161" ht="54" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30T18:26:29+08:00</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 至 2026-09-30</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问93页，访问失败314页，持久化待复核303个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M160"/>
+  <autoFilter ref="A1:M161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -2549,7 +2549,7 @@
         <v>46289</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>46289</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>46289</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>46289</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -53712,7 +53712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M161"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -61757,8 +61757,57 @@
         </is>
       </c>
     </row>
+    <row r="162" ht="54" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30T18:49:58+08:00</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 至 2026-09-30</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>431</v>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问91页，访问失败319页，持久化待复核308个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M161"/>
+  <autoFilter ref="A1:M162"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$163</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -795,7 +795,7 @@
         <v>46294</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46294</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>46294</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>46294</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>46293</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>46293</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>46294</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46293</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>46293</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>46290</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>46290</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>46286</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>46286</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>46280</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>46280</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>46280</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>46280</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>46280</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>46280</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>46254</v>
       </c>
       <c r="AA80" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>46254</v>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>46246</v>
       </c>
       <c r="AA103" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>46234</v>
       </c>
       <c r="AA129" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB129" s="2" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>46238</v>
       </c>
       <c r="AA130" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB130" s="2" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>46238</v>
       </c>
       <c r="AA131" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>46254</v>
       </c>
       <c r="AA137" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         <v>46229</v>
       </c>
       <c r="AA176" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>46254</v>
       </c>
       <c r="AA184" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB184" s="2" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>46258</v>
       </c>
       <c r="AA185" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>46254</v>
       </c>
       <c r="AA186" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB186" s="2" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46258</v>
       </c>
       <c r="AA195" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>46294</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>46294</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>46234</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>46258</v>
       </c>
       <c r="AA54" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>46254</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>46258</v>
       </c>
       <c r="AA61" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>46294</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>46294</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>46293</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46293</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>46294</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>46293</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>46293</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>46290</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>46290</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>46286</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>46286</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>46280</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>46280</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -38227,7 +38227,7 @@
         <v>46280</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>46280</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>46280</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>46280</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>46254</v>
       </c>
       <c r="AA64" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>46254</v>
       </c>
       <c r="AA65" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
@@ -45411,7 +45411,7 @@
         <v>46246</v>
       </c>
       <c r="AA85" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>46238</v>
       </c>
       <c r="AA100" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
@@ -47383,7 +47383,7 @@
         <v>46238</v>
       </c>
       <c r="AA101" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>46254</v>
       </c>
       <c r="AA104" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>46229</v>
       </c>
       <c r="AA127" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>46254</v>
       </c>
       <c r="AA132" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB132" s="2" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -53712,7 +53712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -61806,8 +61806,57 @@
         </is>
       </c>
     </row>
+    <row r="163" ht="54" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01T18:53:34+08:00</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 至 2026-10-01</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/: ConnectionError: HTTPSConnectionPool(host='fuji...</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问88页，访问失败321页，持久化待复核310个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M162"/>
+  <autoFilter ref="A1:M163"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -795,7 +795,7 @@
         <v>46294</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46294</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>46296</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>尚未找到官方原文;第三方来源仅作待核验线索。</t>
+          <t>尚未找到官方原文;第三方来源仅作待核验线索。 Excel 与 CSV 历史数据已合并核对。 字段“当事人名称”存在冲突:保留原值“青海天月德物流有限公司湟源分公司”,新值“青海易创科技有限公司”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
         <v>46296</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>尚未找到官方原文;第三方来源仅作待核验线索。</t>
+          <t>尚未找到官方原文;第三方来源仅作待核验线索。 Excel 与 CSV 历史数据已合并核对。 字段“当事人名称”存在冲突:保留原值“青海天月德物流有限公司湟源分公司”,新值“青海易创科技有限公司”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
         <v>46294</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46294</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>46293</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>46293</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46294</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2597,7 +2597,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -2715,7 +2719,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ17" s="2" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -4167,7 +4175,7 @@
         <v>46286</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -4289,7 +4297,7 @@
         <v>46286</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
@@ -5309,7 +5317,7 @@
         <v>46280</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -5541,7 +5549,7 @@
         <v>46280</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -5659,7 +5667,7 @@
         <v>46280</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
@@ -5773,7 +5781,7 @@
         <v>46280</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5899,7 @@
         <v>46280</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -6009,7 +6017,7 @@
         <v>46280</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -10899,7 +10907,7 @@
         <v>46254</v>
       </c>
       <c r="AA84" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
@@ -11025,7 +11033,7 @@
         <v>46254</v>
       </c>
       <c r="AA85" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
@@ -13721,7 +13729,7 @@
         <v>46246</v>
       </c>
       <c r="AA107" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
@@ -17059,7 +17067,7 @@
         <v>46234</v>
       </c>
       <c r="AA133" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB133" s="2" t="inlineStr">
         <is>
@@ -17181,7 +17189,7 @@
         <v>46238</v>
       </c>
       <c r="AA134" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB134" s="2" t="inlineStr">
         <is>
@@ -17307,7 +17315,7 @@
         <v>46238</v>
       </c>
       <c r="AA135" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
@@ -18085,7 +18093,7 @@
         <v>46254</v>
       </c>
       <c r="AA141" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB141" s="2" t="inlineStr">
         <is>
@@ -23009,7 +23017,7 @@
         <v>46229</v>
       </c>
       <c r="AA180" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
@@ -24037,7 +24045,7 @@
         <v>46254</v>
       </c>
       <c r="AA188" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB188" s="2" t="inlineStr">
         <is>
@@ -24171,7 +24179,7 @@
         <v>46258</v>
       </c>
       <c r="AA189" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
@@ -24313,7 +24321,7 @@
         <v>46254</v>
       </c>
       <c r="AA190" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
@@ -25515,7 +25523,7 @@
         <v>46258</v>
       </c>
       <c r="AA199" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
@@ -26840,7 +26848,7 @@
         <v>46294</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -26982,7 +26990,7 @@
         <v>46294</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -27114,7 +27122,7 @@
         <v>46296</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -27154,7 +27162,7 @@
       </c>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>尚未找到官方原文;第三方来源仅作待核验线索。</t>
+          <t>尚未找到官方原文;第三方来源仅作待核验线索。 Excel 与 CSV 历史数据已合并核对。 字段“当事人名称”存在冲突:保留原值“青海天月德物流有限公司湟源分公司”,新值“青海易创科技有限公司”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -27246,7 +27254,7 @@
         <v>46296</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -27286,7 +27294,7 @@
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>尚未找到官方原文;第三方来源仅作待核验线索。</t>
+          <t>尚未找到官方原文;第三方来源仅作待核验线索。 Excel 与 CSV 历史数据已合并核对。 字段“当事人名称”存在冲突:保留原值“青海天月德物流有限公司湟源分公司”,新值“青海易创科技有限公司”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -30914,7 +30922,7 @@
         <v>46234</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -34002,7 +34010,7 @@
         <v>46258</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -34144,7 +34152,7 @@
         <v>46254</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -34968,7 +34976,7 @@
         <v>46258</v>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
@@ -36077,7 +36085,7 @@
         <v>46294</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -36203,7 +36211,7 @@
         <v>46294</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -36329,7 +36337,7 @@
         <v>46293</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -36455,7 +36463,7 @@
         <v>46293</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -36577,7 +36585,7 @@
         <v>46294</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -37229,7 +37237,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -37347,7 +37359,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -38151,7 +38167,7 @@
         <v>46286</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -38273,7 +38289,7 @@
         <v>46286</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -38887,7 +38903,7 @@
         <v>46280</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
@@ -39119,7 +39135,7 @@
         <v>46280</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -39237,7 +39253,7 @@
         <v>46280</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -39351,7 +39367,7 @@
         <v>46280</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -39469,7 +39485,7 @@
         <v>46280</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
@@ -39587,7 +39603,7 @@
         <v>46280</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
@@ -43857,7 +43873,7 @@
         <v>46254</v>
       </c>
       <c r="AA66" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
@@ -43983,7 +43999,7 @@
         <v>46254</v>
       </c>
       <c r="AA67" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
@@ -46421,7 +46437,7 @@
         <v>46246</v>
       </c>
       <c r="AA87" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
@@ -48267,7 +48283,7 @@
         <v>46238</v>
       </c>
       <c r="AA102" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
@@ -48393,7 +48409,7 @@
         <v>46238</v>
       </c>
       <c r="AA103" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
@@ -48749,7 +48765,7 @@
         <v>46254</v>
       </c>
       <c r="AA106" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
@@ -51547,7 +51563,7 @@
         <v>46229</v>
       </c>
       <c r="AA129" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB129" s="2" t="inlineStr">
         <is>
@@ -52169,7 +52185,7 @@
         <v>46254</v>
       </c>
       <c r="AA134" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB134" s="2" t="inlineStr">
         <is>
@@ -53134,7 +53150,7 @@
         <v>46296</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -53174,7 +53190,7 @@
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>尚未找到官方原文;第三方来源仅作待核验线索。</t>
+          <t>尚未找到官方原文;第三方来源仅作待核验线索。 Excel 与 CSV 历史数据已合并核对。 字段“当事人名称”存在冲突:保留原值“青海天月德物流有限公司湟源分公司”,新值“青海易创科技有限公司”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -53266,7 +53282,7 @@
         <v>46296</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -53306,7 +53322,7 @@
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>尚未找到官方原文;第三方来源仅作待核验线索。</t>
+          <t>尚未找到官方原文;第三方来源仅作待核验线索。 Excel 与 CSV 历史数据已合并核对。 字段“当事人名称”存在冲突:保留原值“青海天月德物流有限公司湟源分公司”,新值“青海易创科技有限公司”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -53392,7 +53408,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -53518,7 +53534,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -53636,7 +53652,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -54669,7 +54685,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -54795,7 +54811,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -54913,7 +54929,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -54992,7 +55008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M164"/>
+  <dimension ref="A1:M165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -63188,8 +63204,57 @@
         </is>
       </c>
     </row>
+    <row r="165" ht="54" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T18:27:28+08:00</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 至 2026-10-02</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问92页，访问失败330页，持久化待复核320个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M164"/>
+  <autoFilter ref="A1:M165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$168</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -815,7 +815,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -929,7 +933,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1043,7 +1051,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1157,7 +1169,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1271,7 +1287,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1385,7 +1405,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1499,7 +1523,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1613,7 +1641,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1727,7 +1759,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1841,7 +1877,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1955,7 +1995,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -2069,7 +2113,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -2183,7 +2231,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -2297,7 +2349,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -2665,7 +2721,7 @@
         <v>46296</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2797,7 +2853,7 @@
         <v>46296</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -28851,7 +28907,7 @@
         <v>46296</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -28983,7 +29039,7 @@
         <v>46296</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -37844,7 +37900,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -37958,7 +38018,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -38072,7 +38136,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -38186,7 +38254,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -38300,7 +38372,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -38414,7 +38490,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -38528,7 +38608,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -38642,7 +38726,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -38756,7 +38844,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -38870,7 +38962,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -38984,7 +39080,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -39098,7 +39198,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -39212,7 +39316,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -39326,7 +39434,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -56608,7 +56720,7 @@
         <v>46296</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -56740,7 +56852,7 @@
         <v>46296</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -58466,7 +58578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -66817,8 +66929,57 @@
         </is>
       </c>
     </row>
+    <row r="168" ht="54" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T18:24:34+08:00</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 至 2026-10-03</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>466</v>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/: ConnectionError: HTTPSConnectionPool(host='fuji...</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问100页，访问失败359页，持久化待复核349个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M167"/>
+  <autoFilter ref="A1:M168"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -2447,7 +2447,7 @@
         <v>46294</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>46294</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>46296</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>46296</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>46294</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>46294</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>46293</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>46293</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>46294</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>46286</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>46286</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>46280</v>
       </c>
       <c r="AA53" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>46280</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>46280</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>46280</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>46280</v>
       </c>
       <c r="AA58" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>46280</v>
       </c>
       <c r="AA59" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>46254</v>
       </c>
       <c r="AA99" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>46254</v>
       </c>
       <c r="AA100" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>46246</v>
       </c>
       <c r="AA122" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>46234</v>
       </c>
       <c r="AA148" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB148" s="2" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>46238</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>46238</v>
       </c>
       <c r="AA150" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>46254</v>
       </c>
       <c r="AA156" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>46229</v>
       </c>
       <c r="AA195" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>46254</v>
       </c>
       <c r="AA203" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>46258</v>
       </c>
       <c r="AA204" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>46254</v>
       </c>
       <c r="AA205" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>46258</v>
       </c>
       <c r="AA214" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>46294</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>46294</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>46296</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>46296</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>46234</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>46258</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>46254</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>46258</v>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>46294</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>46294</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>46293</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>46293</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>46294</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>46286</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>46286</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>46280</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>46280</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>46280</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46280</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>46280</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>46280</v>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>46254</v>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>46254</v>
       </c>
       <c r="AA82" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>46246</v>
       </c>
       <c r="AA102" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>46238</v>
       </c>
       <c r="AA117" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>46238</v>
       </c>
       <c r="AA118" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>46254</v>
       </c>
       <c r="AA121" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
@@ -55118,7 +55118,7 @@
         <v>46229</v>
       </c>
       <c r="AA144" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>46254</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>46296</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>46296</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -66978,8 +66978,57 @@
         </is>
       </c>
     </row>
+    <row r="169" ht="54" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T18:32:20+08:00</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 至 2026-10-04</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>477</v>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问97页，访问失败373页，持久化待复核363个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M168"/>
+  <autoFilter ref="A1:M169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -781,7 +781,7 @@
         <v>46298</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>46298</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>46298</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>46298</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>46298</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>46298</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>46298</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>46298</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46298</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>46298</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>46298</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>46298</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>46298</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>46298</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46298</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>46298</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>46298</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>46298</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>46298</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>46298</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46298</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46298</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>46298</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>46298</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>46298</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>46298</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>46298</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>46298</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -67027,8 +67027,57 @@
         </is>
       </c>
     </row>
+    <row r="170" ht="54" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T19:02:10+08:00</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 至 2026-10-04</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问94页，访问失败374页，持久化待复核364个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M169"/>
+  <autoFilter ref="A1:M170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -781,7 +781,7 @@
         <v>46298</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>46298</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>46298</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>46298</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>46298</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>46298</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>46298</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>46298</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46298</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>46298</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>46298</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>46298</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>46298</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>46298</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46294</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>46294</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>46294</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>46294</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>46293</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>46293</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>46294</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>46286</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>46286</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>46280</v>
       </c>
       <c r="AA53" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>46280</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>46280</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>46280</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>46280</v>
       </c>
       <c r="AA58" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>46280</v>
       </c>
       <c r="AA59" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>46254</v>
       </c>
       <c r="AA99" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>46254</v>
       </c>
       <c r="AA100" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>46246</v>
       </c>
       <c r="AA122" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>46234</v>
       </c>
       <c r="AA148" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB148" s="2" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>46238</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>46238</v>
       </c>
       <c r="AA150" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>46254</v>
       </c>
       <c r="AA156" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>46229</v>
       </c>
       <c r="AA195" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>46254</v>
       </c>
       <c r="AA203" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>46258</v>
       </c>
       <c r="AA204" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>46254</v>
       </c>
       <c r="AA205" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>46258</v>
       </c>
       <c r="AA214" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>46294</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>46294</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>46234</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>46258</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>46254</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>46258</v>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46298</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>46298</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>46298</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>46298</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>46298</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>46298</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46298</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46298</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>46298</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>46298</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>46298</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>46298</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>46298</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>46298</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>46294</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>46294</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>46293</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>46293</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>46294</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>46286</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>46286</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>46280</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>46280</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>46280</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46280</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>46280</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>46280</v>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>46254</v>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>46254</v>
       </c>
       <c r="AA82" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>46246</v>
       </c>
       <c r="AA102" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>46238</v>
       </c>
       <c r="AA117" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>46238</v>
       </c>
       <c r="AA118" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>46254</v>
       </c>
       <c r="AA121" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
@@ -55118,7 +55118,7 @@
         <v>46229</v>
       </c>
       <c r="AA144" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>46254</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M170"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -67076,8 +67076,57 @@
         </is>
       </c>
     </row>
+    <row r="171" ht="54" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T19:23:15+08:00</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 至 2026-10-05</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>468</v>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/pingtanswj/zfxxgkzl/zfxxgkml/qtgg/: ConnectionError: HTTPSConnectionPool(host='...</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问88页，访问失败374页，持久化待复核364个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M170"/>
+  <autoFilter ref="A1:M171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -2721,7 +2721,7 @@
         <v>46296</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>46296</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>46296</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>46296</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>46296</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>46296</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -67125,8 +67125,57 @@
         </is>
       </c>
     </row>
+    <row r="172" ht="54" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T19:50:08+08:00</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 至 2026-10-05</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v>472</v>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/pingtanswj/zfxxgkzl/zfxxgkml/qtgg/: ConnectionError: HTTPSConnectionPool(host='...</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问90页，访问失败375页，持久化待复核365个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M171"/>
+  <autoFilter ref="A1:M172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -781,7 +781,7 @@
         <v>46298</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>46298</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>46298</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>46298</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>46298</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>46298</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>46298</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>46298</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46298</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>46298</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>46298</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>46298</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>46298</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>46298</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46294</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>46294</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>46296</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>46296</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>46294</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>46286</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>46286</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>46280</v>
       </c>
       <c r="AA53" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>46280</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>46280</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>46280</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>46280</v>
       </c>
       <c r="AA58" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>46280</v>
       </c>
       <c r="AA59" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>46254</v>
       </c>
       <c r="AA99" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>46254</v>
       </c>
       <c r="AA100" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>46246</v>
       </c>
       <c r="AA122" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>46234</v>
       </c>
       <c r="AA148" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB148" s="2" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>46238</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>46238</v>
       </c>
       <c r="AA150" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>46254</v>
       </c>
       <c r="AA156" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>46229</v>
       </c>
       <c r="AA195" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>46254</v>
       </c>
       <c r="AA203" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>46258</v>
       </c>
       <c r="AA204" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>46254</v>
       </c>
       <c r="AA205" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>46258</v>
       </c>
       <c r="AA214" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>46294</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>46294</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>46296</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>46296</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>46234</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>46258</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>46254</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>46258</v>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46298</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>46298</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>46298</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>46298</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>46298</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>46298</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46298</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46298</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>46298</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>46298</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>46298</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>46298</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>46298</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>46298</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>46294</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>46286</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>46286</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>46280</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>46280</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>46280</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46280</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>46280</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>46280</v>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>46254</v>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>46254</v>
       </c>
       <c r="AA82" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>46246</v>
       </c>
       <c r="AA102" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>46238</v>
       </c>
       <c r="AA117" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>46238</v>
       </c>
       <c r="AA118" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>46254</v>
       </c>
       <c r="AA121" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
@@ -55118,7 +55118,7 @@
         <v>46229</v>
       </c>
       <c r="AA144" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>46254</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>46296</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>46296</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M172"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -67174,8 +67174,57 @@
         </is>
       </c>
     </row>
+    <row r="173" ht="54" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06T19:12:34+08:00</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 至 2026-10-06</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>471</v>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问85页，访问失败377页，持久化待复核367个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M172"/>
+  <autoFilter ref="A1:M173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -58578,7 +58578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -67223,8 +67223,57 @@
         </is>
       </c>
     </row>
+    <row r="174" ht="54" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06T19:40:26+08:00</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 至 2026-10-06</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>479</v>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/pingtanswj/zfxxgkzl/zfxxgkml/qtgg/: ConnectionError: HTTPSConnectionPool(host='...</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问85页，访问失败383页，持久化待复核373个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M173"/>
+  <autoFilter ref="A1:M174"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -781,7 +781,7 @@
         <v>46298</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>46298</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>46298</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>46298</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>46298</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>46298</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>46298</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>46298</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46298</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>46298</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>46298</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>46298</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>46298</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>46298</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>46294</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>46286</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>46286</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>46280</v>
       </c>
       <c r="AA53" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>46280</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>46280</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>46280</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>46280</v>
       </c>
       <c r="AA58" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>46280</v>
       </c>
       <c r="AA59" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>46254</v>
       </c>
       <c r="AA99" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>46254</v>
       </c>
       <c r="AA100" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>46246</v>
       </c>
       <c r="AA122" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>46234</v>
       </c>
       <c r="AA148" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB148" s="2" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>46238</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>46238</v>
       </c>
       <c r="AA150" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>46254</v>
       </c>
       <c r="AA156" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>46229</v>
       </c>
       <c r="AA195" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>46254</v>
       </c>
       <c r="AA203" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>46258</v>
       </c>
       <c r="AA204" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>46254</v>
       </c>
       <c r="AA205" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>46258</v>
       </c>
       <c r="AA214" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>46234</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>46258</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>46254</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>46258</v>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46298</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>46298</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>46298</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>46298</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>46298</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>46298</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46298</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46298</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>46298</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>46298</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>46298</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>46298</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>46298</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>46298</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>46294</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>46286</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>46286</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>46280</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>46280</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>46280</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46280</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>46280</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>46280</v>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>46254</v>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>46254</v>
       </c>
       <c r="AA82" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>46246</v>
       </c>
       <c r="AA102" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>46238</v>
       </c>
       <c r="AA117" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>46238</v>
       </c>
       <c r="AA118" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>46254</v>
       </c>
       <c r="AA121" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
@@ -55118,7 +55118,7 @@
         <v>46229</v>
       </c>
       <c r="AA144" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>46254</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M174"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -67272,8 +67272,57 @@
         </is>
       </c>
     </row>
+    <row r="175" ht="54" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T19:00:28+08:00</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 至 2026-10-07</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>468</v>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问80页，访问失败384页，持久化待复核374个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M174"/>
+  <autoFilter ref="A1:M175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$176</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -58578,7 +58578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M175"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -67321,8 +67321,57 @@
         </is>
       </c>
     </row>
+    <row r="176" ht="54" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T19:30:42+08:00</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 至 2026-10-07</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>466</v>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/: ConnectionError: HTTPSConnectionPool(host='fuji...</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问79页，访问失败383页，持久化待复核373个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M175"/>
+  <autoFilter ref="A1:M176"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$177</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -3715,7 +3715,7 @@
         <v>46294</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>46254</v>
       </c>
       <c r="AA99" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>46254</v>
       </c>
       <c r="AA100" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>46246</v>
       </c>
       <c r="AA122" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>46234</v>
       </c>
       <c r="AA148" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB148" s="2" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>46238</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>46238</v>
       </c>
       <c r="AA150" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>46254</v>
       </c>
       <c r="AA156" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>46229</v>
       </c>
       <c r="AA195" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>46254</v>
       </c>
       <c r="AA203" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>46258</v>
       </c>
       <c r="AA204" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>46254</v>
       </c>
       <c r="AA205" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>46258</v>
       </c>
       <c r="AA214" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>46234</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>46258</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>46254</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>46258</v>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>46294</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>46254</v>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>46254</v>
       </c>
       <c r="AA82" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>46246</v>
       </c>
       <c r="AA102" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>46238</v>
       </c>
       <c r="AA117" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>46238</v>
       </c>
       <c r="AA118" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>46254</v>
       </c>
       <c r="AA121" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
@@ -55118,7 +55118,7 @@
         <v>46229</v>
       </c>
       <c r="AA144" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>46254</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -58499,7 +58499,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M176"/>
+  <dimension ref="A1:M177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -67370,8 +67370,57 @@
         </is>
       </c>
     </row>
+    <row r="177" ht="54" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T19:18:01+08:00</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 至 2026-10-08</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问75页，访问失败387页，持久化待复核377个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M176"/>
+  <autoFilter ref="A1:M177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -781,7 +781,7 @@
         <v>46298</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>46298</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>46298</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>46298</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>46298</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>46298</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>46298</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>46298</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46298</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>46298</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>46298</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>46298</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>46298</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>46298</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>46296</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AJ31" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://dalian.chinatax.gov.cn/art/2026/9/24/art_1715_711161.html”,新值“http://dalian.chinatax.gov.cn/art/2026/9/24/art_2892_711160.html”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>46296</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AJ32" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://dalian.chinatax.gov.cn/art/2026/9/24/art_1715_711161.html”,新值“http://dalian.chinatax.gov.cn/art/2026/9/24/art_2892_711160.html”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5945,7 @@
         <v>46286</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>46286</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>46280</v>
       </c>
       <c r="AA53" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>46280</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>46280</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>46280</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>46280</v>
       </c>
       <c r="AA58" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>46280</v>
       </c>
       <c r="AA59" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46298</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>46298</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>46298</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>46298</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>46298</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>46298</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46298</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46298</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>46298</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>46298</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>46298</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>46298</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>46298</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>46298</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>46296</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="AJ26" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://dalian.chinatax.gov.cn/art/2026/9/24/art_1715_711161.html”,新值“http://dalian.chinatax.gov.cn/art/2026/9/24/art_2892_711160.html”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -40880,7 +40880,7 @@
         <v>46296</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
       </c>
       <c r="AJ27" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://dalian.chinatax.gov.cn/art/2026/9/24/art_1715_711161.html”,新值“http://dalian.chinatax.gov.cn/art/2026/9/24/art_2892_711160.html”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -41722,7 +41722,7 @@
         <v>46286</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>46286</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>46280</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>46280</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>46280</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46280</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>46280</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>46280</v>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M177"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -67419,8 +67419,57 @@
         </is>
       </c>
     </row>
+    <row r="178" ht="54" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T19:46:27+08:00</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 至 2026-10-08</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>468</v>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问79页，访问失败387页，持久化待复核377个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M177"/>
+  <autoFilter ref="A1:M178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$182</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -815,7 +815,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -895,7 +899,7 @@
         <v>46304</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -39092,7 +39096,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -39172,7 +39180,7 @@
         <v>46304</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -60374,7 +60382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M181"/>
+  <dimension ref="A1:M182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -69423,8 +69431,57 @@
         </is>
       </c>
     </row>
+    <row r="182" ht="54" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10T19:01:08+08:00</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 至 2026-10-10</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n">
+        <v>481</v>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问82页，访问失败392页，持久化待复核382个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M181"/>
+  <autoFilter ref="A1:M182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -781,7 +781,7 @@
         <v>46305</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>46294</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>46296</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>46296</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>46286</v>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>46286</v>
       </c>
       <c r="AA47" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>46280</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>46280</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>46280</v>
       </c>
       <c r="AA58" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>46280</v>
       </c>
       <c r="AA59" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>46280</v>
       </c>
       <c r="AA60" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>46280</v>
       </c>
       <c r="AA61" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>46254</v>
       </c>
       <c r="AA102" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>46254</v>
       </c>
       <c r="AA103" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>46246</v>
       </c>
       <c r="AA127" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>46234</v>
       </c>
       <c r="AA153" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB153" s="2" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>46238</v>
       </c>
       <c r="AA154" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>46238</v>
       </c>
       <c r="AA155" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB155" s="2" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>46254</v>
       </c>
       <c r="AA161" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB161" s="2" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>46229</v>
       </c>
       <c r="AA202" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB202" s="2" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>46254</v>
       </c>
       <c r="AA210" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>46258</v>
       </c>
       <c r="AA211" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB211" s="2" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>46254</v>
       </c>
       <c r="AA212" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB212" s="2" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>46258</v>
       </c>
       <c r="AA221" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>46234</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>46258</v>
       </c>
       <c r="AA58" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>46254</v>
       </c>
       <c r="AA59" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>46258</v>
       </c>
       <c r="AA65" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>46305</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -41572,7 +41572,7 @@
         <v>46294</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>46296</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>46296</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>46286</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
@@ -43276,7 +43276,7 @@
         <v>46286</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>46280</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>46280</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>46280</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>46280</v>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>46280</v>
       </c>
       <c r="AA47" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>46280</v>
       </c>
       <c r="AA48" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>46254</v>
       </c>
       <c r="AA84" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>46254</v>
       </c>
       <c r="AA85" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>46246</v>
       </c>
       <c r="AA107" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>46238</v>
       </c>
       <c r="AA122" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>46238</v>
       </c>
       <c r="AA123" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>46254</v>
       </c>
       <c r="AA126" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>46229</v>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
@@ -57538,7 +57538,7 @@
         <v>46254</v>
       </c>
       <c r="AA154" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
@@ -58782,7 +58782,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -59026,7 +59026,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -60059,7 +60059,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -60185,7 +60185,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -60303,7 +60303,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -60382,7 +60382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M182"/>
+  <dimension ref="A1:M183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -69480,8 +69480,57 @@
         </is>
       </c>
     </row>
+    <row r="183" ht="54" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11T18:46:11+08:00</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 至 2026-10-11</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/: ConnectionError: HTTPSConnectionPool(host='fuji...</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问88页，访问失败393页，持久化待复核383个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M182"/>
+  <autoFilter ref="A1:M183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -943,7 +943,7 @@
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
         <v>46306</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1307,7 +1307,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1391,7 +1395,7 @@
         <v>46306</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1425,7 +1429,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -4439,7 +4447,7 @@
         <v>46294</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
@@ -5057,7 +5065,7 @@
         <v>46296</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
@@ -5179,7 +5187,7 @@
         <v>46296</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -6669,7 +6677,7 @@
         <v>46286</v>
       </c>
       <c r="AA50" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
@@ -6791,7 +6799,7 @@
         <v>46286</v>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
@@ -7811,7 +7819,7 @@
         <v>46280</v>
       </c>
       <c r="AA59" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
@@ -8043,7 +8051,7 @@
         <v>46280</v>
       </c>
       <c r="AA61" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
@@ -8161,7 +8169,7 @@
         <v>46280</v>
       </c>
       <c r="AA62" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
@@ -8275,7 +8283,7 @@
         <v>46280</v>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
@@ -8393,7 +8401,7 @@
         <v>46280</v>
       </c>
       <c r="AA64" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
@@ -8511,7 +8519,7 @@
         <v>46280</v>
       </c>
       <c r="AA65" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
@@ -13523,7 +13531,7 @@
         <v>46254</v>
       </c>
       <c r="AA106" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
@@ -13649,7 +13657,7 @@
         <v>46254</v>
       </c>
       <c r="AA107" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
@@ -16589,7 +16597,7 @@
         <v>46246</v>
       </c>
       <c r="AA131" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
@@ -19927,7 +19935,7 @@
         <v>46234</v>
       </c>
       <c r="AA157" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
@@ -20049,7 +20057,7 @@
         <v>46238</v>
       </c>
       <c r="AA158" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
@@ -20175,7 +20183,7 @@
         <v>46238</v>
       </c>
       <c r="AA159" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
@@ -26167,7 +26175,7 @@
         <v>46229</v>
       </c>
       <c r="AA206" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
@@ -27195,7 +27203,7 @@
         <v>46254</v>
       </c>
       <c r="AA214" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
@@ -28673,7 +28681,7 @@
         <v>46258</v>
       </c>
       <c r="AA225" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
@@ -34103,7 +34111,7 @@
         <v>46234</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -38447,7 +38455,7 @@
         <v>46258</v>
       </c>
       <c r="AA65" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
@@ -39718,7 +39726,7 @@
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -39844,7 +39852,7 @@
       </c>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -40048,7 +40056,7 @@
         <v>46306</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -40082,7 +40090,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -40166,7 +40178,7 @@
         <v>46306</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -40200,7 +40212,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -42554,7 +42570,7 @@
         <v>46294</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
@@ -43172,7 +43188,7 @@
         <v>46296</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
@@ -43294,7 +43310,7 @@
         <v>46296</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -44136,7 +44152,7 @@
         <v>46286</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -44258,7 +44274,7 @@
         <v>46286</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
@@ -44872,7 +44888,7 @@
         <v>46280</v>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
@@ -45104,7 +45120,7 @@
         <v>46280</v>
       </c>
       <c r="AA48" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
@@ -45222,7 +45238,7 @@
         <v>46280</v>
       </c>
       <c r="AA49" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
@@ -45336,7 +45352,7 @@
         <v>46280</v>
       </c>
       <c r="AA50" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
@@ -45454,7 +45470,7 @@
         <v>46280</v>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
@@ -45572,7 +45588,7 @@
         <v>46280</v>
       </c>
       <c r="AA52" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
@@ -49964,7 +49980,7 @@
         <v>46254</v>
       </c>
       <c r="AA88" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
@@ -50090,7 +50106,7 @@
         <v>46254</v>
       </c>
       <c r="AA89" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
@@ -52772,7 +52788,7 @@
         <v>46246</v>
       </c>
       <c r="AA111" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
@@ -54618,7 +54634,7 @@
         <v>46238</v>
       </c>
       <c r="AA126" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
@@ -54744,7 +54760,7 @@
         <v>46238</v>
       </c>
       <c r="AA127" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
@@ -57898,7 +57914,7 @@
         <v>46229</v>
       </c>
       <c r="AA153" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB153" s="2" t="inlineStr">
         <is>
@@ -58520,7 +58536,7 @@
         <v>46254</v>
       </c>
       <c r="AA158" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
@@ -59770,7 +59786,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -59896,7 +59912,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -60014,7 +60030,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -61047,7 +61063,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -61173,7 +61189,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -61291,7 +61307,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -61370,7 +61386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M184"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -70570,8 +70586,57 @@
         </is>
       </c>
     </row>
+    <row r="185" ht="54" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12T19:52:13+08:00</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 至 2026-10-12</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G185" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I185" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/pingtanswj/zfxxgkzl/zfxxgkml/qtgg/: ConnectionError: HTTPSConnectionPool(host='...</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问74页，访问失败407页，持久化待复核397个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M184"/>
+  <autoFilter ref="A1:M185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日运行日志" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文书汇总'!$A$1:$AJ$231</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'完整文书'!$A$1:$AJ$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$162</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ230"/>
+  <dimension ref="A1:AJ231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -903,7 +903,7 @@
         <v>46306</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46306</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>46304</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“官方发布日期”存在冲突:保留原值“2026-10-08”,新值“2026-10-09”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://jiangsu.chinatax.gov.cn/art/2026/10/8/art_9566_1790007.html”,新值“https://jiangsu.chinatax.gov.cn/art/2026/10/9/art_9566_1790687.html”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
         <v>46264</v>
       </c>
       <c r="AA93" s="4" t="n">
-        <v>46268</v>
+        <v>46307</v>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>46264</v>
       </c>
       <c r="AA94" s="4" t="n">
-        <v>46268</v>
+        <v>46307</v>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>46254</v>
       </c>
       <c r="AA165" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>46229</v>
       </c>
       <c r="AA182" s="4" t="n">
-        <v>46263</v>
+        <v>46307</v>
       </c>
       <c r="AB182" s="2" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>46229</v>
       </c>
       <c r="AA183" s="4" t="n">
-        <v>46263</v>
+        <v>46307</v>
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>46254</v>
       </c>
       <c r="AA187" s="4" t="n">
-        <v>46263</v>
+        <v>46307</v>
       </c>
       <c r="AB187" s="2" t="inlineStr">
         <is>
@@ -24595,47 +24595,47 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>62</v>
+        <v>234</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>CASE-8ad048252137a915</t>
+          <t>CASE-f77ed45b302a9f5d</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>DOC-0719b49b0466ec3f</t>
+          <t>DOC-73433b3e087ef737</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第二稽查局</t>
+          <t>国家税务总局嘉兴市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第二稽查局</t>
+          <t>国家税务总局嘉兴市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>常州跃柯隆商贸有限公司</t>
+          <t>嘉兴市昇悦供应链服务有限公司</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>91320412MAENMTKR0P</t>
+          <t>91330424MAEBW7AXXK</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
@@ -24646,25 +24646,17 @@
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>常税稽二处〔2026〕57号</t>
+          <t>嘉税一稽处〔2026〕67号</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr">
         <is>
-          <t>常税稽二处〔2026〕57号</t>
+          <t>嘉税一稽处〔2026〕67号</t>
         </is>
       </c>
       <c r="O194" s="2" t="inlineStr"/>
-      <c r="P194" s="2" t="inlineStr">
-        <is>
-          <t>根据《税务处理决定书》(常税稽二处〔2026〕57号),你单位让他人为自己开具与实际经营业务情况不符的增值税电子专用发票 2 份以及为他人开具与实际经营业务情况不符的增值税电子专用发票 72 份,属于虚开发票行为。</t>
-        </is>
-      </c>
-      <c r="Q194" s="2" t="inlineStr">
-        <is>
-          <t>增值税</t>
-        </is>
-      </c>
+      <c r="P194" s="2" t="inlineStr"/>
+      <c r="Q194" s="2" t="inlineStr"/>
       <c r="R194" s="3" t="n"/>
       <c r="S194" s="3" t="n"/>
       <c r="T194" s="3" t="n"/>
@@ -24672,18 +24664,18 @@
       <c r="V194" s="2" t="inlineStr"/>
       <c r="W194" s="4" t="n"/>
       <c r="X194" s="4" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="Y194" s="4" t="n"/>
       <c r="Z194" s="4" t="n">
-        <v>46249</v>
+        <v>46307</v>
       </c>
       <c r="AA194" s="4" t="n">
-        <v>46273</v>
+        <v>46307</v>
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
@@ -24701,36 +24693,40 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF194" s="2" t="inlineStr"/>
+      <c r="AF194" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG194" s="2" t="inlineStr"/>
       <c r="AH194" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第二稽查局关于送达常州跃柯隆商贸有限公司税务处理决定书的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局嘉兴市税务局第一稽查局关于送达《税务处理决定书》的公告嘉税一稽公告〔2026〕18号</t>
         </is>
       </c>
       <c r="AI194" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ194" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>CASE-19ac83ce45eed77e</t>
+          <t>CASE-8ad048252137a915</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>DOC-10aa252af6524cfb</t>
+          <t>DOC-0719b49b0466ec3f</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -24740,26 +24736,30 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr"/>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局常州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局无锡市税务局稽查局</t>
+          <t>国家税务总局常州市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>无锡锦久事达商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="inlineStr"/>
+          <t>常州跃柯隆商贸有限公司</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>91320412MAENMTKR0P</t>
+        </is>
+      </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
@@ -24768,18 +24768,18 @@
       </c>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>锡税稽处〔2026〕39号</t>
+          <t>常税稽二处〔2026〕57号</t>
         </is>
       </c>
       <c r="N195" s="2" t="inlineStr">
         <is>
-          <t>锡税稽处〔2026〕39号</t>
+          <t>常税稽二处〔2026〕57号</t>
         </is>
       </c>
       <c r="O195" s="2" t="inlineStr"/>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>你单位开具的1705份增值税专用发票为虚开发票,限在15日内按规定进行相关账务调整。</t>
+          <t>根据《税务处理决定书》(常税稽二处〔2026〕57号),你单位让他人为自己开具与实际经营业务情况不符的增值税电子专用发票 2 份以及为他人开具与实际经营业务情况不符的增值税电子专用发票 72 份,属于虚开发票行为。</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24794,14 +24794,14 @@
       <c r="V195" s="2" t="inlineStr"/>
       <c r="W195" s="4" t="n"/>
       <c r="X195" s="4" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="Y195" s="4" t="n"/>
       <c r="Z195" s="4" t="n">
-        <v>46258</v>
+        <v>46249</v>
       </c>
       <c r="AA195" s="4" t="n">
-        <v>46263</v>
+        <v>46273</v>
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
       <c r="AG195" s="2" t="inlineStr"/>
       <c r="AH195" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局无锡市税务局稽查局关于送达税务处理决定书的公告(无锡锦久事达商贸有限公司)</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第二稽查局关于送达常州跃柯隆商贸有限公司税务处理决定书的公告</t>
         </is>
       </c>
       <c r="AI195" s="2" t="inlineStr">
@@ -24843,16 +24843,16 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>CASE-e40d107c68519ec9</t>
+          <t>CASE-19ac83ce45eed77e</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>DOC-9ef391c9693605f7</t>
+          <t>DOC-10aa252af6524cfb</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -24862,30 +24862,26 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>连云港市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局连云港市税务局第二稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局连云港市税务局第二稽查局</t>
+          <t>国家税务总局无锡市税务局稽查局</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>江苏韵书澜贸易有限公司</t>
-        </is>
-      </c>
-      <c r="J196" s="2" t="inlineStr">
-        <is>
-          <t>91320791MAEC2E07XC</t>
-        </is>
-      </c>
+          <t>无锡锦久事达商贸有限公司</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
@@ -24894,23 +24890,23 @@
       </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>连税稽二处〔2026〕28号</t>
+          <t>锡税稽处〔2026〕39号</t>
         </is>
       </c>
       <c r="N196" s="2" t="inlineStr">
         <is>
-          <t>连税稽二处〔2026〕28号</t>
+          <t>锡税稽处〔2026〕39号</t>
         </is>
       </c>
       <c r="O196" s="2" t="inlineStr"/>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2026年2月6日至2026年4月13日对你(单位)(地址:中国(江苏)自由贸易试验区连云港片区经济技术开发区盐池西路7号办公楼201-186号)2025年1月1日至2025年12月30日涉税情况进行了检查,违法事实及处理决定如下: 且你单位唯一上游泰州南顺含贸易有限公司(以下简称泰州南顺含),已被泰州市稽查局认定为虚开发票走逃失联企业。 经查,你单位自2025年7月15日申报增值税、城市维护建设税、教育费附加、地方教育附加、企业所得税后,一直未有申报。 经查询税收大数据管理平台的交易对象,上游无水电费、房租费、运输费等受票信息。 根据《中华人民共和国发票管理办法》(中华人民共和国国务院令第764号)第二十一条之规定,你单位为他人开具与实际经营业务情况不符的发票,定性为虚开发票,不含税金额3785138.94元,税额492068.06元,价税合计4277207元。</t>
+          <t>你单位开具的1705份增值税专用发票为虚开发票,限在15日内按规定进行相关账务调整。</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>增值税</t>
         </is>
       </c>
       <c r="R196" s="3" t="n"/>
@@ -24918,15 +24914,13 @@
       <c r="T196" s="3" t="n"/>
       <c r="U196" s="3" t="n"/>
       <c r="V196" s="2" t="inlineStr"/>
-      <c r="W196" s="4" t="n">
-        <v>46126</v>
-      </c>
+      <c r="W196" s="4" t="n"/>
       <c r="X196" s="4" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="Y196" s="4" t="n"/>
       <c r="Z196" s="4" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="AA196" s="4" t="n">
         <v>46263</v>
@@ -24951,20 +24945,16 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF196" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF196" s="2" t="inlineStr"/>
       <c r="AG196" s="2" t="inlineStr"/>
       <c r="AH196" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局连云港市税务局第二稽查局税务处理决定书送达公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局无锡市税务局稽查局关于送达税务处理决定书的公告(无锡锦久事达商贸有限公司)</t>
         </is>
       </c>
       <c r="AI196" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ196" s="2" t="inlineStr">
@@ -24975,47 +24965,47 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>CASE-7340a0efacb01147</t>
+          <t>CASE-e40d107c68519ec9</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>DOC-026a5ef7f0de1dbe</t>
+          <t>DOC-9ef391c9693605f7</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
+          <t>连云港市</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局嘉兴市税务局第二稽查局</t>
+          <t>国家税务总局连云港市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局嘉兴市税务局第二稽查局</t>
+          <t>国家税务总局连云港市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>桐乡市高峰贸易有限公司</t>
+          <t>江苏韵书澜贸易有限公司</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>91330483MA29HEQL72</t>
+          <t>91320791MAEC2E07XC</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
@@ -25026,23 +25016,23 @@
       </c>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>嘉税二稽处〔2026〕45号</t>
+          <t>连税稽二处〔2026〕28号</t>
         </is>
       </c>
       <c r="N197" s="2" t="inlineStr">
         <is>
-          <t>嘉税二稽处〔2026〕45号</t>
+          <t>连税稽二处〔2026〕28号</t>
         </is>
       </c>
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>我局于2025年9月15日至2026年3月23日对你单位(地址:桐乡市梧桐街道振兴西路1幢二楼)2009年1月1日至2017年12月31日涉税情况进行了检查,你单位存在以下违法事实: 无其他的税款入库记录,你单位计税依据错误,少缴城镇土地使用税。 根据《中华人民共和国企业所得税法》第一条、第二条、第三条、第四条、第五条、第六条、第二十二条、第五十三条及《国家税务总局关于发布〈企业政策性搬迁所得税管理办法〉的公告》(国家税务总局公告2012年第40号)第三条、第五条、第六条、第十六条的规定,你单位在收到政府土地征收补偿款后直接分配给8名股东,但你单位未将取得的应计入收入总额的财政性资金申报纳税,经计算少缴企业所得税8430203.25元。 根据《中华人民共和国城镇土地使用税暂行条例》第一条、第二条、第三条、第四条、第八条、《调整城镇土地使用税政策促进土地集约节约利用实施办法(试行)》(桐政办发〔2014〕67号)、《调整城镇土地使用税政策促进土地集约节约利用实施办法》(桐政办发〔2015〕98号)的规定,你单位未按规定申报城镇土地使用税,少缴2009年至2017年度城镇土地使用税共计247749.94元。 上述少缴企业所得税、城镇土地使用税的行为已构成偷税,少扣缴个人所得税的行为已构成扣缴义务人不履行代扣代缴义务。</t>
+          <t>我局(所)于2026年2月6日至2026年4月13日对你(单位)(地址:中国(江苏)自由贸易试验区连云港片区经济技术开发区盐池西路7号办公楼201-186号)2025年1月1日至2025年12月30日涉税情况进行了检查,违法事实及处理决定如下: 且你单位唯一上游泰州南顺含贸易有限公司(以下简称泰州南顺含),已被泰州市稽查局认定为虚开发票走逃失联企业。 经查,你单位自2025年7月15日申报增值税、城市维护建设税、教育费附加、地方教育附加、企业所得税后,一直未有申报。 经查询税收大数据管理平台的交易对象,上游无水电费、房租费、运输费等受票信息。 根据《中华人民共和国发票管理办法》(中华人民共和国国务院令第764号)第二十一条之规定,你单位为他人开具与实际经营业务情况不符的发票,定性为虚开发票,不含税金额3785138.94元,税额492068.06元,价税合计4277207元。</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
         <is>
-          <t>企业所得税、个人所得税、城镇土地使用税</t>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R197" s="3" t="n"/>
@@ -25050,7 +25040,9 @@
       <c r="T197" s="3" t="n"/>
       <c r="U197" s="3" t="n"/>
       <c r="V197" s="2" t="inlineStr"/>
-      <c r="W197" s="4" t="n"/>
+      <c r="W197" s="4" t="n">
+        <v>46126</v>
+      </c>
       <c r="X197" s="4" t="n">
         <v>46126</v>
       </c>
@@ -25089,7 +25081,7 @@
       <c r="AG197" s="2" t="inlineStr"/>
       <c r="AH197" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局嘉兴市税务局第二稽查局关于送达《税务处理决定书》(嘉税二稽处〔2026〕45号)、《不予税务行政处罚决定书》(嘉税二稽不罚〔2026〕4号)的公告嘉税二稽公告〔2026〕43号</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局连云港市税务局第二稽查局税务处理决定书送达公告</t>
         </is>
       </c>
       <c r="AI197" s="2" t="inlineStr">
@@ -25105,47 +25097,47 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-7340a0efacb01147</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>DOC-6f25d6b79e123d03</t>
+          <t>DOC-026a5ef7f0de1dbe</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局嘉兴市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局嘉兴市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
+          <t>桐乡市高峰贸易有限公司</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>91520115MAAK0DB335</t>
+          <t>91330483MA29HEQL72</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
@@ -25156,21 +25148,25 @@
       </c>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>嘉税二稽处〔2026〕45号</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O198" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
-      <c r="P198" s="2" t="inlineStr"/>
-      <c r="Q198" s="2" t="inlineStr"/>
+          <t>嘉税二稽处〔2026〕45号</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr"/>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>我局于2025年9月15日至2026年3月23日对你单位(地址:桐乡市梧桐街道振兴西路1幢二楼)2009年1月1日至2017年12月31日涉税情况进行了检查,你单位存在以下违法事实: 无其他的税款入库记录,你单位计税依据错误,少缴城镇土地使用税。 根据《中华人民共和国企业所得税法》第一条、第二条、第三条、第四条、第五条、第六条、第二十二条、第五十三条及《国家税务总局关于发布〈企业政策性搬迁所得税管理办法〉的公告》(国家税务总局公告2012年第40号)第三条、第五条、第六条、第十六条的规定,你单位在收到政府土地征收补偿款后直接分配给8名股东,但你单位未将取得的应计入收入总额的财政性资金申报纳税,经计算少缴企业所得税8430203.25元。 根据《中华人民共和国城镇土地使用税暂行条例》第一条、第二条、第三条、第四条、第八条、《调整城镇土地使用税政策促进土地集约节约利用实施办法(试行)》(桐政办发〔2014〕67号)、《调整城镇土地使用税政策促进土地集约节约利用实施办法》(桐政办发〔2015〕98号)的规定,你单位未按规定申报城镇土地使用税,少缴2009年至2017年度城镇土地使用税共计247749.94元。 上述少缴企业所得税、城镇土地使用税的行为已构成偷税,少扣缴个人所得税的行为已构成扣缴义务人不履行代扣代缴义务。</t>
+        </is>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>企业所得税、个人所得税、城镇土地使用税</t>
+        </is>
+      </c>
       <c r="R198" s="3" t="n"/>
       <c r="S198" s="3" t="n"/>
       <c r="T198" s="3" t="n"/>
@@ -25178,18 +25174,18 @@
       <c r="V198" s="2" t="inlineStr"/>
       <c r="W198" s="4" t="n"/>
       <c r="X198" s="4" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="Y198" s="4" t="n"/>
       <c r="Z198" s="4" t="n">
-        <v>46229</v>
+        <v>46254</v>
       </c>
       <c r="AA198" s="4" t="n">
         <v>46263</v>
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
@@ -25207,16 +25203,20 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF198" s="2" t="inlineStr"/>
+      <c r="AF198" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG198" s="2" t="inlineStr"/>
       <c r="AH198" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局嘉兴市税务局第二稽查局关于送达《税务处理决定书》(嘉税二稽处〔2026〕45号)、《不予税务行政处罚决定书》(嘉税二稽不罚〔2026〕4号)的公告嘉税二稽公告〔2026〕43号</t>
         </is>
       </c>
       <c r="AI198" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ198" s="2" t="inlineStr">
@@ -25227,7 +25227,7 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
+          <t>DOC-6f25d6b79e123d03</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -25273,12 +25273,12 @@
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="N199" s="2" t="inlineStr">
@@ -25349,103 +25349,91 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>CASE-b1782a5113598b13</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>DOC-316ca7f345c80c2a</t>
+          <t>DOC-e8233eb0e06b6e3e</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>福建省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>日照市</t>
-        </is>
-      </c>
-      <c r="F200" s="2" t="inlineStr">
-        <is>
-          <t>平潭综合实验区</t>
-        </is>
-      </c>
+          <t>贵阳市</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局海南省税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局海南省税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>福建平潭长福海运有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>91350128MA8U1EMF5H</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>岚综实税稽处〔2026〕26号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
         <is>
-          <t>岚综实税稽处〔2026〕26号</t>
-        </is>
-      </c>
-      <c r="O200" s="2" t="inlineStr"/>
-      <c r="P200" s="2" t="inlineStr">
-        <is>
-          <t>情况进行了检查,违法事实及处理决定如下: 根据国家税务总局海南省税务局第二稽查局发来的已证实虚开通知单,你公司取得海南洋浦昌源海运有限公司开具的已证实虚开的 根据国家税务总局日照市税务局第一稽查局发来的已证实虚开通知单,你公司取得山东日兴智慧物流有限公司开具的已证实虚开的2份增值税专用发票。 根据《全国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值税专用发票犯罪的决定》、(中华人民共和国主席令第57号)第一条、《中华人民共和国发票管理办法》第二十一条及《国家税务总局关于走逃(失联)企业涉嫌虚开增值税专用发票检查问题的通知》(税总发〔2016〕172号)的规定,认定你公司开具给福建嘉飞运输有限公司、响水德强物流运输有限公司等2家公司的12份增值税专用发票(涉及金额1,108,256.86元,税额99,743.14元,价税合计1,208,000.00元)为虚开增值税专用发票; 认定你公司取得山东万通石油化工集团有限公司、海南洋浦昌源海运有限公司、日照盈润海运有限公司等3家公司开具的36份增值税专用发票(涉及金额23,186,305.80元,税额2,976,922.60元,价税合计26,163,228.40元)为虚开增值税专用发票。</t>
-        </is>
-      </c>
-      <c r="Q200" s="2" t="inlineStr">
-        <is>
-          <t>增值税</t>
-        </is>
-      </c>
+          <t>筑税三稽处〔2026〕17号</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>筑税三稽罚〔2026〕22号</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr"/>
+      <c r="Q200" s="2" t="inlineStr"/>
       <c r="R200" s="3" t="n"/>
       <c r="S200" s="3" t="n"/>
       <c r="T200" s="3" t="n"/>
       <c r="U200" s="3" t="n"/>
-      <c r="V200" s="2" t="inlineStr">
-        <is>
-          <t>号),因文书无法以直接、委托、留置、邮寄的方式送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条规定,将该文书予以公告送达。</t>
-        </is>
-      </c>
+      <c r="V200" s="2" t="inlineStr"/>
       <c r="W200" s="4" t="n"/>
       <c r="X200" s="4" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="Y200" s="4" t="n"/>
       <c r="Z200" s="4" t="n">
-        <v>46254</v>
+        <v>46229</v>
       </c>
       <c r="AA200" s="4" t="n">
         <v>46263</v>
       </c>
       <c r="AB200" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC200" s="2" t="inlineStr">
@@ -25467,9 +25455,7 @@
       <c r="AG200" s="2" t="inlineStr"/>
       <c r="AH200" s="2" t="inlineStr">
         <is>
-          <t>关于送达福建平潭长福海运有限公司《税务处理决定书》的公告_
- 其他公告_
- 国家税务总局平潭综合实验区税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI200" s="2" t="inlineStr">
@@ -25485,47 +25471,51 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-b1782a5113598b13</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>DOC-551df7dc5c028b27</t>
+          <t>DOC-316ca7f345c80c2a</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>福建省</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
-        </is>
-      </c>
-      <c r="F201" s="2" t="inlineStr"/>
+          <t>日照市</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>平潭综合实验区</t>
+        </is>
+      </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局海南省税务局第二稽查局</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局海南省税务局第二稽查局</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>福建平潭长福海运有限公司</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91350128MA8U1EMF5H</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
@@ -25536,40 +25526,48 @@
       </c>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>岚综实税稽处〔2026〕26号</t>
         </is>
       </c>
       <c r="N201" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
-        </is>
-      </c>
-      <c r="O201" s="2" t="inlineStr">
-        <is>
-          <t>来市税二稽罚〔2026〕4号</t>
-        </is>
-      </c>
-      <c r="P201" s="2" t="inlineStr"/>
-      <c r="Q201" s="2" t="inlineStr"/>
+          <t>岚综实税稽处〔2026〕26号</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="inlineStr"/>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t>情况进行了检查,违法事实及处理决定如下: 根据国家税务总局海南省税务局第二稽查局发来的已证实虚开通知单,你公司取得海南洋浦昌源海运有限公司开具的已证实虚开的 根据国家税务总局日照市税务局第一稽查局发来的已证实虚开通知单,你公司取得山东日兴智慧物流有限公司开具的已证实虚开的2份增值税专用发票。 根据《全国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值税专用发票犯罪的决定》、(中华人民共和国主席令第57号)第一条、《中华人民共和国发票管理办法》第二十一条及《国家税务总局关于走逃(失联)企业涉嫌虚开增值税专用发票检查问题的通知》(税总发〔2016〕172号)的规定,认定你公司开具给福建嘉飞运输有限公司、响水德强物流运输有限公司等2家公司的12份增值税专用发票(涉及金额1,108,256.86元,税额99,743.14元,价税合计1,208,000.00元)为虚开增值税专用发票; 认定你公司取得山东万通石油化工集团有限公司、海南洋浦昌源海运有限公司、日照盈润海运有限公司等3家公司开具的36份增值税专用发票(涉及金额23,186,305.80元,税额2,976,922.60元,价税合计26,163,228.40元)为虚开增值税专用发票。</t>
+        </is>
+      </c>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>增值税</t>
+        </is>
+      </c>
       <c r="R201" s="3" t="n"/>
       <c r="S201" s="3" t="n"/>
       <c r="T201" s="3" t="n"/>
       <c r="U201" s="3" t="n"/>
-      <c r="V201" s="2" t="inlineStr"/>
+      <c r="V201" s="2" t="inlineStr">
+        <is>
+          <t>号),因文书无法以直接、委托、留置、邮寄的方式送达,现根据《中华人民共和国税收征收管理法实施细则》第一百零六条规定,将该文书予以公告送达。</t>
+        </is>
+      </c>
       <c r="W201" s="4" t="n"/>
       <c r="X201" s="4" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="Y201" s="4" t="n"/>
       <c r="Z201" s="4" t="n">
-        <v>46229</v>
+        <v>46254</v>
       </c>
       <c r="AA201" s="4" t="n">
-        <v>46273</v>
+        <v>46263</v>
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
@@ -25591,7 +25589,9 @@
       <c r="AG201" s="2" t="inlineStr"/>
       <c r="AH201" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>关于送达福建平潭长福海运有限公司《税务处理决定书》的公告_
+ 其他公告_
+ 国家税务总局平潭综合实验区税务局</t>
         </is>
       </c>
       <c r="AI201" s="2" t="inlineStr">
@@ -25607,7 +25607,7 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>DOC-21f0193b66d5c3e9</t>
+          <t>DOC-551df7dc5c028b27</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -25653,12 +25653,12 @@
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>来市税二稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr">
@@ -25729,68 +25729,68 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>175</v>
+        <v>9</v>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>CASE-ac24bc507b11c4b9</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>DOC-023f2cf01f84fa12</t>
+          <t>DOC-21f0193b66d5c3e9</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>乌鲁木齐市</t>
+          <t>来宾市</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局乌鲁木齐市税务局稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局乌鲁木齐市税务局稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>新疆伍纬智兴工程设计有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>91650102MA7AB6M720</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>乌税稽处〔2026〕35号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="N203" s="2" t="inlineStr">
         <is>
-          <t>乌税稽处〔2026〕35号</t>
+          <t>来市税二稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
-          <t>乌税稽罚〔2026〕26号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="P203" s="2" t="inlineStr"/>
@@ -25802,14 +25802,14 @@
       <c r="V203" s="2" t="inlineStr"/>
       <c r="W203" s="4" t="n"/>
       <c r="X203" s="4" t="n">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="Y203" s="4" t="n"/>
       <c r="Z203" s="4" t="n">
-        <v>46286</v>
+        <v>46229</v>
       </c>
       <c r="AA203" s="4" t="n">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
@@ -25831,31 +25831,27 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF203" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF203" s="2" t="inlineStr"/>
       <c r="AG203" s="2" t="inlineStr"/>
       <c r="AH203" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局乌鲁木齐市税务局-通知公告-国家税务总局乌鲁木齐市税务局稽查局关于送达《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI203" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ203" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
@@ -25864,7 +25860,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>DOC-7e3d72fa54372f41</t>
+          <t>DOC-023f2cf01f84fa12</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -25901,12 +25897,12 @@
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>乌税稽罚〔2026〕26号</t>
+          <t>乌税稽处〔2026〕35号</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
@@ -25981,66 +25977,70 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>CASE-eb7e9c22bd97f211</t>
+          <t>CASE-ac24bc507b11c4b9</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>DOC-4c99e9a228472ee1</t>
+          <t>DOC-7e3d72fa54372f41</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>乌鲁木齐市</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局无锡市税务局第一稽查局</t>
+          <t>国家税务总局乌鲁木齐市税务局稽查局</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局无锡市税务局第一稽查局</t>
+          <t>国家税务总局乌鲁木齐市税务局稽查局</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>宜兴市华欧金属材料有限公司</t>
+          <t>新疆伍纬智兴工程设计有限公司</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>91320282MA1MMJ8YXD</t>
+          <t>91650102MA7AB6M720</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>锡税一稽处〔2026〕71号</t>
+          <t>乌税稽罚〔2026〕26号</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>锡税一稽处〔2026〕71号</t>
-        </is>
-      </c>
-      <c r="O205" s="2" t="inlineStr"/>
+          <t>乌税稽处〔2026〕35号</t>
+        </is>
+      </c>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>乌税稽罚〔2026〕26号</t>
+        </is>
+      </c>
       <c r="P205" s="2" t="inlineStr"/>
       <c r="Q205" s="2" t="inlineStr"/>
       <c r="R205" s="3" t="n"/>
@@ -26050,14 +26050,14 @@
       <c r="V205" s="2" t="inlineStr"/>
       <c r="W205" s="4" t="n"/>
       <c r="X205" s="4" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="Y205" s="4" t="n"/>
       <c r="Z205" s="4" t="n">
-        <v>46250</v>
+        <v>46286</v>
       </c>
       <c r="AA205" s="4" t="n">
-        <v>46263</v>
+        <v>46286</v>
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
@@ -26079,86 +26079,90 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF205" s="2" t="inlineStr"/>
+      <c r="AF205" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG205" s="2" t="inlineStr"/>
       <c r="AH205" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局无锡市税务局第一稽查局关于送达《税务处理决定书》的公告(宜兴市华欧金属材料有限公司)</t>
+          <t>国家税务总局乌鲁木齐市税务局-通知公告-国家税务总局乌鲁木齐市税务局稽查局关于送达《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI205" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ205" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>CASE-393a878d93a22709</t>
+          <t>CASE-eb7e9c22bd97f211</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>DOC-cda8cba853896b18</t>
+          <t>DOC-4c99e9a228472ee1</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F206" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
+          <t>无锡市</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H206" s="2" t="inlineStr"/>
+          <t>国家税务总局无锡市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局无锡市税务局第一稽查局</t>
+        </is>
+      </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>广州赞荣服装有限公司</t>
+          <t>宜兴市华欧金属材料有限公司</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>91440113MA59AJFJ1J</t>
+          <t>91320282MA1MMJ8YXD</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M206" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N206" s="2" t="inlineStr"/>
-      <c r="O206" s="2" t="inlineStr">
-        <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
+          <t>锡税一稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>锡税一稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr"/>
       <c r="Q206" s="2" t="inlineStr"/>
       <c r="R206" s="3" t="n"/>
@@ -26168,14 +26172,14 @@
       <c r="V206" s="2" t="inlineStr"/>
       <c r="W206" s="4" t="n"/>
       <c r="X206" s="4" t="n">
-        <v>46091</v>
+        <v>46111</v>
       </c>
       <c r="Y206" s="4" t="n"/>
       <c r="Z206" s="4" t="n">
-        <v>46229</v>
+        <v>46250</v>
       </c>
       <c r="AA206" s="4" t="n">
-        <v>46307</v>
+        <v>46263</v>
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
@@ -26189,7 +26193,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE206" s="5" t="inlineStr">
@@ -26197,131 +26201,107 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF206" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF206" s="2" t="inlineStr"/>
       <c r="AG206" s="2" t="inlineStr"/>
       <c r="AH206" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局无锡市税务局第一稽查局关于送达《税务处理决定书》的公告(宜兴市华欧金属材料有限公司)</t>
         </is>
       </c>
       <c r="AI206" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ206" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>CASE-f94bf08964abff5a</t>
+          <t>CASE-393a878d93a22709</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>DOC-4574b1aadef8f30d</t>
+          <t>DOC-cda8cba853896b18</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="inlineStr"/>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
-        </is>
-      </c>
-      <c r="H207" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局常州市税务局稽查局</t>
-        </is>
-      </c>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr"/>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>常州市文杰车辆配件厂</t>
+          <t>广州赞荣服装有限公司</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>91320411799075280A</t>
-        </is>
-      </c>
-      <c r="K207" s="2" t="inlineStr">
-        <is>
-          <t>朱某</t>
-        </is>
-      </c>
+          <t>91440113MA59AJFJ1J</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M207" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕73号</t>
-        </is>
-      </c>
-      <c r="N207" s="2" t="inlineStr">
-        <is>
-          <t>常税稽处〔2026〕73号</t>
-        </is>
-      </c>
-      <c r="O207" s="2" t="inlineStr"/>
-      <c r="P207" s="2" t="inlineStr">
-        <is>
-          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
-        </is>
-      </c>
-      <c r="Q207" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R207" s="3" t="n">
-        <v>179137.12</v>
-      </c>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr"/>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr"/>
+      <c r="Q207" s="2" t="inlineStr"/>
+      <c r="R207" s="3" t="n"/>
       <c r="S207" s="3" t="n"/>
       <c r="T207" s="3" t="n"/>
       <c r="U207" s="3" t="n"/>
-      <c r="V207" s="2" t="inlineStr">
-        <is>
-          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市</t>
-        </is>
-      </c>
-      <c r="W207" s="4" t="n">
-        <v>46044</v>
-      </c>
+      <c r="V207" s="2" t="inlineStr"/>
+      <c r="W207" s="4" t="n"/>
       <c r="X207" s="4" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="Y207" s="4" t="n"/>
       <c r="Z207" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA207" s="4" t="n">
-        <v>46263</v>
+        <v>46307</v>
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
@@ -26331,7 +26311,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE207" s="5" t="inlineStr">
@@ -26347,66 +26327,70 @@
       <c r="AG207" s="2" t="inlineStr"/>
       <c r="AH207" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
         </is>
       </c>
       <c r="AI207" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ207" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“主要违法事实”已根据官方附件重新解析。 字段“处理或处罚结果”已根据官方附件重新解析。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>CASE-cd07b952e6e3cbfe</t>
+          <t>CASE-f94bf08964abff5a</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>DOC-b08bd7ef9ec8845c</t>
+          <t>DOC-4574b1aadef8f30d</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局嘉兴市税务局第一稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局嘉兴市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市全胜贵金属有限公司</t>
+          <t>常州市文杰车辆配件厂</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>91330400MA28A96A7D</t>
-        </is>
-      </c>
-      <c r="K208" s="2" t="inlineStr"/>
+          <t>91320411799075280A</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>朱某</t>
+        </is>
+      </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -26414,36 +26398,52 @@
       </c>
       <c r="M208" s="2" t="inlineStr">
         <is>
-          <t>嘉税一稽处〔2026〕41号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="N208" s="2" t="inlineStr">
         <is>
-          <t>嘉税一稽处〔2026〕41号</t>
+          <t>常税稽处〔2026〕73号</t>
         </is>
       </c>
       <c r="O208" s="2" t="inlineStr"/>
-      <c r="P208" s="2" t="inlineStr"/>
-      <c r="Q208" s="2" t="inlineStr"/>
-      <c r="R208" s="3" t="n"/>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t>月1日至2025年7月15日涉税情况进行了检查, 违法事实及处 述发票已被常州市税务局第一稽查局定性为虚开。 资金往来时,亦与严某个人账户存在交易,虚开团伙利用严某个 人账户提前向你单位垫付虚开资金, 你单位后通过对公账户向虚 簿上虚列进项税额及虚列支出,达到少缴税款的目的。 家税务总局关于纳税人虚开增值税专用发票征补税款问题的公</t>
+        </is>
+      </c>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R208" s="3" t="n">
+        <v>179137.12</v>
+      </c>
       <c r="S208" s="3" t="n"/>
       <c r="T208" s="3" t="n"/>
       <c r="U208" s="3" t="n"/>
-      <c r="V208" s="2" t="inlineStr"/>
-      <c r="W208" s="4" t="n"/>
+      <c r="V208" s="2" t="inlineStr">
+        <is>
+          <t>份,需要补缴2017年9月增值税16211.46元,城市维护建设税 需要补缴增值税22261.06元,城市维护建设税1558.27元,教 需要补缴增值税36353.98元,城市维护建设税2544.78元,教 需要补缴增值税24057.63元,城市维护建设税1684.03元,教 需要补缴增值税19468.89元,城市维护建设税1362.82元,教 需要补缴增值税21794.95元,城市维护建设税1525.65元,教 需要补缴增值税32586.07元,城市维护建设税2281.02元,教 金额,需要补缴增值税644.16元,城市维护建设税45.09元, 金额,需要补缴增值税30.21元,城市维护建设税2.11元,教 金额,需要补缴增值税1264.25元,城市维护建设税88.5元, 金额,需要补缴增值税4464.46元,城市维护建设税312.51元, 合计需补缴增值税179137.12元, 城市维护建设税12539.58 本次检查决定追缴少申报缴纳的增值税179137.12元、 城市</t>
+        </is>
+      </c>
+      <c r="W208" s="4" t="n">
+        <v>46044</v>
+      </c>
       <c r="X208" s="4" t="n">
         <v>46090</v>
       </c>
       <c r="Y208" s="4" t="n"/>
       <c r="Z208" s="4" t="n">
-        <v>46254</v>
+        <v>46229</v>
       </c>
       <c r="AA208" s="4" t="n">
         <v>46263</v>
       </c>
       <c r="AB208" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC208" s="2" t="inlineStr">
@@ -26469,7 +26469,7 @@
       <c r="AG208" s="2" t="inlineStr"/>
       <c r="AH208" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局嘉兴市税务局第一稽查局关于送达《税务处理决定书》的公告(嘉税一稽公告(2026)6号)</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州市文杰车辆配件厂《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI208" s="2" t="inlineStr">
@@ -26479,53 +26479,53 @@
       </c>
       <c r="AJ208" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“主要违法事实”已根据官方附件重新解析。 字段“处理或处罚结果”已根据官方附件重新解析。</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>CASE-0b4a4519ba4f5ad9</t>
+          <t>CASE-cd07b952e6e3cbfe</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>DOC-5376b9bae81cfc82</t>
+          <t>DOC-b08bd7ef9ec8845c</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局嘉兴市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局稽查局</t>
+          <t>国家税务总局嘉兴市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>常州好佳车辆配件有限公司</t>
+          <t>嘉兴市全胜贵金属有限公司</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>91320411094264460B</t>
+          <t>91330400MA28A96A7D</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr"/>
@@ -26536,12 +26536,12 @@
       </c>
       <c r="M209" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
+          <t>嘉税一稽处〔2026〕41号</t>
         </is>
       </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
+          <t>嘉税一稽处〔2026〕41号</t>
         </is>
       </c>
       <c r="O209" s="2" t="inlineStr"/>
@@ -26554,11 +26554,11 @@
       <c r="V209" s="2" t="inlineStr"/>
       <c r="W209" s="4" t="n"/>
       <c r="X209" s="4" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="Y209" s="4" t="n"/>
       <c r="Z209" s="4" t="n">
-        <v>46229</v>
+        <v>46254</v>
       </c>
       <c r="AA209" s="4" t="n">
         <v>46263</v>
@@ -26591,7 +26591,7 @@
       <c r="AG209" s="2" t="inlineStr"/>
       <c r="AH209" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局嘉兴市税务局第一稽查局关于送达《税务处理决定书》的公告(嘉税一稽公告(2026)6号)</t>
         </is>
       </c>
       <c r="AI209" s="2" t="inlineStr">
@@ -26607,54 +26607,50 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>169</v>
+        <v>13</v>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>CASE-fff2e023850214a5</t>
+          <t>CASE-0b4a4519ba4f5ad9</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>DOC-089127a6678b838f</t>
+          <t>DOC-5376b9bae81cfc82</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>巴音郭楞蒙古自治州</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>库尔勒兆庆商贸有限公司</t>
+          <t>常州好佳车辆配件有限公司</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>91652801MA77Q8JE59</t>
-        </is>
-      </c>
-      <c r="K210" s="2" t="inlineStr">
-        <is>
-          <t>冯某玲及实际控制人王某涛</t>
-        </is>
-      </c>
+          <t>91320411094264460B</t>
+        </is>
+      </c>
+      <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -26662,19 +26658,15 @@
       </c>
       <c r="M210" s="2" t="inlineStr">
         <is>
-          <t>巴税稽处〔2026〕11号</t>
+          <t>常税稽处〔2026〕71号</t>
         </is>
       </c>
       <c r="N210" s="2" t="inlineStr">
         <is>
-          <t>巴税稽处〔2026〕11号</t>
-        </is>
-      </c>
-      <c r="O210" s="2" t="inlineStr">
-        <is>
-          <t>巴税稽罚〔2026〕13号</t>
-        </is>
-      </c>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr"/>
       <c r="P210" s="2" t="inlineStr"/>
       <c r="Q210" s="2" t="inlineStr"/>
       <c r="R210" s="3" t="n"/>
@@ -26684,14 +26676,14 @@
       <c r="V210" s="2" t="inlineStr"/>
       <c r="W210" s="4" t="n"/>
       <c r="X210" s="4" t="n">
-        <v>46077</v>
+        <v>46087</v>
       </c>
       <c r="Y210" s="4" t="n"/>
       <c r="Z210" s="4" t="n">
-        <v>46286</v>
+        <v>46229</v>
       </c>
       <c r="AA210" s="4" t="n">
-        <v>46286</v>
+        <v>46263</v>
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
@@ -26721,7 +26713,7 @@
       <c r="AG210" s="2" t="inlineStr"/>
       <c r="AH210" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局巴州税务局-通知公告-国家税务总局巴音郭楞蒙古自治州税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI210" s="2" t="inlineStr">
@@ -26731,13 +26723,13 @@
       </c>
       <c r="AJ210" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
@@ -26746,7 +26738,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>DOC-73007b3650cf14c2</t>
+          <t>DOC-089127a6678b838f</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -26787,12 +26779,12 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M211" s="2" t="inlineStr">
         <is>
-          <t>巴税稽罚〔2026〕13号</t>
+          <t>巴税稽处〔2026〕11号</t>
         </is>
       </c>
       <c r="N211" s="2" t="inlineStr">
@@ -26867,101 +26859,95 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>CASE-61b9b55a9d3357c7</t>
+          <t>CASE-fff2e023850214a5</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>DOC-1228a9c92b2b0632</t>
+          <t>DOC-73007b3650cf14c2</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>巴音郭楞蒙古自治州</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局第一稽查局</t>
+          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>常州市三鹏机械有限公司</t>
+          <t>库尔勒兆庆商贸有限公司</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>91320404732260748Q</t>
-        </is>
-      </c>
-      <c r="K212" s="2" t="inlineStr"/>
+          <t>91652801MA77Q8JE59</t>
+        </is>
+      </c>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t>冯某玲及实际控制人王某涛</t>
+        </is>
+      </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M212" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>巴税稽罚〔2026〕13号</t>
         </is>
       </c>
       <c r="N212" s="2" t="inlineStr">
         <is>
-          <t>常税稽一处〔2026〕35号</t>
+          <t>巴税稽处〔2026〕11号</t>
         </is>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>巴税稽罚〔2026〕13号</t>
         </is>
       </c>
       <c r="P212" s="2" t="inlineStr"/>
-      <c r="Q212" s="2" t="inlineStr">
-        <is>
-          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R212" s="3" t="n">
-        <v>63464.09</v>
-      </c>
+      <c r="Q212" s="2" t="inlineStr"/>
+      <c r="R212" s="3" t="n"/>
       <c r="S212" s="3" t="n"/>
       <c r="T212" s="3" t="n"/>
       <c r="U212" s="3" t="n"/>
-      <c r="V212" s="2" t="inlineStr">
-        <is>
-          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
-        </is>
-      </c>
+      <c r="V212" s="2" t="inlineStr"/>
       <c r="W212" s="4" t="n"/>
       <c r="X212" s="4" t="n">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="Y212" s="4" t="n"/>
       <c r="Z212" s="4" t="n">
-        <v>46229</v>
+        <v>46286</v>
       </c>
       <c r="AA212" s="4" t="n">
-        <v>46273</v>
+        <v>46286</v>
       </c>
       <c r="AB212" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC212" s="2" t="inlineStr">
@@ -26979,27 +26965,31 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF212" s="2" t="inlineStr"/>
+      <c r="AF212" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG212" s="2" t="inlineStr"/>
       <c r="AH212" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局巴州税务局-通知公告-国家税务总局巴音郭楞蒙古自治州税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI212" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ212" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
@@ -27008,7 +26998,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>DOC-b97456a64b153f67</t>
+          <t>DOC-1228a9c92b2b0632</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -27045,12 +27035,12 @@
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M213" s="2" t="inlineStr">
         <is>
-          <t>常税稽一罚〔2026〕14号</t>
+          <t>常税稽一处〔2026〕35号</t>
         </is>
       </c>
       <c r="N213" s="2" t="inlineStr">
@@ -27069,11 +27059,11 @@
           <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R213" s="3" t="n"/>
+      <c r="R213" s="3" t="n">
+        <v>63464.09</v>
+      </c>
       <c r="S213" s="3" t="n"/>
-      <c r="T213" s="3" t="n">
-        <v>20000</v>
-      </c>
+      <c r="T213" s="3" t="n"/>
       <c r="U213" s="3" t="n"/>
       <c r="V213" s="2" t="inlineStr">
         <is>
@@ -27131,83 +27121,101 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>92</v>
+        <v>3</v>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>CASE-4ae87644334697ee</t>
+          <t>CASE-61b9b55a9d3357c7</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>DOC-bb4f7abf3229ef95</t>
+          <t>DOC-b97456a64b153f67</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>揭阳市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局揭阳市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局揭阳市税务局第一稽查局</t>
+          <t>国家税务总局常州市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>广东润升药械有限公司</t>
-        </is>
-      </c>
-      <c r="J214" s="2" t="inlineStr"/>
+          <t>常州市三鹏机械有限公司</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>91320404732260748Q</t>
+        </is>
+      </c>
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M214" s="2" t="inlineStr">
         <is>
-          <t>揭税一稽处〔2026〕3号</t>
+          <t>常税稽一罚〔2026〕14号</t>
         </is>
       </c>
       <c r="N214" s="2" t="inlineStr">
         <is>
-          <t>揭税一稽处〔2026〕3号</t>
-        </is>
-      </c>
-      <c r="O214" s="2" t="inlineStr"/>
+          <t>常税稽一处〔2026〕35号</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>常税稽一罚〔2026〕14号</t>
+        </is>
+      </c>
       <c r="P214" s="2" t="inlineStr"/>
-      <c r="Q214" s="2" t="inlineStr"/>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>增值税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
       <c r="R214" s="3" t="n"/>
       <c r="S214" s="3" t="n"/>
-      <c r="T214" s="3" t="n"/>
+      <c r="T214" s="3" t="n">
+        <v>20000</v>
+      </c>
       <c r="U214" s="3" t="n"/>
-      <c r="V214" s="2" t="inlineStr"/>
+      <c r="V214" s="2" t="inlineStr">
+        <is>
+          <t>根据《税务处理决定书》(常税稽一处〔2026〕35号)应追缴你单位增值税56664.36元、城市维护建设税3966.51元、教育费附加1699.93元、地方教育附加1133.29元; 根据《税务行政处罚决定书》(常税稽一罚〔2026〕14号)应对你单位处罚款20000元。</t>
+        </is>
+      </c>
       <c r="W214" s="4" t="n"/>
       <c r="X214" s="4" t="n">
-        <v>46048</v>
+        <v>46066</v>
       </c>
       <c r="Y214" s="4" t="n"/>
       <c r="Z214" s="4" t="n">
-        <v>46254</v>
+        <v>46229</v>
       </c>
       <c r="AA214" s="4" t="n">
-        <v>46307</v>
+        <v>46273</v>
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC214" s="2" t="inlineStr">
@@ -27229,7 +27237,7 @@
       <c r="AG214" s="2" t="inlineStr"/>
       <c r="AH214" s="2" t="inlineStr">
         <is>
-          <t>广东润升药械有限公司税务文书送达公告(揭税一稽公〔2026〕6号)</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局第一稽查局关于送达常州市三鹏机械有限公司《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI214" s="2" t="inlineStr">
@@ -27239,55 +27247,51 @@
       </c>
       <c r="AJ214" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“城市”存在冲突:保留原值“揭阳市”,新值“返回市”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>CASE-55a6de3243ad7d4c</t>
+          <t>CASE-4ae87644334697ee</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>DOC-364befd1052566a8</t>
+          <t>DOC-bb4f7abf3229ef95</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
+          <t>揭阳市</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr"/>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局嘉兴市税务局第一稽查局</t>
+          <t>国家税务总局揭阳市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局嘉兴市税务局第一稽查局</t>
+          <t>国家税务总局揭阳市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>浙江鑫牛食品有限公司</t>
-        </is>
-      </c>
-      <c r="J215" s="2" t="inlineStr">
-        <is>
-          <t>91330421062048093A</t>
-        </is>
-      </c>
+          <t>广东润升药械有限公司</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr"/>
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="2" t="inlineStr">
         <is>
@@ -27296,52 +27300,36 @@
       </c>
       <c r="M215" s="2" t="inlineStr">
         <is>
-          <t>嘉税一稽处〔2026〕10号</t>
+          <t>揭税一稽处〔2026〕3号</t>
         </is>
       </c>
       <c r="N215" s="2" t="inlineStr">
         <is>
-          <t>嘉税一稽处〔2026〕10号</t>
-        </is>
-      </c>
-      <c r="O215" s="2" t="inlineStr">
-        <is>
-          <t>嘉税一稽罚〔2026〕11号</t>
-        </is>
-      </c>
-      <c r="P215" s="2" t="inlineStr">
-        <is>
-          <t>我局于2025年6月23日至2025年9月9日对你单位(地址:浙江省嘉兴市嘉善县魏塘街道南星路65弄89号三楼302室)2024年1月1日至2024年12月31日纳税情况进行了检查,你单位存在违法事实及处罚决定如下: 经检查,查明你单位存在下述违法事实: 违法事实一:经查,2024年期间,你单位股东向你单位净借款合计8545846.41元,该笔借款在纳税年度终了后既未归还,又未用于企业生产经营。 违法事实二:你单位无偿借款给股东13296707.88元,但你单位未按金融服务视同销售申报利息收入,按照2024年贷款市场报价利率计算,利息收入金额应为41630.78元。 违法事实一:根据上述违法事实和证据,你单位少代扣代缴利息、股息、红利所得”个人所得税1709169.28元。 违法事实二:根据上述违法事实和证据,你单位少缴增值税2497.84元,少缴城市维护建设税62.45元。 根据《中华人民共和国税收征收管理法》第六十三条第一款,《财政部 国家税务总局关于全面推开营业税改征增值税试点的通知》附件1《营业税改征增值税试点实施办法》第十四条第一款、第四十四条的规定,个人投资者从其投资企业无偿借款,应视同公司无偿提供贷款服务,上述违法行为已构成偷税。 违法事实一:根据《中华人民共和国税收征收管理法》第六十九条规定,我局决定对你单位少代扣代缴个人所得税款1709169.28元处以两倍的罚款计3418338.56元。 违法事实二:根据《中华人民共和国税收征收管理法》第六十三条第一款规定,我局决定对你单位所偷税款2560.29元处以百分之五十的罚款计1280.15元。</t>
-        </is>
-      </c>
-      <c r="Q215" s="2" t="inlineStr">
-        <is>
-          <t>增值税、个人所得税、城市维护建设税</t>
-        </is>
-      </c>
+          <t>揭税一稽处〔2026〕3号</t>
+        </is>
+      </c>
+      <c r="O215" s="2" t="inlineStr"/>
+      <c r="P215" s="2" t="inlineStr"/>
+      <c r="Q215" s="2" t="inlineStr"/>
       <c r="R215" s="3" t="n"/>
       <c r="S215" s="3" t="n"/>
       <c r="T215" s="3" t="n"/>
       <c r="U215" s="3" t="n"/>
-      <c r="V215" s="2" t="inlineStr">
-        <is>
-          <t>到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
-        </is>
-      </c>
+      <c r="V215" s="2" t="inlineStr"/>
       <c r="W215" s="4" t="n"/>
       <c r="X215" s="4" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="Y215" s="4" t="n"/>
       <c r="Z215" s="4" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="AA215" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB215" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC215" s="2" t="inlineStr">
@@ -27359,31 +27347,27 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF215" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF215" s="2" t="inlineStr"/>
       <c r="AG215" s="2" t="inlineStr"/>
       <c r="AH215" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局嘉兴市税务局第一稽查局关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税信用修复告知书》的公告(嘉税一稽公告(2026)2号)</t>
+          <t>广东润升药械有限公司税务文书送达公告(揭税一稽公〔2026〕6号)</t>
         </is>
       </c>
       <c r="AI215" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ215" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“城市”存在冲突:保留原值“揭阳市”,新值“返回市”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
@@ -27392,7 +27376,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>DOC-316338f630372c72</t>
+          <t>DOC-364befd1052566a8</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -27429,12 +27413,12 @@
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M216" s="2" t="inlineStr">
         <is>
-          <t>嘉税一稽罚〔2026〕11号</t>
+          <t>嘉税一稽处〔2026〕10号</t>
         </is>
       </c>
       <c r="N216" s="2" t="inlineStr">
@@ -27459,27 +27443,23 @@
       </c>
       <c r="R216" s="3" t="n"/>
       <c r="S216" s="3" t="n"/>
-      <c r="T216" s="3" t="n">
-        <v>3418338.56</v>
-      </c>
+      <c r="T216" s="3" t="n"/>
       <c r="U216" s="3" t="n"/>
       <c r="V216" s="2" t="inlineStr">
         <is>
           <t>到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
         </is>
       </c>
-      <c r="W216" s="4" t="n">
-        <v>46035</v>
-      </c>
+      <c r="W216" s="4" t="n"/>
       <c r="X216" s="4" t="n">
         <v>46045</v>
       </c>
       <c r="Y216" s="4" t="n"/>
       <c r="Z216" s="4" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="AA216" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB216" s="2" t="inlineStr">
         <is>
@@ -27519,109 +27499,109 @@
       </c>
       <c r="AJ216" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“决定书作出日期”存在冲突:保留原值“2026-01-13”,新值“2025-09-09”未静默覆盖。 字段“附件链接”存在冲突:保留原值“https://zhejiang.chinatax.gov.cn/module/download/downfile.jsp?classid=0&amp;filename=b9fd478b49534c8fba0d421cfe4d06cd.docx”,新值“https://zhejiang.chinatax.gov.cn/module/download/downfile.jsp?classid=0&amp;filename=6871faa287fb4b60bcfb96e15e9d3576.docx”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>CASE-f78ec1a594442165</t>
+          <t>CASE-55a6de3243ad7d4c</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>DOC-fbbe4a664b14f54b</t>
+          <t>DOC-316338f630372c72</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>安顺市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局</t>
+          <t>国家税务总局嘉兴市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局</t>
+          <t>国家税务总局嘉兴市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+          <t>浙江鑫牛食品有限公司</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>91520423MA6DLH799Q</t>
+          <t>91330421062048093A</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M217" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>嘉税一稽罚〔2026〕11号</t>
         </is>
       </c>
       <c r="N217" s="2" t="inlineStr">
         <is>
-          <t>安市税稽处〔2026〕1号</t>
+          <t>嘉税一稽处〔2026〕10号</t>
         </is>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
-          <t>安市税稽罚〔2026〕1号</t>
+          <t>嘉税一稽罚〔2026〕11号</t>
         </is>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+          <t>我局于2025年6月23日至2025年9月9日对你单位(地址:浙江省嘉兴市嘉善县魏塘街道南星路65弄89号三楼302室)2024年1月1日至2024年12月31日纳税情况进行了检查,你单位存在违法事实及处罚决定如下: 经检查,查明你单位存在下述违法事实: 违法事实一:经查,2024年期间,你单位股东向你单位净借款合计8545846.41元,该笔借款在纳税年度终了后既未归还,又未用于企业生产经营。 违法事实二:你单位无偿借款给股东13296707.88元,但你单位未按金融服务视同销售申报利息收入,按照2024年贷款市场报价利率计算,利息收入金额应为41630.78元。 违法事实一:根据上述违法事实和证据,你单位少代扣代缴利息、股息、红利所得”个人所得税1709169.28元。 违法事实二:根据上述违法事实和证据,你单位少缴增值税2497.84元,少缴城市维护建设税62.45元。 根据《中华人民共和国税收征收管理法》第六十三条第一款,《财政部 国家税务总局关于全面推开营业税改征增值税试点的通知》附件1《营业税改征增值税试点实施办法》第十四条第一款、第四十四条的规定,个人投资者从其投资企业无偿借款,应视同公司无偿提供贷款服务,上述违法行为已构成偷税。 违法事实一:根据《中华人民共和国税收征收管理法》第六十九条规定,我局决定对你单位少代扣代缴个人所得税款1709169.28元处以两倍的罚款计3418338.56元。 违法事实二:根据《中华人民共和国税收征收管理法》第六十三条第一款规定,我局决定对你单位所偷税款2560.29元处以百分之五十的罚款计1280.15元。</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R217" s="3" t="n">
-        <v>64884.41</v>
-      </c>
+          <t>增值税、个人所得税、城市维护建设税</t>
+        </is>
+      </c>
+      <c r="R217" s="3" t="n"/>
       <c r="S217" s="3" t="n"/>
-      <c r="T217" s="3" t="n"/>
+      <c r="T217" s="3" t="n">
+        <v>3418338.56</v>
+      </c>
       <c r="U217" s="3" t="n"/>
       <c r="V217" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
+          <t>到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
         </is>
       </c>
       <c r="W217" s="4" t="n">
-        <v>45898</v>
+        <v>46035</v>
       </c>
       <c r="X217" s="4" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="Y217" s="4" t="n"/>
       <c r="Z217" s="4" t="n">
-        <v>46229</v>
+        <v>46254</v>
       </c>
       <c r="AA217" s="4" t="n">
-        <v>46263</v>
+        <v>46307</v>
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
@@ -27651,7 +27631,7 @@
       <c r="AG217" s="2" t="inlineStr"/>
       <c r="AH217" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局嘉兴市税务局第一稽查局关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税信用修复告知书》的公告(嘉税一稽公告(2026)2号)</t>
         </is>
       </c>
       <c r="AI217" s="2" t="inlineStr">
@@ -27661,13 +27641,13 @@
       </c>
       <c r="AJ217" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“处理或处罚结果”历史冲突已由官方附件复核,保留当前值。 字段“主要违法事实”已根据官方附件重新解析。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“决定书作出日期”存在冲突:保留原值“2026-01-13”,新值“2025-09-09”未静默覆盖。 字段“附件链接”存在冲突:保留原值“https://zhejiang.chinatax.gov.cn/module/download/downfile.jsp?classid=0&amp;filename=b9fd478b49534c8fba0d421cfe4d06cd.docx”,新值“https://zhejiang.chinatax.gov.cn/module/download/downfile.jsp?classid=0&amp;filename=6871faa287fb4b60bcfb96e15e9d3576.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
@@ -27676,7 +27656,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>DOC-9a828a6048b54b6c</t>
+          <t>DOC-fbbe4a664b14f54b</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -27713,27 +27693,27 @@
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M218" s="2" t="inlineStr">
         <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N218" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
           <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
-      <c r="N218" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽处〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="O218" s="2" t="inlineStr">
-        <is>
-          <t>安市税稽罚〔2026〕1号</t>
-        </is>
-      </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,违法事实及处理决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27741,15 +27721,15 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R218" s="3" t="n"/>
+      <c r="R218" s="3" t="n">
+        <v>64884.41</v>
+      </c>
       <c r="S218" s="3" t="n"/>
-      <c r="T218" s="3" t="n">
-        <v>200000</v>
-      </c>
+      <c r="T218" s="3" t="n"/>
       <c r="U218" s="3" t="n"/>
       <c r="V218" s="2" t="inlineStr">
         <is>
-          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; ”之规定,你单位应就少缴的增值税696,485.49元补缴教育费附加20,894.56元,应补缴地方教育附加13,929.71元。 ”之规定,你单位应补缴印花税312.70元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共计应补缴企业所得税64,884.41元。 ”、第五十二条“因税务机关的责任,致使纳税人、扣缴义务人未缴或者少缴税款的,税务机关在三年内可以要求纳税人、扣缴义务人补缴税款,但是不得加收滞纳金。 ”、《中华人民共和国税收征收管理法实施细则》(国务院令第362号)第七十五条“税收征管法第三十二条规定的加收滞纳金的起止时间,为法律、行政法规规定或者税务机关依照法律、行政法规的规定确定的税款缴纳期限届满次日起至纳税人、扣缴义务人实际缴纳或者解缴税款之日止”之规定,我局决定追缴你单位少缴的增值税696,485.49元、城市维护建设税50,019.66元、印花税312.70元、企业所得税64,884.41元。 逾期仍不补缴的,对单位处以1000元以上3万元以下罚款,对个人处以100元以上1000元以下的罚款”之规定,现责令你单位缴纳少缴的教育费附加30,011.79元、地方教育附加20,007.86元,并对少缴的教育费附加、地方教育附加从滞纳之日起至实际缴纳之日止,按日加收万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="W218" s="4" t="n">
@@ -27803,89 +27783,113 @@
       </c>
       <c r="AJ218" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”已根据官方附件重新解析。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“追缴税款金额”存在冲突:保留原值“64884.41”,新值“1521925.53”未静默覆盖。 字段“处理或处罚结果”历史冲突已由官方附件复核,保留当前值。 字段“主要违法事实”已根据官方附件重新解析。</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>CASE-0345194bffc3b105</t>
+          <t>CASE-f78ec1a594442165</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>DOC-849dbbf92d95f7da</t>
+          <t>DOC-9a828a6048b54b6c</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>连云港市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr"/>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局连云港市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局连云港市税务局第一稽查局</t>
+          <t>国家税务总局安顺市税务局稽查局</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>灌南时路能源有限公司</t>
-        </is>
-      </c>
-      <c r="J219" s="2" t="inlineStr"/>
+          <t>贵州华泰宁安工程建筑设计有限责任公司</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>91520423MA6DLH799Q</t>
+        </is>
+      </c>
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M219" s="2" t="inlineStr">
         <is>
-          <t>连税稽一处〔2026〕3号</t>
+          <t>安市税稽罚〔2026〕1号</t>
         </is>
       </c>
       <c r="N219" s="2" t="inlineStr">
         <is>
-          <t>连税稽一处〔2026〕3号</t>
-        </is>
-      </c>
-      <c r="O219" s="2" t="inlineStr"/>
-      <c r="P219" s="2" t="inlineStr"/>
-      <c r="Q219" s="2" t="inlineStr"/>
+          <t>安市税稽处〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>安市税稽罚〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="inlineStr">
+        <is>
+          <t>我局于2022年5月9日至2025年8月29日对你单位(地址:贵州省安顺市镇宁布依族苗族自治县城关镇城西村五组)2019年1月1日至2022年3月31日涉税情况进行了检查,你单位存在违法事实及处罚决定如下: 2022年6月,安顺市税务局稽查局将你单位上述虚开发票的线索移送给镇宁布依族苗族自治县公安局经济犯罪侦查大队,经公安机关对王*立案及检察院起诉后,2024年12月30日镇宁布依族苗族自治县人民法院作出王*犯虚开增值税发票罪的刑事判决,《刑事判决书》((2024)黔0423刑初198号)确认上述贵州宏翼翔汽车销售服务有限公司开具给你单位的6份增值税专用发票(金额460,177.02元,税额59,822.98元)、安顺润亨化工贸易有限公司开具给你单位的91份增值税专用发票(金额8,325,968.72元,税额1,047,999.48元)为虚开发票,判决王*犯虚开增值税专用发票罪,并处罚金人民币5万元。 经查,上述业务款项是贵州安顺家喻物业管理有限公司直接付款给罗*,罗*为了向贵州安顺家喻物业管理有限公司提供发票,通过支付手续费的方式找王*为其提供发票,王*指使贵州理得清财务有限公司员工彭*毕通过微信收取罗*手续费2,129.00元,后彭*毕又将该笔资金转到了贵州理得清财务有限公司微信账号。 根据《中华人民共和国发票管理办法》第二十一条第二款“任何单位和个人不得有下列虚开发票行为:(一)为他人、为自己开具与实际经营业务情况不符的发票; ”、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(国家税务总局公告2012年第33号)“......纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额。</t>
+        </is>
+      </c>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、房产税、城镇土地使用税、印花税、资源税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
       <c r="R219" s="3" t="n"/>
       <c r="S219" s="3" t="n"/>
-      <c r="T219" s="3" t="n"/>
+      <c r="T219" s="3" t="n">
+        <v>200000</v>
+      </c>
       <c r="U219" s="3" t="n"/>
-      <c r="V219" s="2" t="inlineStr"/>
-      <c r="W219" s="4" t="n"/>
+      <c r="V219" s="2" t="inlineStr">
+        <is>
+          <t>你单位应就少缴的增值税696,485.49元补缴城市维护建设税34,824.28元; 综上,应追缴你单位2020年至2022年少缴的城市维护建设税50,019.66元。 ”之规定,本次稽查你单位2020年应补缴的城市维护建设税20,172.19元、教育费附加12,103.32元、地方教育附加8,068.88元、印花税95.20元准予在企业所得税前扣除,应调减2020年企业所得税应纳税所得额40,439.59元; 2021年应补缴的城市维护建设税24,475.99元、教育费附加14,685.58元、地方教育附加9,790.39元、印花税217.50元准予在企业所得税前扣除,应调减2021年企业所得税应纳税所得额49,169.46元。 你单位2020年至2021年共应补缴企业所得税64,884.41元。 ”、《中华人民共和国发票管理办法》第三十五条第一款“违反本办法的规定虚开发票的,由税务机关没收违法所得; 对你单位取得安顺润亨化工贸易有限公司2021年12月虚开28份增值税专用发票以及2019年6月向贵州安顺家喻物业管理有限公司虚开1份增值税专用发票的行为,决定处以罚款200,000.00元。 综上,对你单位决定处以罚款200,000.00元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W219" s="4" t="n">
+        <v>45898</v>
+      </c>
       <c r="X219" s="4" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="Y219" s="4" t="n"/>
       <c r="Z219" s="4" t="n">
-        <v>46273</v>
+        <v>46229</v>
       </c>
       <c r="AA219" s="4" t="n">
-        <v>46273</v>
+        <v>46263</v>
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
@@ -27911,7 +27915,7 @@
       <c r="AG219" s="2" t="inlineStr"/>
       <c r="AH219" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局连云港市税务局第一稽查局税务处理决定书送达公告</t>
+          <t>国家税务总局安顺市税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI219" s="2" t="inlineStr">
@@ -27921,22 +27925,22 @@
       </c>
       <c r="AJ219" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“处理或处罚结果”已根据官方附件重新解析。</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>CASE-cbe0568f57d71cf7</t>
+          <t>CASE-0345194bffc3b105</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>DOC-a8b21140da417008</t>
+          <t>DOC-849dbbf92d95f7da</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -27946,30 +27950,26 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>徐州市</t>
+          <t>连云港市</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局连云港市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局徐州市税务局稽查局</t>
+          <t>国家税务总局连云港市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>徐州市乐居商贸有限公司</t>
-        </is>
-      </c>
-      <c r="J220" s="2" t="inlineStr">
-        <is>
-          <t>91320382576668185R</t>
-        </is>
-      </c>
+          <t>灌南时路能源有限公司</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr"/>
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="2" t="inlineStr">
         <is>
@@ -27978,56 +27978,36 @@
       </c>
       <c r="M220" s="2" t="inlineStr">
         <is>
-          <t>徐税稽处〔2025〕124号</t>
+          <t>连税稽一处〔2026〕3号</t>
         </is>
       </c>
       <c r="N220" s="2" t="inlineStr">
         <is>
-          <t>徐税稽处〔2025〕124号</t>
-        </is>
-      </c>
-      <c r="O220" s="2" t="inlineStr">
-        <is>
-          <t>徐税稽罚〔2025〕63号</t>
-        </is>
-      </c>
-      <c r="P220" s="2" t="inlineStr">
-        <is>
-          <t>我局于2024年9月26日至2025年9月12日对你单位(地址:邳州市东湖街道盛鑫商务中心楼1单元103铺)2020年1月1日至2023年12月31日涉税情况进行了检查,违法事实及处理决定如下: 你单位少缴的增值税税款应按规定申报缴纳城市维护建设税、教育费附加及地方教育附加。 1.根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条、第十九条、《财政部 税务总局关于支持个体工商户复工复业增值税政策的公告》(财政部 税务总局公告2020年第13号)、《财政部 税务总局关于延续实施应对疫情部分税费优惠政策的公告》(财政部 税务总局公告2021年第7号)第一条、《财政部 税务总局关于对增值税小规模纳税人免征增值税的公告》(财政部 税务总局公告2022年第15号)及《财政部 税务总局关于明确增值税小规模纳税人减免增值税等政策的公告》(财政部 税务总局公告2023年第1号)第二条之规定,追缴你单位少缴的2020年增值税683014.76元、2021年增值税406567.72元、2022年增值税115500.02元、2023年增值税339741.35元,合计追缴增值税1544823.85元。 2.根据《中华人民共和国城市维护建设税暂行条例》第二条、第三条、第四条、《中华人民共和国城市维护建设税法》第一条、第二条第一款、第四条第一款第(一)项、第五条、第七条、《财政部 税务总局关于实施小微企业普惠性税收减免政策的通知》(财税〔2019〕13号)第三条、第六条及《财政部 税务总局关于进一步实施小微企业“六税两费”减免政策的公告》(财政部 税务总局公告2022年第10号)第一条、第四条之规定,追缴你单位少缴的2020年城市维护建设税47811.04元、2021年城市维护建设税28459.74元、2022年城市维护建设税8085元、2023年城市维护建设税23781.89元,合计追缴城市维护建设税108137.67元。</t>
-        </is>
-      </c>
-      <c r="Q220" s="2" t="inlineStr">
-        <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R220" s="3" t="n">
-        <v>3089647.7</v>
-      </c>
+          <t>连税稽一处〔2026〕3号</t>
+        </is>
+      </c>
+      <c r="O220" s="2" t="inlineStr"/>
+      <c r="P220" s="2" t="inlineStr"/>
+      <c r="Q220" s="2" t="inlineStr"/>
+      <c r="R220" s="3" t="n"/>
       <c r="S220" s="3" t="n"/>
       <c r="T220" s="3" t="n"/>
       <c r="U220" s="3" t="n"/>
-      <c r="V220" s="2" t="inlineStr">
-        <is>
-          <t>你单位2020年少计收入48893898.07元(不含税),经审核计算,2020年1季度应补缴增值税330085.94元,2季度应补缴增值税121142.51元,3季度应补缴增值税127184.72元,4季度应补缴增值税104601.59元,合计2020年应补缴增值税683014.76元。 你单位2021年少计收入40656771.73元(不含税),经审核计算,2021年1季度应补缴增值税101037.42元,2季度应补缴增值税97557.50元,3季度应补缴增值税107173.48元,4季度应补缴增值税100799.32元,合计2021年应补缴增值税406567.72元。 你单位2022年少计收入11550002.29元(不含税),经审核计算,2022年1季度应补缴增值税115500.02元。 你单位2023年少计收入33974135.26元(不含税),经审核计算,2023年1季度应补缴增值税100992.64元,2季度应补缴增值税95313.11元,3季度应补缴增值税132243.55元,4季度应补缴增值税11192.05元,合计2023年应补缴增值税339741.35元。 以上合计应补缴增值税1544823.85元。 你单位应按季度计算补缴2020、2021、2022、2023年城市维护建设税分别为47811.04元、28459.74元、8085元、23781.89元,合计应补缴城市维护建设税108137.67元。 你单位应按季度计算补缴2020、2021、2022、2023年教育费附加分别为20490.45元、12197.03元、3465元、10192.24元,合计应补缴教育费附加46344.72元。</t>
-        </is>
-      </c>
-      <c r="W220" s="4" t="n">
-        <v>45912</v>
-      </c>
+      <c r="V220" s="2" t="inlineStr"/>
+      <c r="W220" s="4" t="n"/>
       <c r="X220" s="4" t="n">
-        <v>46035</v>
+        <v>46038</v>
       </c>
       <c r="Y220" s="4" t="n"/>
       <c r="Z220" s="4" t="n">
-        <v>46254</v>
+        <v>46273</v>
       </c>
       <c r="AA220" s="4" t="n">
-        <v>46263</v>
+        <v>46273</v>
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
@@ -28053,7 +28033,7 @@
       <c r="AG220" s="2" t="inlineStr"/>
       <c r="AH220" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局徐州市税务局稽查局关于送达徐州市乐居商贸有限公司税务处理决定书和税务行政处罚决定书的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局连云港市税务局第一稽查局税务处理决定书送达公告</t>
         </is>
       </c>
       <c r="AI220" s="2" t="inlineStr">
@@ -28063,13 +28043,13 @@
       </c>
       <c r="AJ220" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
@@ -28078,7 +28058,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>DOC-91cd2a54cfef9b64</t>
+          <t>DOC-a8b21140da417008</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -28115,47 +28095,47 @@
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M221" s="2" t="inlineStr">
         <is>
+          <t>徐税稽处〔2025〕124号</t>
+        </is>
+      </c>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t>徐税稽处〔2025〕124号</t>
+        </is>
+      </c>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
           <t>徐税稽罚〔2025〕63号</t>
         </is>
       </c>
-      <c r="N221" s="2" t="inlineStr">
-        <is>
-          <t>徐税稽处〔2025〕124号</t>
-        </is>
-      </c>
-      <c r="O221" s="2" t="inlineStr">
-        <is>
-          <t>徐税稽罚〔2025〕63号</t>
-        </is>
-      </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>我局于2024年09月26日至2025年11月12日对你单位(地址:邳州市东湖街道盛鑫商务中心楼1单元103铺)2020年01月01日至2023年12月31日涉税情况进行检查,你单位存在违法事实及处罚决定如下: 你单位少缴的增值税税款应按规定申报缴纳城市维护建设税。 根据《中华人民共和国税收征收管理法》第六十三条第一款、《国家税务总局关于发布&lt;税务行政处罚裁量权行使规则&gt;的公告》(国家税务总局公告2016年第78号)、《国家税务总局江苏省税务局关于发布&lt;江苏省税务行政处罚裁量权实施办法&gt;的公告》(国家税务总局江苏省税务局公告2018年第11号)第十六条及《国家税务总局上海市税务局江苏省税务局浙江省税务局安徽省税务局宁波市税务局关于发布&lt;长江三角洲区域登记账证征收检查类税务违法行为行政处罚裁量基准&gt;的公告》(国家税务总局上海市税务局江苏省税务局浙江省税务局安徽省税务局宁波市税务局公告2022年第5号)之规定,决定对你单位2020-2023年少缴的增值税1544823.85元处少缴税款50%的罚款合计772411.95元,少缴的城市维护建设税108137.67元处少缴税款50%的罚款合计54068.86元,少缴的企业所得税369658.84元处少缴税款50%的罚款合计184829.44元。</t>
+          <t>我局于2024年9月26日至2025年9月12日对你单位(地址:邳州市东湖街道盛鑫商务中心楼1单元103铺)2020年1月1日至2023年12月31日涉税情况进行了检查,违法事实及处理决定如下: 你单位少缴的增值税税款应按规定申报缴纳城市维护建设税、教育费附加及地方教育附加。 1.根据《中华人民共和国增值税暂行条例》第一条、第十一条、第十二条、第十九条、《财政部 税务总局关于支持个体工商户复工复业增值税政策的公告》(财政部 税务总局公告2020年第13号)、《财政部 税务总局关于延续实施应对疫情部分税费优惠政策的公告》(财政部 税务总局公告2021年第7号)第一条、《财政部 税务总局关于对增值税小规模纳税人免征增值税的公告》(财政部 税务总局公告2022年第15号)及《财政部 税务总局关于明确增值税小规模纳税人减免增值税等政策的公告》(财政部 税务总局公告2023年第1号)第二条之规定,追缴你单位少缴的2020年增值税683014.76元、2021年增值税406567.72元、2022年增值税115500.02元、2023年增值税339741.35元,合计追缴增值税1544823.85元。 2.根据《中华人民共和国城市维护建设税暂行条例》第二条、第三条、第四条、《中华人民共和国城市维护建设税法》第一条、第二条第一款、第四条第一款第(一)项、第五条、第七条、《财政部 税务总局关于实施小微企业普惠性税收减免政策的通知》(财税〔2019〕13号)第三条、第六条及《财政部 税务总局关于进一步实施小微企业“六税两费”减免政策的公告》(财政部 税务总局公告2022年第10号)第一条、第四条之规定,追缴你单位少缴的2020年城市维护建设税47811.04元、2021年城市维护建设税28459.74元、2022年城市维护建设税8085元、2023年城市维护建设税23781.89元,合计追缴城市维护建设税108137.67元。</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、城市维护建设税</t>
-        </is>
-      </c>
-      <c r="R221" s="3" t="n"/>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R221" s="3" t="n">
+        <v>3089647.7</v>
+      </c>
       <c r="S221" s="3" t="n"/>
-      <c r="T221" s="3" t="n">
-        <v>772411.95</v>
-      </c>
+      <c r="T221" s="3" t="n"/>
       <c r="U221" s="3" t="n"/>
       <c r="V221" s="2" t="inlineStr">
         <is>
-          <t>你单位2020年少计收入48893898.07元(不含税),经审核计算,2020年1季度应补缴增值税330085.94元,2季度应补缴增值税121142.51元,3季度应补缴增值税127184.72元,4季度应补缴增值税104601.59元,合计2020年应补缴增值税683014.76元。 你单位2021年少计收入40656771.73元(不含税),经审核计算,2021年1季度应补缴增值税101037.42元,2季度应补缴增值税97557.50元,3季度应补缴增值税107173.48元,4季度应补缴增值税100799.32元,合计2021年应补缴增值税406567.72元。 你单位2022年少计收入11550002.29元(不含税),经审核计算,2022年1季度应补缴增值税115500.02元。 你单位2023年少计收入33974135.26元(不含税),经审核计算,2023年1季度应补缴增值税100992.64元,2季度应补缴增值税95313.11元,3季度应补缴增值税132243.55元,4季度应补缴增值税11192.05元,合计2023年应补缴增值税339741.35元。 以上合计应补缴增值税1544823.85元。 你单位应按季度计算补缴2020、2021、2022、2023年城市维护建设税分别为47811.04元、28459.74元、8085元、23781.89元,合计应补缴城市维护建设税108137.67元。 2020年应税收入额48893898.07元,核定2020年度应纳税所得额为1955755.92元,应补缴企业所得税145575.59元; 2021年应税收入额40656771.73元,核定2021年度应纳税所得额为1626270.87元,应补缴企业所得税87627.09元;</t>
+          <t>你单位2020年少计收入48893898.07元(不含税),经审核计算,2020年1季度应补缴增值税330085.94元,2季度应补缴增值税121142.51元,3季度应补缴增值税127184.72元,4季度应补缴增值税104601.59元,合计2020年应补缴增值税683014.76元。 你单位2021年少计收入40656771.73元(不含税),经审核计算,2021年1季度应补缴增值税101037.42元,2季度应补缴增值税97557.50元,3季度应补缴增值税107173.48元,4季度应补缴增值税100799.32元,合计2021年应补缴增值税406567.72元。 你单位2022年少计收入11550002.29元(不含税),经审核计算,2022年1季度应补缴增值税115500.02元。 你单位2023年少计收入33974135.26元(不含税),经审核计算,2023年1季度应补缴增值税100992.64元,2季度应补缴增值税95313.11元,3季度应补缴增值税132243.55元,4季度应补缴增值税11192.05元,合计2023年应补缴增值税339741.35元。 以上合计应补缴增值税1544823.85元。 你单位应按季度计算补缴2020、2021、2022、2023年城市维护建设税分别为47811.04元、28459.74元、8085元、23781.89元,合计应补缴城市维护建设税108137.67元。 你单位应按季度计算补缴2020、2021、2022、2023年教育费附加分别为20490.45元、12197.03元、3465元、10192.24元,合计应补缴教育费附加46344.72元。</t>
         </is>
       </c>
       <c r="W221" s="4" t="n">
-        <v>45973</v>
+        <v>45912</v>
       </c>
       <c r="X221" s="4" t="n">
         <v>46035</v>
@@ -28211,95 +28191,107 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>CASE-bef08dfa2f488cf9</t>
+          <t>CASE-cbe0568f57d71cf7</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>DOC-700a551817c8c5fa</t>
+          <t>DOC-91cd2a54cfef9b64</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>巴音郭楞蒙古自治州</t>
+          <t>徐州市</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
+          <t>国家税务总局徐州市税务局稽查局</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>若羌县宏源加油站有限公司</t>
+          <t>徐州市乐居商贸有限公司</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>91652824080224388F</t>
-        </is>
-      </c>
-      <c r="K222" s="2" t="inlineStr">
-        <is>
-          <t>朱某庭</t>
-        </is>
-      </c>
+          <t>91320382576668185R</t>
+        </is>
+      </c>
+      <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M222" s="2" t="inlineStr">
         <is>
-          <t>巴税稽处〔2025〕97号</t>
+          <t>徐税稽罚〔2025〕63号</t>
         </is>
       </c>
       <c r="N222" s="2" t="inlineStr">
         <is>
-          <t>巴税稽处〔2025〕97号</t>
+          <t>徐税稽处〔2025〕124号</t>
         </is>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
-          <t>巴税稽罚〔2025〕97号</t>
-        </is>
-      </c>
-      <c r="P222" s="2" t="inlineStr"/>
-      <c r="Q222" s="2" t="inlineStr"/>
+          <t>徐税稽罚〔2025〕63号</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t>我局于2024年09月26日至2025年11月12日对你单位(地址:邳州市东湖街道盛鑫商务中心楼1单元103铺)2020年01月01日至2023年12月31日涉税情况进行检查,你单位存在违法事实及处罚决定如下: 你单位少缴的增值税税款应按规定申报缴纳城市维护建设税。 根据《中华人民共和国税收征收管理法》第六十三条第一款、《国家税务总局关于发布&lt;税务行政处罚裁量权行使规则&gt;的公告》(国家税务总局公告2016年第78号)、《国家税务总局江苏省税务局关于发布&lt;江苏省税务行政处罚裁量权实施办法&gt;的公告》(国家税务总局江苏省税务局公告2018年第11号)第十六条及《国家税务总局上海市税务局江苏省税务局浙江省税务局安徽省税务局宁波市税务局关于发布&lt;长江三角洲区域登记账证征收检查类税务违法行为行政处罚裁量基准&gt;的公告》(国家税务总局上海市税务局江苏省税务局浙江省税务局安徽省税务局宁波市税务局公告2022年第5号)之规定,决定对你单位2020-2023年少缴的增值税1544823.85元处少缴税款50%的罚款合计772411.95元,少缴的城市维护建设税108137.67元处少缴税款50%的罚款合计54068.86元,少缴的企业所得税369658.84元处少缴税款50%的罚款合计184829.44元。</t>
+        </is>
+      </c>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、城市维护建设税</t>
+        </is>
+      </c>
       <c r="R222" s="3" t="n"/>
       <c r="S222" s="3" t="n"/>
-      <c r="T222" s="3" t="n"/>
+      <c r="T222" s="3" t="n">
+        <v>772411.95</v>
+      </c>
       <c r="U222" s="3" t="n"/>
-      <c r="V222" s="2" t="inlineStr"/>
-      <c r="W222" s="4" t="n"/>
+      <c r="V222" s="2" t="inlineStr">
+        <is>
+          <t>你单位2020年少计收入48893898.07元(不含税),经审核计算,2020年1季度应补缴增值税330085.94元,2季度应补缴增值税121142.51元,3季度应补缴增值税127184.72元,4季度应补缴增值税104601.59元,合计2020年应补缴增值税683014.76元。 你单位2021年少计收入40656771.73元(不含税),经审核计算,2021年1季度应补缴增值税101037.42元,2季度应补缴增值税97557.50元,3季度应补缴增值税107173.48元,4季度应补缴增值税100799.32元,合计2021年应补缴增值税406567.72元。 你单位2022年少计收入11550002.29元(不含税),经审核计算,2022年1季度应补缴增值税115500.02元。 你单位2023年少计收入33974135.26元(不含税),经审核计算,2023年1季度应补缴增值税100992.64元,2季度应补缴增值税95313.11元,3季度应补缴增值税132243.55元,4季度应补缴增值税11192.05元,合计2023年应补缴增值税339741.35元。 以上合计应补缴增值税1544823.85元。 你单位应按季度计算补缴2020、2021、2022、2023年城市维护建设税分别为47811.04元、28459.74元、8085元、23781.89元,合计应补缴城市维护建设税108137.67元。 2020年应税收入额48893898.07元,核定2020年度应纳税所得额为1955755.92元,应补缴企业所得税145575.59元; 2021年应税收入额40656771.73元,核定2021年度应纳税所得额为1626270.87元,应补缴企业所得税87627.09元;</t>
+        </is>
+      </c>
+      <c r="W222" s="4" t="n">
+        <v>45973</v>
+      </c>
       <c r="X222" s="4" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="Y222" s="4" t="n"/>
       <c r="Z222" s="4" t="n">
-        <v>46286</v>
+        <v>46254</v>
       </c>
       <c r="AA222" s="4" t="n">
-        <v>46286</v>
+        <v>46263</v>
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>仅公告送达/仅文号线索</t>
+          <t>完整文书</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
@@ -28325,7 +28317,7 @@
       <c r="AG222" s="2" t="inlineStr"/>
       <c r="AH222" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局巴州税务局-通知公告-国家税务总局巴音郭楞蒙古自治州税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局徐州市税务局稽查局关于送达徐州市乐居商贸有限公司税务处理决定书和税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI222" s="2" t="inlineStr">
@@ -28335,13 +28327,13 @@
       </c>
       <c r="AJ222" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
@@ -28350,7 +28342,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>DOC-65bfc2d5b7ed46f9</t>
+          <t>DOC-700a551817c8c5fa</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -28391,12 +28383,12 @@
       </c>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M223" s="2" t="inlineStr">
         <is>
-          <t>巴税稽罚〔2025〕97号</t>
+          <t>巴税稽处〔2025〕97号</t>
         </is>
       </c>
       <c r="N223" s="2" t="inlineStr">
@@ -28471,76 +28463,76 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>CASE-fe959d4c6c52d910</t>
+          <t>CASE-bef08dfa2f488cf9</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>DOC-f2643f2a0719d8d1</t>
+          <t>DOC-65bfc2d5b7ed46f9</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>巴音郭楞蒙古自治州</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局</t>
+          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>南宁洪谦金贸易有限公司</t>
+          <t>若羌县宏源加油站有限公司</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>91450103MA5K9WHY7U</t>
-        </is>
-      </c>
-      <c r="K224" s="2" t="inlineStr"/>
+          <t>91652824080224388F</t>
+        </is>
+      </c>
+      <c r="K224" s="2" t="inlineStr">
+        <is>
+          <t>朱某庭</t>
+        </is>
+      </c>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M224" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
+          <t>巴税稽罚〔2025〕97号</t>
         </is>
       </c>
       <c r="N224" s="2" t="inlineStr">
         <is>
-          <t>南市税一稽处〔2026〕2号</t>
-        </is>
-      </c>
-      <c r="O224" s="2" t="inlineStr"/>
-      <c r="P224" s="2" t="inlineStr">
-        <is>
-          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
-        </is>
-      </c>
-      <c r="Q224" s="2" t="inlineStr">
-        <is>
-          <t>增值税</t>
-        </is>
-      </c>
+          <t>巴税稽处〔2025〕97号</t>
+        </is>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>巴税稽罚〔2025〕97号</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr"/>
+      <c r="Q224" s="2" t="inlineStr"/>
       <c r="R224" s="3" t="n"/>
       <c r="S224" s="3" t="n"/>
       <c r="T224" s="3" t="n"/>
@@ -28548,18 +28540,18 @@
       <c r="V224" s="2" t="inlineStr"/>
       <c r="W224" s="4" t="n"/>
       <c r="X224" s="4" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="Y224" s="4" t="n"/>
       <c r="Z224" s="4" t="n">
-        <v>46229</v>
+        <v>46286</v>
       </c>
       <c r="AA224" s="4" t="n">
-        <v>46263</v>
+        <v>46286</v>
       </c>
       <c r="AB224" s="2" t="inlineStr">
         <is>
-          <t>完整文书</t>
+          <t>仅公告送达/仅文号线索</t>
         </is>
       </c>
       <c r="AC224" s="2" t="inlineStr">
@@ -28585,7 +28577,7 @@
       <c r="AG224" s="2" t="inlineStr"/>
       <c r="AH224" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
+          <t>国家税务总局巴州税务局-通知公告-国家税务总局巴音郭楞蒙古自治州税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI224" s="2" t="inlineStr">
@@ -28595,51 +28587,55 @@
       </c>
       <c r="AJ224" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>CASE-55b061008af48dba</t>
+          <t>CASE-fe959d4c6c52d910</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>DOC-e2ddf1bdd7c9d7dd</t>
+          <t>DOC-f2643f2a0719d8d1</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局无锡市税务局稽查局</t>
+          <t>国家税务总局南宁市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>无锡宝双贸易有限公司</t>
-        </is>
-      </c>
-      <c r="J225" s="2" t="inlineStr"/>
+          <t>南宁洪谦金贸易有限公司</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>91450103MA5K9WHY7U</t>
+        </is>
+      </c>
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="2" t="inlineStr">
         <is>
@@ -28648,23 +28644,23 @@
       </c>
       <c r="M225" s="2" t="inlineStr">
         <is>
-          <t>锡税稽处〔2025〕173号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="N225" s="2" t="inlineStr">
         <is>
-          <t>锡税稽处〔2025〕173号</t>
+          <t>南市税一稽处〔2026〕2号</t>
         </is>
       </c>
       <c r="O225" s="2" t="inlineStr"/>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>你单位取得上海岳齐钢材贸易有限公司开具的11份增值税专用发票为虚开发票,追缴相应的增值税、企业所得税、城市维护建设税、教育费附加和地方教育附加,加收对应滞纳金。</t>
+          <t>经我局2025年10月29日至2025年12月8日对你公司(地址:南宁市青秀区云景路11号春晖花园C区3栋2单元1606号)2015年12月2日至2016年12月31日期间的涉税情况进行了检查,你(单位)存在以下违法事实: 经查询你公司向税务机关报备的银行账号:广西北部湾银行南宁市财富国际支行800099398800015,经函询广西北部湾银行南宁市财富国际支行,存在以下问题: 上述行为属于开具与实际经营业务情况不符的增值税发票,违反了《中华人民共和国发票管理办法》(财政部令第6号发布,国务院令第587号修改)第二十二条第一款、第二款第(一)项的规定,属于虚开发票行为。</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
+          <t>增值税</t>
         </is>
       </c>
       <c r="R225" s="3" t="n"/>
@@ -28674,14 +28670,14 @@
       <c r="V225" s="2" t="inlineStr"/>
       <c r="W225" s="4" t="n"/>
       <c r="X225" s="4" t="n">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="Y225" s="4" t="n"/>
       <c r="Z225" s="4" t="n">
-        <v>46258</v>
+        <v>46229</v>
       </c>
       <c r="AA225" s="4" t="n">
-        <v>46307</v>
+        <v>46263</v>
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
@@ -28703,62 +28699,66 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF225" s="2" t="inlineStr"/>
+      <c r="AF225" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG225" s="2" t="inlineStr"/>
       <c r="AH225" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局无锡市税务局稽查局关于送达税务处理决定书的公告(无锡宝双贸易有限公司)</t>
+          <t>国家税务总局南宁市税务局第一稽查局税务文书送达公告_国家税务总局南宁市税务局</t>
         </is>
       </c>
       <c r="AI225" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ225" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“发布机关”存在冲突:保留原值“国家税务总局江苏省税务局”,新值“国家税务总局无锡市税务局稽查局”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>CASE-1983d97878508732</t>
+          <t>CASE-55b061008af48dba</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>DOC-f9760895b4f08cc2</t>
+          <t>DOC-e2ddf1bdd7c9d7dd</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>二连浩特市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局二连浩特市税务局稽查局</t>
+          <t>国家税务总局无锡市税务局稽查局</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>二连市坤益腾金属有限公司</t>
+          <t>无锡宝双贸易有限公司</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr"/>
@@ -28770,42 +28770,40 @@
       </c>
       <c r="M226" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>锡税稽处〔2025〕173号</t>
         </is>
       </c>
       <c r="N226" s="2" t="inlineStr">
         <is>
-          <t>二税稽处〔2025〕1号</t>
+          <t>锡税稽处〔2025〕173号</t>
         </is>
       </c>
       <c r="O226" s="2" t="inlineStr"/>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
+          <t>你单位取得上海岳齐钢材贸易有限公司开具的11份增值税专用发票为虚开发票,追缴相应的增值税、企业所得税、城市维护建设税、教育费附加和地方教育附加,加收对应滞纳金。</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
       <c r="R226" s="3" t="n"/>
       <c r="S226" s="3" t="n"/>
       <c r="T226" s="3" t="n"/>
       <c r="U226" s="3" t="n"/>
-      <c r="V226" s="2" t="inlineStr">
-        <is>
-          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
-        </is>
-      </c>
+      <c r="V226" s="2" t="inlineStr"/>
       <c r="W226" s="4" t="n"/>
-      <c r="X226" s="4" t="n"/>
+      <c r="X226" s="4" t="n">
+        <v>46027</v>
+      </c>
       <c r="Y226" s="4" t="n"/>
       <c r="Z226" s="4" t="n">
-        <v>46229</v>
+        <v>46258</v>
       </c>
       <c r="AA226" s="4" t="n">
-        <v>46263</v>
+        <v>46307</v>
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
@@ -28819,7 +28817,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE226" s="5" t="inlineStr">
@@ -28831,7 +28829,7 @@
       <c r="AG226" s="2" t="inlineStr"/>
       <c r="AH226" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局无锡市税务局稽查局关于送达税务处理决定书的公告(无锡宝双贸易有限公司)</t>
         </is>
       </c>
       <c r="AI226" s="2" t="inlineStr">
@@ -28841,22 +28839,22 @@
       </c>
       <c r="AJ226" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“页面标题”存在冲突:保留原值“税务处理决定书”,新值“Á®éŚä°Ś§ĄÁźÜŚÜ≥ŚģöšĻ¶”未静默覆盖。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“发布机关”存在冲突:保留原值“国家税务总局江苏省税务局”,新值“国家税务总局无锡市税务局稽查局”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>CASE-d4b6986f3f97cd28</t>
+          <t>CASE-1983d97878508732</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>DOC-442cf3d9a5280c12</t>
+          <t>DOC-f9760895b4f08cc2</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -28866,19 +28864,23 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>二连浩特市</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr"/>
-      <c r="G227" s="2" t="inlineStr"/>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局二连浩特市税务局</t>
+        </is>
+      </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>第二稽查局</t>
+          <t>国家税务总局二连浩特市税务局稽查局</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>廖礼平</t>
+          <t>二连市坤益腾金属有限公司</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr"/>
@@ -28890,36 +28892,32 @@
       </c>
       <c r="M227" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="N227" s="2" t="inlineStr">
         <is>
-          <t>鄂税二稽处〔2023〕29号</t>
+          <t>二税稽处〔2025〕1号</t>
         </is>
       </c>
       <c r="O227" s="2" t="inlineStr"/>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
+          <t>公司院内)涉嫌虚开增值税专用发票的情况进行检查,违法事实 你公司在无真实货物交易的情况下,“让他人为自己”虚开 得有下列虚开发票行为:(一)为他人、为自己开具与实际经营 国人民代表大会常务委员会关于惩治虚开、伪造和非法出售增值 〔1996〕210号)文件:“虚开增值税专用发票的,构成虚开增 值税专用发票罪,具有下列行为之一的,属于虚开增值税专用发 定,你公司上述违法事实中,“让他人为自己”虚开增值税专用 “为他人”虚开增值税专用发票97 份,金额 87,923,181.86 元, 二条第二款的规定虚开发票的,由税务机关没收违法所得; 虚开增值税专用发票行为暂不进行行政处罚,在司法部门作出决 十二条第二款的规定虚开发票的,由税务机关没收违法所得; 依法查处违法行为过程中,发现违法事实涉及的金额、违法事实 的情节、违法事实造成的后果等,根据刑法关于破坏社会主义市 定(二)》(公通字〔2022〕12 号)第五十六条:“〔虚开增值 税专用发票、用于骗取出口退税、抵扣税款发票案(刑法第二百 零五条)〕虚开增值税专用发票或者虚开用于骗取出口退税、抵 扣税款的其他发票,虚开的税款数额在十万元以上或者致使国家 公司虚开增值税专用发票的行为移送公安机关。</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
         <is>
-          <t>个人所得税、印花税</t>
-        </is>
-      </c>
-      <c r="R227" s="3" t="n">
-        <v>15072487.5</v>
-      </c>
-      <c r="S227" s="3" t="n">
-        <v>1046925</v>
-      </c>
+          <t>增值税</t>
+        </is>
+      </c>
+      <c r="R227" s="3" t="n"/>
+      <c r="S227" s="3" t="n"/>
       <c r="T227" s="3" t="n"/>
       <c r="U227" s="3" t="n"/>
       <c r="V227" s="2" t="inlineStr">
         <is>
-          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
+          <t>二条第二款的规定虚开发票的,由税务机关没收违法所得; 十二条第二款的规定虚开发票的,由税务机关没收违法所得;</t>
         </is>
       </c>
       <c r="W227" s="4" t="n"/>
@@ -28965,55 +28963,47 @@
       </c>
       <c r="AJ227" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“页面标题”存在冲突:保留原值“税务处理决定书”,新值“Á®éŚä°Ś§ĄÁźÜŚÜ≥ŚģöšĻ¶”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/elht/xjtzgghhht/202501/W020250110616020148238.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/elht/tzgghhht/202501/W020250110616020148238.pdf”未静默覆盖。 字段“页面标题”存在冲突:保留原值“税务处理决定书”,新值“Á®éŚä°Ś§ĄÁźÜŚÜ≥ŚģöšĻ¶”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>CASE-3996d04fd944424e</t>
+          <t>CASE-d4b6986f3f97cd28</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>DOC-af179599b7f27421</t>
+          <t>DOC-442cf3d9a5280c12</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr"/>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
-        </is>
-      </c>
+      <c r="G228" s="2" t="inlineStr"/>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局</t>
+          <t>第二稽查局</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>信硕(天津)国际货运代理有限公司</t>
-        </is>
-      </c>
-      <c r="J228" s="2" t="inlineStr">
-        <is>
-          <t>91120105MA06WEYU7C</t>
-        </is>
-      </c>
+          <t>廖礼平</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr"/>
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="2" t="inlineStr">
         <is>
@@ -29022,35 +29012,43 @@
       </c>
       <c r="M228" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2022〕270号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="N228" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2022〕270号</t>
+          <t>鄂税二稽处〔2023〕29号</t>
         </is>
       </c>
       <c r="O228" s="2" t="inlineStr"/>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2022年6月24日至2022年8月18日对你(单位)(地址:天津市河北区建昌道街道铁工东里增57-1号)2019年12月2日至2022年5月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位无生产经营地点,虚假注册,无社保信息,与上下游企业无银行交易记录,收取上游企业虚开的增值税发票后脱离税务机关监管,经核实,你单位不符合正常企业构成要件,认定为假企业。 你单位在2019年12月02日-2022年5月31日期间,未发生真实货物、劳务交易,对下游13户企业开具增值税普通发票990份,发票代码012001900105,发票号码04884187-04884216,04893407-04893421,04898548,06548576-06548620,06671887-06671896,06807185-06807194,06909763-06909797,07353556-07353600,07359910-07359954,07369273-07369317,07374190-07374214,07379166-07379235,09307219-09307288,09319483-09319552,09327879-09327948,11915880-11915949,11925651-11925720,11937167-11937236,11941265-11941334,11945987-11946000,11948001-11948056,发票代码012001900104,发票号码24048210-24048219,虚开增值税普通发票不含税金额73000214.83元,税额0元,价税合计73000214.83元。</t>
+          <t>利煤炭有限责任公司股权涉税问题开展了检查,违法事实及处理</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
         <is>
-          <t>增值税、消费税</t>
-        </is>
-      </c>
-      <c r="R228" s="3" t="n"/>
-      <c r="S228" s="3" t="n"/>
+          <t>个人所得税、印花税</t>
+        </is>
+      </c>
+      <c r="R228" s="3" t="n">
+        <v>15072487.5</v>
+      </c>
+      <c r="S228" s="3" t="n">
+        <v>1046925</v>
+      </c>
       <c r="T228" s="3" t="n"/>
       <c r="U228" s="3" t="n"/>
-      <c r="V228" s="2" t="inlineStr"/>
+      <c r="V228" s="2" t="inlineStr">
+        <is>
+          <t>以上共计应补缴个人所得税14,997,500.00元。 以上共计应补缴印花税74,987.50元。 规定,对应补缴个人所得税14,997,500.00元加收从2011年4月1</t>
+        </is>
+      </c>
       <c r="W228" s="4" t="n"/>
       <c r="X228" s="4" t="n"/>
       <c r="Y228" s="4" t="n"/>
       <c r="Z228" s="4" t="n">
-        <v>46248</v>
+        <v>46229</v>
       </c>
       <c r="AA228" s="4" t="n">
         <v>46263</v>
@@ -29079,7 +29077,7 @@
       <c r="AG228" s="2" t="inlineStr"/>
       <c r="AH228" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达信硕(天津)国际货运代理有限公司《税务处理决定书》的公告</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="AI228" s="2" t="inlineStr">
@@ -29089,22 +29087,22 @@
       </c>
       <c r="AJ228" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“涉及税种”存在冲突:保留原值“增值税、消费税”,新值“增值税”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“http://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202311/P020231101635149652485.pdf”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202311/P020231101635149652485.pdf”未静默覆盖。 字段“页面标题”存在冲突:保留原值“税务处理决定书”,新值“Á®éŚä°Ś§ĄÁźÜŚÜ≥ŚģöšĻ¶”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>CASE-7e3d4a321440d6a7</t>
+          <t>CASE-3996d04fd944424e</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>DOC-bed9330343ed06af</t>
+          <t>DOC-af179599b7f27421</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -29130,12 +29128,12 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>天津展达科技有限公司</t>
+          <t>信硕(天津)国际货运代理有限公司</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>91120116300738701X</t>
+          <t>91120105MA06WEYU7C</t>
         </is>
       </c>
       <c r="K229" s="2" t="inlineStr"/>
@@ -29146,45 +29144,35 @@
       </c>
       <c r="M229" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
+          <t>津税一稽处〔2022〕270号</t>
         </is>
       </c>
       <c r="N229" s="2" t="inlineStr">
         <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O229" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
+          <t>津税一稽处〔2022〕270号</t>
+        </is>
+      </c>
+      <c r="O229" s="2" t="inlineStr"/>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+          <t>我局(所)于2022年6月24日至2022年8月18日对你(单位)(地址:天津市河北区建昌道街道铁工东里增57-1号)2019年12月2日至2022年5月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位无生产经营地点,虚假注册,无社保信息,与上下游企业无银行交易记录,收取上游企业虚开的增值税发票后脱离税务机关监管,经核实,你单位不符合正常企业构成要件,认定为假企业。 你单位在2019年12月02日-2022年5月31日期间,未发生真实货物、劳务交易,对下游13户企业开具增值税普通发票990份,发票代码012001900105,发票号码04884187-04884216,04893407-04893421,04898548,06548576-06548620,06671887-06671896,06807185-06807194,06909763-06909797,07353556-07353600,07359910-07359954,07369273-07369317,07374190-07374214,07379166-07379235,09307219-09307288,09319483-09319552,09327879-09327948,11915880-11915949,11925651-11925720,11937167-11937236,11941265-11941334,11945987-11946000,11948001-11948056,发票代码012001900104,发票号码24048210-24048219,虚开增值税普通发票不含税金额73000214.83元,税额0元,价税合计73000214.83元。</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
         <is>
-          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
-        </is>
-      </c>
-      <c r="R229" s="3" t="n">
-        <v>920146.9399999999</v>
-      </c>
+          <t>增值税、消费税</t>
+        </is>
+      </c>
+      <c r="R229" s="3" t="n"/>
       <c r="S229" s="3" t="n"/>
       <c r="T229" s="3" t="n"/>
       <c r="U229" s="3" t="n"/>
-      <c r="V229" s="2" t="inlineStr">
-        <is>
-          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
-        </is>
-      </c>
+      <c r="V229" s="2" t="inlineStr"/>
       <c r="W229" s="4" t="n"/>
       <c r="X229" s="4" t="n"/>
       <c r="Y229" s="4" t="n"/>
       <c r="Z229" s="4" t="n">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="AA229" s="4" t="n">
         <v>46263</v>
@@ -29213,7 +29201,7 @@
       <c r="AG229" s="2" t="inlineStr"/>
       <c r="AH229" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局天津市税务局第一稽查局关于送达信硕(天津)国际货运代理有限公司《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI229" s="2" t="inlineStr">
@@ -29223,13 +29211,13 @@
       </c>
       <c r="AJ229" s="2" t="inlineStr">
         <is>
-          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“涉及税种”存在冲突:保留原值“增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加”,新值“增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加”未静默覆盖。</t>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“涉及税种”存在冲突:保留原值“增值税、消费税”,新值“增值税”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
@@ -29238,7 +29226,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>DOC-388bd01c01bbb789</t>
+          <t>DOC-bed9330343ed06af</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -29275,24 +29263,24 @@
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M230" s="2" t="inlineStr">
         <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="N230" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
           <t>津税一稽罚〔2023〕21号</t>
         </is>
       </c>
-      <c r="N230" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽处〔2023〕59号</t>
-        </is>
-      </c>
-      <c r="O230" s="2" t="inlineStr">
-        <is>
-          <t>津税一稽罚〔2023〕21号</t>
-        </is>
-      </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
           <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
@@ -29303,11 +29291,11 @@
           <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
         </is>
       </c>
-      <c r="R230" s="3" t="n"/>
+      <c r="R230" s="3" t="n">
+        <v>920146.9399999999</v>
+      </c>
       <c r="S230" s="3" t="n"/>
-      <c r="T230" s="3" t="n">
-        <v>131368.5</v>
-      </c>
+      <c r="T230" s="3" t="n"/>
       <c r="U230" s="3" t="n"/>
       <c r="V230" s="2" t="inlineStr">
         <is>
@@ -29361,20 +29349,154 @@
         </is>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>CASE-7e3d4a321440d6a7</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>DOC-388bd01c01bbb789</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr"/>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>天津展达科技有限公司</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t>91120116300738701X</t>
+        </is>
+      </c>
+      <c r="K231" s="2" t="inlineStr"/>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="N231" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽处〔2023〕59号</t>
+        </is>
+      </c>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>津税一稽罚〔2023〕21号</t>
+        </is>
+      </c>
+      <c r="P231" s="2" t="inlineStr">
+        <is>
+          <t>我局(所)于2020年8月7日至2022年11月30日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709)2016年1月1日至2017年12月31日纳税情况进行了检查,违法事实及处理决定如下: 经查,你单位取得天津盛汇康机械制品销售有限公司已证实虚开的10份增值税专用发票,发票代码1200154130,发票号码02675003-02675012,发票金额970,696.88元,税额159,933.52元,价税合计1,130,630.4元; 取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元。 根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 经我局(所)于2022年02月14 日至2023年03月09日对你(单位)(地址:天津华苑产业区榕苑路15号1-B-1709 )2016年01月01 日至2017年12月31 日纳税情况进行检查,你(单位)存在违法事实及处罚决定如下: 你单位取得天津明珠电子器件有限公司已证实虚开的15份增值税专用发票,发票代码1200162130,发票号码15241705-15241719,发票金额1,438,034.13元,税额244,465.87元,价税合计1,682,500元,你单位利用他人虚开的专用发票,向税务机关申报抵扣税款进行偷税,少缴增值税244,465.87元、少缴城市维护建设税17,112.61元、少缴企业所得税262,737.00。</t>
+        </is>
+      </c>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加</t>
+        </is>
+      </c>
+      <c r="R231" s="3" t="n"/>
+      <c r="S231" s="3" t="n"/>
+      <c r="T231" s="3" t="n">
+        <v>131368.5</v>
+      </c>
+      <c r="U231" s="3" t="n"/>
+      <c r="V231" s="2" t="inlineStr">
+        <is>
+          <t>根据《中华人民共和国增值税暂行条例》第九条、《中华人民共和国增值税暂行条例实施细则》第十九条、《国家税务总局关于纳税人虚开增值税专用发票征补税款问题的公告》(2012年第33号)中“纳税人取得虚开的增值税专用发票,不得作为增值税合法有效的扣税凭证抵扣其进项税额”之规定,决定追缴2016年8月增值税159,933.52元,2017年1月增值税244,465.87元。 到期不缴纳罚款,我局(所)可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+        </is>
+      </c>
+      <c r="W231" s="4" t="n"/>
+      <c r="X231" s="4" t="n"/>
+      <c r="Y231" s="4" t="n"/>
+      <c r="Z231" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="AA231" s="4" t="n">
+        <v>46263</v>
+      </c>
+      <c r="AB231" s="2" t="inlineStr">
+        <is>
+          <t>完整文书</t>
+        </is>
+      </c>
+      <c r="AC231" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD231" s="2" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="AE231" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF231" s="2" t="inlineStr"/>
+      <c r="AG231" s="2" t="inlineStr"/>
+      <c r="AH231" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局天津市税务局第一稽查局关于送达天津展达科技有限公司《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI231" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="AJ231" s="2" t="inlineStr">
+        <is>
+          <t>页面未提取到可确认的官方发布日期。 Excel 与 CSV 历史数据已合并核对。 字段“涉及税种”存在冲突:保留原值“增值税、企业所得税、消费税、城市维护建设税、教育费附加、地方教育附加”,新值“增值税、企业所得税、城市维护建设税、教育费附加、地方教育附加”未静默覆盖。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ230"/>
-  <conditionalFormatting sqref="AD2:AD230">
+  <autoFilter ref="A1:AJ231"/>
+  <conditionalFormatting sqref="AD2:AD231">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI230">
+  <conditionalFormatting sqref="AI2:AI231">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD230" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD231" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -29654,23 +29776,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE193" r:id="rId273"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF193" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE194" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE195" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE196" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF196" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF194" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE195" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE196" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE197" r:id="rId279"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF197" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE198" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE199" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE200" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE201" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE202" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE203" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF203" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF198" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE199" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE200" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE201" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE202" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE203" r:id="rId287"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE204" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF204" r:id="rId289"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE205" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE206" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF206" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF205" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE206" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE207" r:id="rId293"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF207" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE208" r:id="rId295"/>
@@ -29682,10 +29804,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE211" r:id="rId301"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF211" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE212" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE213" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE214" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE215" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF215" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF212" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE213" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE214" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE215" r:id="rId307"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE216" r:id="rId308"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF216" r:id="rId309"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE217" r:id="rId310"/>
@@ -29705,11 +29827,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE224" r:id="rId324"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF224" r:id="rId325"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE225" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE226" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE227" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE228" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE229" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE230" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF225" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE226" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE227" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE228" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE229" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE230" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE231" r:id="rId333"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -36035,7 +36159,7 @@
         <v>46254</v>
       </c>
       <c r="AA47" s="4" t="n">
-        <v>46263</v>
+        <v>46307</v>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
@@ -37489,7 +37613,7 @@
         <v>46258</v>
       </c>
       <c r="AA58" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
@@ -37631,7 +37755,7 @@
         <v>46254</v>
       </c>
       <c r="AA59" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
@@ -39263,7 +39387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ161"/>
+  <dimension ref="A1:AJ162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -39686,7 +39810,7 @@
         <v>46306</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -39812,7 +39936,7 @@
         <v>46306</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -39934,7 +40058,7 @@
         <v>46304</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -39970,7 +40094,7 @@
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“官方发布日期”存在冲突:保留原值“2026-10-08”,新值“2026-10-09”未静默覆盖。 字段“官方原文链接”存在冲突:保留原值“https://jiangsu.chinatax.gov.cn/art/2026/10/8/art_9566_1790007.html”,新值“https://jiangsu.chinatax.gov.cn/art/2026/10/9/art_9566_1790687.html”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -48390,7 +48514,7 @@
         <v>46264</v>
       </c>
       <c r="AA75" s="4" t="n">
-        <v>46268</v>
+        <v>46307</v>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
@@ -48512,7 +48636,7 @@
         <v>46264</v>
       </c>
       <c r="AA76" s="4" t="n">
-        <v>46268</v>
+        <v>46307</v>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
@@ -55116,7 +55240,7 @@
         <v>46254</v>
       </c>
       <c r="AA130" s="4" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="AB130" s="2" t="inlineStr">
         <is>
@@ -55970,7 +56094,7 @@
         <v>46229</v>
       </c>
       <c r="AA137" s="4" t="n">
-        <v>46263</v>
+        <v>46307</v>
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
@@ -56092,7 +56216,7 @@
         <v>46229</v>
       </c>
       <c r="AA138" s="4" t="n">
-        <v>46263</v>
+        <v>46307</v>
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
@@ -56980,47 +57104,47 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>CASE-0f4867f7b70d12f3</t>
+          <t>CASE-f77ed45b302a9f5d</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>DOC-6f25d6b79e123d03</t>
+          <t>DOC-73433b3e087ef737</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局嘉兴市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局</t>
+          <t>国家税务总局嘉兴市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>贵州铂朗物流有限公司</t>
+          <t>嘉兴市昇悦供应链服务有限公司</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>91520115MAAK0DB335</t>
+          <t>91330424MAEBW7AXXK</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -57031,19 +57155,15 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
+          <t>嘉税一稽处〔2026〕67号</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽处〔2026〕17号</t>
-        </is>
-      </c>
-      <c r="O146" s="2" t="inlineStr">
-        <is>
-          <t>筑税三稽罚〔2026〕22号</t>
-        </is>
-      </c>
+          <t>嘉税一稽处〔2026〕67号</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr"/>
       <c r="P146" s="2" t="inlineStr"/>
       <c r="Q146" s="2" t="inlineStr"/>
       <c r="R146" s="3" t="n"/>
@@ -57053,14 +57173,14 @@
       <c r="V146" s="2" t="inlineStr"/>
       <c r="W146" s="4" t="n"/>
       <c r="X146" s="4" t="n">
-        <v>46122</v>
+        <v>46129</v>
       </c>
       <c r="Y146" s="4" t="n"/>
       <c r="Z146" s="4" t="n">
-        <v>46229</v>
+        <v>46307</v>
       </c>
       <c r="AA146" s="4" t="n">
-        <v>46263</v>
+        <v>46307</v>
       </c>
       <c r="AB146" s="2" t="inlineStr">
         <is>
@@ -57082,27 +57202,31 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF146" s="2" t="inlineStr"/>
+      <c r="AF146" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG146" s="2" t="inlineStr"/>
       <c r="AH146" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局嘉兴市税务局第一稽查局关于送达《税务处理决定书》的公告嘉税一稽公告〔2026〕18号</t>
         </is>
       </c>
       <c r="AI146" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ146" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
@@ -57111,7 +57235,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>DOC-e8233eb0e06b6e3e</t>
+          <t>DOC-6f25d6b79e123d03</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -57148,12 +57272,12 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>筑税三稽罚〔2026〕22号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -57224,68 +57348,68 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>CASE-136615addd5d0c0e</t>
+          <t>CASE-0f4867f7b70d12f3</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>DOC-551df7dc5c028b27</t>
+          <t>DOC-e8233eb0e06b6e3e</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>贵州省</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>来宾市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>广西欣瑞木业有限公司</t>
+          <t>贵州铂朗物流有限公司</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>91451322MAD89XWX07</t>
+          <t>91520115MAAK0DB335</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽处〔2026〕6号</t>
+          <t>筑税三稽处〔2026〕17号</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>筑税三稽罚〔2026〕22号</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr"/>
@@ -57297,14 +57421,14 @@
       <c r="V148" s="2" t="inlineStr"/>
       <c r="W148" s="4" t="n"/>
       <c r="X148" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="Y148" s="4" t="n"/>
       <c r="Z148" s="4" t="n">
         <v>46229</v>
       </c>
       <c r="AA148" s="4" t="n">
-        <v>46273</v>
+        <v>46263</v>
       </c>
       <c r="AB148" s="2" t="inlineStr">
         <is>
@@ -57330,7 +57454,7 @@
       <c r="AG148" s="2" t="inlineStr"/>
       <c r="AH148" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
+          <t>国家税务总局贵阳市税务局第三稽查局关于送达税务处理决定书税务行政处罚决定书的公告</t>
         </is>
       </c>
       <c r="AI148" s="2" t="inlineStr">
@@ -57346,7 +57470,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
@@ -57355,7 +57479,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>DOC-21f0193b66d5c3e9</t>
+          <t>DOC-551df7dc5c028b27</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -57392,12 +57516,12 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>来市税二稽罚〔2026〕4号</t>
+          <t>来市税二稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -57468,68 +57592,68 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>175</v>
+        <v>9</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>CASE-ac24bc507b11c4b9</t>
+          <t>CASE-136615addd5d0c0e</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>DOC-023f2cf01f84fa12</t>
+          <t>DOC-21f0193b66d5c3e9</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>乌鲁木齐市</t>
+          <t>来宾市</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局乌鲁木齐市税务局稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局乌鲁木齐市税务局稽查局</t>
+          <t>国家税务总局来宾市税务局第二稽查局</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>新疆伍纬智兴工程设计有限公司</t>
+          <t>广西欣瑞木业有限公司</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>91650102MA7AB6M720</t>
+          <t>91451322MAD89XWX07</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>乌税稽处〔2026〕35号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>乌税稽处〔2026〕35号</t>
+          <t>来市税二稽处〔2026〕6号</t>
         </is>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>乌税稽罚〔2026〕26号</t>
+          <t>来市税二稽罚〔2026〕4号</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr"/>
@@ -57541,14 +57665,14 @@
       <c r="V150" s="2" t="inlineStr"/>
       <c r="W150" s="4" t="n"/>
       <c r="X150" s="4" t="n">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="Y150" s="4" t="n"/>
       <c r="Z150" s="4" t="n">
-        <v>46286</v>
+        <v>46229</v>
       </c>
       <c r="AA150" s="4" t="n">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
@@ -57570,31 +57694,27 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF150" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF150" s="2" t="inlineStr"/>
       <c r="AG150" s="2" t="inlineStr"/>
       <c r="AH150" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局乌鲁木齐市税务局-通知公告-国家税务总局乌鲁木齐市税务局稽查局关于送达《税务处理决定书》和《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局来宾市税务局第二稽查局 关于送达《税务处理决定书》、《税务行政处罚决定书》、《纳税缴费信用修复事项告知书》的公告_国家税务总局来宾市税务局</t>
         </is>
       </c>
       <c r="AI150" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ150" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
@@ -57603,7 +57723,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>DOC-7e3d72fa54372f41</t>
+          <t>DOC-023f2cf01f84fa12</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -57640,12 +57760,12 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>乌税稽罚〔2026〕26号</t>
+          <t>乌税稽处〔2026〕35号</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -57720,66 +57840,70 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>CASE-eb7e9c22bd97f211</t>
+          <t>CASE-ac24bc507b11c4b9</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>DOC-4c99e9a228472ee1</t>
+          <t>DOC-7e3d72fa54372f41</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>乌鲁木齐市</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局无锡市税务局第一稽查局</t>
+          <t>国家税务总局乌鲁木齐市税务局稽查局</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局无锡市税务局第一稽查局</t>
+          <t>国家税务总局乌鲁木齐市税务局稽查局</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>宜兴市华欧金属材料有限公司</t>
+          <t>新疆伍纬智兴工程设计有限公司</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>91320282MA1MMJ8YXD</t>
+          <t>91650102MA7AB6M720</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>锡税一稽处〔2026〕71号</t>
+          <t>乌税稽罚〔2026〕26号</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>锡税一稽处〔2026〕71号</t>
-        </is>
-      </c>
-      <c r="O152" s="2" t="inlineStr"/>
+          <t>乌税稽处〔2026〕35号</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>乌税稽罚〔2026〕26号</t>
+        </is>
+      </c>
       <c r="P152" s="2" t="inlineStr"/>
       <c r="Q152" s="2" t="inlineStr"/>
       <c r="R152" s="3" t="n"/>
@@ -57789,14 +57913,14 @@
       <c r="V152" s="2" t="inlineStr"/>
       <c r="W152" s="4" t="n"/>
       <c r="X152" s="4" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="Y152" s="4" t="n"/>
       <c r="Z152" s="4" t="n">
-        <v>46250</v>
+        <v>46286</v>
       </c>
       <c r="AA152" s="4" t="n">
-        <v>46263</v>
+        <v>46286</v>
       </c>
       <c r="AB152" s="2" t="inlineStr">
         <is>
@@ -57818,86 +57942,90 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF152" s="2" t="inlineStr"/>
+      <c r="AF152" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG152" s="2" t="inlineStr"/>
       <c r="AH152" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局无锡市税务局第一稽查局关于送达《税务处理决定书》的公告(宜兴市华欧金属材料有限公司)</t>
+          <t>国家税务总局乌鲁木齐市税务局-通知公告-国家税务总局乌鲁木齐市税务局稽查局关于送达《税务处理决定书》和《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI152" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ152" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>CASE-393a878d93a22709</t>
+          <t>CASE-eb7e9c22bd97f211</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>DOC-cda8cba853896b18</t>
+          <t>DOC-4c99e9a228472ee1</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>番禺区</t>
-        </is>
-      </c>
+          <t>无锡市</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr"/>
+          <t>国家税务总局无锡市税务局第一稽查局</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局无锡市税务局第一稽查局</t>
+        </is>
+      </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>广州赞荣服装有限公司</t>
+          <t>宜兴市华欧金属材料有限公司</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>91440113MA59AJFJ1J</t>
+          <t>91320282MA1MMJ8YXD</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
-      <c r="N153" s="2" t="inlineStr"/>
-      <c r="O153" s="2" t="inlineStr">
-        <is>
-          <t>穗番税退罚字〔2026〕1号</t>
-        </is>
-      </c>
+          <t>锡税一稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>锡税一稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr"/>
       <c r="P153" s="2" t="inlineStr"/>
       <c r="Q153" s="2" t="inlineStr"/>
       <c r="R153" s="3" t="n"/>
@@ -57907,14 +58035,14 @@
       <c r="V153" s="2" t="inlineStr"/>
       <c r="W153" s="4" t="n"/>
       <c r="X153" s="4" t="n">
-        <v>46091</v>
+        <v>46111</v>
       </c>
       <c r="Y153" s="4" t="n"/>
       <c r="Z153" s="4" t="n">
-        <v>46229</v>
+        <v>46250</v>
       </c>
       <c r="AA153" s="4" t="n">
-        <v>46307</v>
+        <v>46263</v>
       </c>
       <c r="AB153" s="2" t="inlineStr">
         <is>
@@ -57928,7 +58056,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>待核验</t>
+          <t>已核验</t>
         </is>
       </c>
       <c r="AE153" s="5" t="inlineStr">
@@ -57936,90 +58064,86 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF153" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF153" s="2" t="inlineStr"/>
       <c r="AG153" s="2" t="inlineStr"/>
       <c r="AH153" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局无锡市税务局第一稽查局关于送达《税务处理决定书》的公告(宜兴市华欧金属材料有限公司)</t>
         </is>
       </c>
       <c r="AI153" s="2" t="inlineStr">
         <is>
-          <t>内容不匹配</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ153" s="2" t="inlineStr">
         <is>
-          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>CASE-cd07b952e6e3cbfe</t>
+          <t>CASE-393a878d93a22709</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>DOC-b08bd7ef9ec8845c</t>
+          <t>DOC-cda8cba853896b18</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr"/>
+          <t>广州市</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>番禺区</t>
+        </is>
+      </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局嘉兴市税务局第一稽查局</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>国家税务总局嘉兴市税务局第一稽查局</t>
-        </is>
-      </c>
+          <t>国家税务总局广州市番禺区税务局</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr"/>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市全胜贵金属有限公司</t>
+          <t>广州赞荣服装有限公司</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>91330400MA28A96A7D</t>
+          <t>91440113MA59AJFJ1J</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>嘉税一稽处〔2026〕41号</t>
-        </is>
-      </c>
-      <c r="N154" s="2" t="inlineStr">
-        <is>
-          <t>嘉税一稽处〔2026〕41号</t>
-        </is>
-      </c>
-      <c r="O154" s="2" t="inlineStr"/>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr"/>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>穗番税退罚字〔2026〕1号</t>
+        </is>
+      </c>
       <c r="P154" s="2" t="inlineStr"/>
       <c r="Q154" s="2" t="inlineStr"/>
       <c r="R154" s="3" t="n"/>
@@ -58029,14 +58153,14 @@
       <c r="V154" s="2" t="inlineStr"/>
       <c r="W154" s="4" t="n"/>
       <c r="X154" s="4" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="Y154" s="4" t="n"/>
       <c r="Z154" s="4" t="n">
-        <v>46254</v>
+        <v>46229</v>
       </c>
       <c r="AA154" s="4" t="n">
-        <v>46263</v>
+        <v>46307</v>
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
@@ -58050,7 +58174,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>已核验</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="AE154" s="5" t="inlineStr">
@@ -58066,63 +58190,63 @@
       <c r="AG154" s="2" t="inlineStr"/>
       <c r="AH154" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局浙江省税务局 通知公告 国家税务总局嘉兴市税务局第一稽查局关于送达《税务处理决定书》的公告(嘉税一稽公告(2026)6号)</t>
+          <t>国家税务总局广州市番禺区税务局关于送达税务行政处罚告知书的公告</t>
         </is>
       </c>
       <c r="AI154" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>内容不匹配</t>
         </is>
       </c>
       <c r="AJ154" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。</t>
+          <t>页面标题与正文/附件文书类型不一致,需人工复核。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>CASE-0b4a4519ba4f5ad9</t>
+          <t>CASE-cd07b952e6e3cbfe</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>DOC-5376b9bae81cfc82</t>
+          <t>DOC-b08bd7ef9ec8845c</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局</t>
+          <t>国家税务总局嘉兴市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局常州市税务局稽查局</t>
+          <t>国家税务总局嘉兴市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>常州好佳车辆配件有限公司</t>
+          <t>嘉兴市全胜贵金属有限公司</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>91320411094264460B</t>
+          <t>91330400MA28A96A7D</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr"/>
@@ -58133,12 +58257,12 @@
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
+          <t>嘉税一稽处〔2026〕41号</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>常税稽处〔2026〕71号</t>
+          <t>嘉税一稽处〔2026〕41号</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr"/>
@@ -58151,11 +58275,11 @@
       <c r="V155" s="2" t="inlineStr"/>
       <c r="W155" s="4" t="n"/>
       <c r="X155" s="4" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="Y155" s="4" t="n"/>
       <c r="Z155" s="4" t="n">
-        <v>46229</v>
+        <v>46254</v>
       </c>
       <c r="AA155" s="4" t="n">
         <v>46263</v>
@@ -58188,7 +58312,7 @@
       <c r="AG155" s="2" t="inlineStr"/>
       <c r="AH155" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
+          <t>国家税务总局浙江省税务局 通知公告 国家税务总局嘉兴市税务局第一稽查局关于送达《税务处理决定书》的公告(嘉税一稽公告(2026)6号)</t>
         </is>
       </c>
       <c r="AI155" s="2" t="inlineStr">
@@ -58204,54 +58328,50 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>169</v>
+        <v>13</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>CASE-fff2e023850214a5</t>
+          <t>CASE-0b4a4519ba4f5ad9</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>DOC-089127a6678b838f</t>
+          <t>DOC-5376b9bae81cfc82</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>巴音郭楞蒙古自治州</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
+          <t>国家税务总局江苏省税务局</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
+          <t>国家税务总局常州市税务局稽查局</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>库尔勒兆庆商贸有限公司</t>
+          <t>常州好佳车辆配件有限公司</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>91652801MA77Q8JE59</t>
-        </is>
-      </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>冯某玲及实际控制人王某涛</t>
-        </is>
-      </c>
+          <t>91320411094264460B</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -58259,19 +58379,15 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>巴税稽处〔2026〕11号</t>
+          <t>常税稽处〔2026〕71号</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>巴税稽处〔2026〕11号</t>
-        </is>
-      </c>
-      <c r="O156" s="2" t="inlineStr">
-        <is>
-          <t>巴税稽罚〔2026〕13号</t>
-        </is>
-      </c>
+          <t>常税稽处〔2026〕71号</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr"/>
       <c r="P156" s="2" t="inlineStr"/>
       <c r="Q156" s="2" t="inlineStr"/>
       <c r="R156" s="3" t="n"/>
@@ -58281,14 +58397,14 @@
       <c r="V156" s="2" t="inlineStr"/>
       <c r="W156" s="4" t="n"/>
       <c r="X156" s="4" t="n">
-        <v>46077</v>
+        <v>46087</v>
       </c>
       <c r="Y156" s="4" t="n"/>
       <c r="Z156" s="4" t="n">
-        <v>46286</v>
+        <v>46229</v>
       </c>
       <c r="AA156" s="4" t="n">
-        <v>46286</v>
+        <v>46263</v>
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
@@ -58318,7 +58434,7 @@
       <c r="AG156" s="2" t="inlineStr"/>
       <c r="AH156" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局巴州税务局-通知公告-国家税务总局巴音郭楞蒙古自治州税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局常州市税务局稽查局关于送达常州好佳车辆配件有限公司《税务处理决定书》的公告</t>
         </is>
       </c>
       <c r="AI156" s="2" t="inlineStr">
@@ -58328,13 +58444,13 @@
       </c>
       <c r="AJ156" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
@@ -58343,7 +58459,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>DOC-73007b3650cf14c2</t>
+          <t>DOC-089127a6678b838f</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -58384,12 +58500,12 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>巴税稽罚〔2026〕13号</t>
+          <t>巴税稽处〔2026〕11号</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -58464,62 +58580,74 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>92</v>
+        <v>170</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>CASE-4ae87644334697ee</t>
+          <t>CASE-fff2e023850214a5</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>DOC-bb4f7abf3229ef95</t>
+          <t>DOC-73007b3650cf14c2</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>揭阳市</t>
+          <t>巴音郭楞蒙古自治州</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局揭阳市税务局第一稽查局</t>
+          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局揭阳市税务局第一稽查局</t>
+          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>广东润升药械有限公司</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="inlineStr"/>
-      <c r="K158" s="2" t="inlineStr"/>
+          <t>库尔勒兆庆商贸有限公司</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>91652801MA77Q8JE59</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>冯某玲及实际控制人王某涛</t>
+        </is>
+      </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>税务处理决定书</t>
+          <t>税务行政处罚决定书</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>揭税一稽处〔2026〕3号</t>
+          <t>巴税稽罚〔2026〕13号</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>揭税一稽处〔2026〕3号</t>
-        </is>
-      </c>
-      <c r="O158" s="2" t="inlineStr"/>
+          <t>巴税稽处〔2026〕11号</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>巴税稽罚〔2026〕13号</t>
+        </is>
+      </c>
       <c r="P158" s="2" t="inlineStr"/>
       <c r="Q158" s="2" t="inlineStr"/>
       <c r="R158" s="3" t="n"/>
@@ -58529,14 +58657,14 @@
       <c r="V158" s="2" t="inlineStr"/>
       <c r="W158" s="4" t="n"/>
       <c r="X158" s="4" t="n">
-        <v>46048</v>
+        <v>46077</v>
       </c>
       <c r="Y158" s="4" t="n"/>
       <c r="Z158" s="4" t="n">
-        <v>46254</v>
+        <v>46286</v>
       </c>
       <c r="AA158" s="4" t="n">
-        <v>46307</v>
+        <v>46286</v>
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
@@ -58558,62 +58686,66 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF158" s="2" t="inlineStr"/>
+      <c r="AF158" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
       <c r="AG158" s="2" t="inlineStr"/>
       <c r="AH158" s="2" t="inlineStr">
         <is>
-          <t>广东润升药械有限公司税务文书送达公告(揭税一稽公〔2026〕6号)</t>
+          <t>国家税务总局巴州税务局-通知公告-国家税务总局巴音郭楞蒙古自治州税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
         </is>
       </c>
       <c r="AI158" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>附件正常</t>
         </is>
       </c>
       <c r="AJ158" s="2" t="inlineStr">
         <is>
-          <t>Excel 与 CSV 历史数据已合并核对。 字段“城市”存在冲突:保留原值“揭阳市”,新值“返回市”未静默覆盖。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>CASE-0345194bffc3b105</t>
+          <t>CASE-4ae87644334697ee</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>DOC-849dbbf92d95f7da</t>
+          <t>DOC-bb4f7abf3229ef95</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>连云港市</t>
+          <t>揭阳市</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局连云港市税务局第一稽查局</t>
+          <t>国家税务总局揭阳市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局连云港市税务局第一稽查局</t>
+          <t>国家税务总局揭阳市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>灌南时路能源有限公司</t>
+          <t>广东润升药械有限公司</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr"/>
@@ -58625,12 +58757,12 @@
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>连税稽一处〔2026〕3号</t>
+          <t>揭税一稽处〔2026〕3号</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>连税稽一处〔2026〕3号</t>
+          <t>揭税一稽处〔2026〕3号</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr"/>
@@ -58643,14 +58775,14 @@
       <c r="V159" s="2" t="inlineStr"/>
       <c r="W159" s="4" t="n"/>
       <c r="X159" s="4" t="n">
-        <v>46038</v>
+        <v>46048</v>
       </c>
       <c r="Y159" s="4" t="n"/>
       <c r="Z159" s="4" t="n">
-        <v>46273</v>
+        <v>46254</v>
       </c>
       <c r="AA159" s="4" t="n">
-        <v>46273</v>
+        <v>46307</v>
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
@@ -58672,78 +58804,66 @@
           <t>打开原文</t>
         </is>
       </c>
-      <c r="AF159" s="5" t="inlineStr">
-        <is>
-          <t>打开附件</t>
-        </is>
-      </c>
+      <c r="AF159" s="2" t="inlineStr"/>
       <c r="AG159" s="2" t="inlineStr"/>
       <c r="AH159" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局连云港市税务局第一稽查局税务处理决定书送达公告</t>
+          <t>广东润升药械有限公司税务文书送达公告(揭税一稽公〔2026〕6号)</t>
         </is>
       </c>
       <c r="AI159" s="2" t="inlineStr">
         <is>
-          <t>附件正常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="AJ159" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
+          <t>Excel 与 CSV 历史数据已合并核对。 字段“城市”存在冲突:保留原值“揭阳市”,新值“返回市”未静默覆盖。</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>CASE-bef08dfa2f488cf9</t>
+          <t>CASE-0345194bffc3b105</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>DOC-700a551817c8c5fa</t>
+          <t>DOC-849dbbf92d95f7da</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>巴音郭楞蒙古自治州</t>
+          <t>连云港市</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
+          <t>国家税务总局连云港市税务局第一稽查局</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
+          <t>国家税务总局连云港市税务局第一稽查局</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>若羌县宏源加油站有限公司</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>91652824080224388F</t>
-        </is>
-      </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>朱某庭</t>
-        </is>
-      </c>
+          <t>灌南时路能源有限公司</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
           <t>税务处理决定书</t>
@@ -58751,19 +58871,15 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>巴税稽处〔2025〕97号</t>
+          <t>连税稽一处〔2026〕3号</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>巴税稽处〔2025〕97号</t>
-        </is>
-      </c>
-      <c r="O160" s="2" t="inlineStr">
-        <is>
-          <t>巴税稽罚〔2025〕97号</t>
-        </is>
-      </c>
+          <t>连税稽一处〔2026〕3号</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr"/>
       <c r="P160" s="2" t="inlineStr"/>
       <c r="Q160" s="2" t="inlineStr"/>
       <c r="R160" s="3" t="n"/>
@@ -58773,14 +58889,14 @@
       <c r="V160" s="2" t="inlineStr"/>
       <c r="W160" s="4" t="n"/>
       <c r="X160" s="4" t="n">
-        <v>46034</v>
+        <v>46038</v>
       </c>
       <c r="Y160" s="4" t="n"/>
       <c r="Z160" s="4" t="n">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="AA160" s="4" t="n">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
@@ -58810,7 +58926,7 @@
       <c r="AG160" s="2" t="inlineStr"/>
       <c r="AH160" s="2" t="inlineStr">
         <is>
-          <t>国家税务总局巴州税务局-通知公告-国家税务总局巴音郭楞蒙古自治州税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+          <t>国家税务总局江苏省税务局网站 通知公告 国家税务总局连云港市税务局第一稽查局税务处理决定书送达公告</t>
         </is>
       </c>
       <c r="AI160" s="2" t="inlineStr">
@@ -58826,7 +58942,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
@@ -58835,7 +58951,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>DOC-65bfc2d5b7ed46f9</t>
+          <t>DOC-700a551817c8c5fa</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -58876,12 +58992,12 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>税务行政处罚决定书</t>
+          <t>税务处理决定书</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>巴税稽罚〔2025〕97号</t>
+          <t>巴税稽处〔2025〕97号</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -58954,20 +59070,150 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>CASE-bef08dfa2f488cf9</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>DOC-65bfc2d5b7ed46f9</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>新疆维吾尔自治区</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>巴音郭楞蒙古自治州</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局巴音郭楞蒙古自治州税务局稽查局</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>若羌县宏源加油站有限公司</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>91652824080224388F</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>朱某庭</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>税务行政处罚决定书</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>巴税稽罚〔2025〕97号</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>巴税稽处〔2025〕97号</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>巴税稽罚〔2025〕97号</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr"/>
+      <c r="Q162" s="2" t="inlineStr"/>
+      <c r="R162" s="3" t="n"/>
+      <c r="S162" s="3" t="n"/>
+      <c r="T162" s="3" t="n"/>
+      <c r="U162" s="3" t="n"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="4" t="n"/>
+      <c r="X162" s="4" t="n">
+        <v>46034</v>
+      </c>
+      <c r="Y162" s="4" t="n"/>
+      <c r="Z162" s="4" t="n">
+        <v>46286</v>
+      </c>
+      <c r="AA162" s="4" t="n">
+        <v>46286</v>
+      </c>
+      <c r="AB162" s="2" t="inlineStr">
+        <is>
+          <t>仅公告送达/仅文号线索</t>
+        </is>
+      </c>
+      <c r="AC162" s="2" t="inlineStr">
+        <is>
+          <t>税务机关官网</t>
+        </is>
+      </c>
+      <c r="AD162" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AE162" s="5" t="inlineStr">
+        <is>
+          <t>打开原文</t>
+        </is>
+      </c>
+      <c r="AF162" s="5" t="inlineStr">
+        <is>
+          <t>打开附件</t>
+        </is>
+      </c>
+      <c r="AG162" s="2" t="inlineStr"/>
+      <c r="AH162" s="2" t="inlineStr">
+        <is>
+          <t>国家税务总局巴州税务局-通知公告-国家税务总局巴音郭楞蒙古自治州税务局稽查局关于送达《税务处理决定书》《税务行政处罚决定书》的公告</t>
+        </is>
+      </c>
+      <c r="AI162" s="2" t="inlineStr">
+        <is>
+          <t>附件正常</t>
+        </is>
+      </c>
+      <c r="AJ162" s="2" t="inlineStr">
+        <is>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ161"/>
-  <conditionalFormatting sqref="AD2:AD161">
+  <autoFilter ref="A1:AJ162"/>
+  <conditionalFormatting sqref="AD2:AD162">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AD2="待核验"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI161">
+  <conditionalFormatting sqref="AI2:AI162">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($AI2&lt;&gt;"正常",$AI2&lt;&gt;"附件正常")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AD2:AD161" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="AD2:AD162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"已核验,待核验,人工复核完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -59180,16 +59426,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE144" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE145" r:id="rId207"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE146" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE147" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE148" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE149" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE150" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF150" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF146" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE147" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE148" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE149" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE150" r:id="rId213"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE151" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF151" r:id="rId215"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE152" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE153" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF153" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF152" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE153" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE154" r:id="rId219"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF154" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE155" r:id="rId221"/>
@@ -59199,12 +59445,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE157" r:id="rId225"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF157" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE158" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE159" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF159" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF158" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE159" r:id="rId229"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE160" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF160" r:id="rId231"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE161" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF161" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE162" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF162" r:id="rId235"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -61386,7 +61634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -70635,8 +70883,61 @@
         </is>
       </c>
     </row>
+    <row r="186" ht="54" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12T20:23:53+08:00</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 至 2026-10-12</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="n">
+        <v>513</v>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G186" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I186" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>嘉兴市昇悦供应链服务有限公司</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: RetryError: HTTPConnectionPool(host='qinghai.chinatax.gov.cn', port=80): Max retries exceeded with url: /hxz/sjtzgg/ (Caused by ResponseError('too many 502 error responses')) | discover_official_index: https://fujian.chinatax.go...</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增1份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问80页，访问失败407页，持久化待复核398个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M185"/>
+  <autoFilter ref="A1:M186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -797,7 +797,7 @@
         <v>46308</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>46308</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46308</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46308</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46308</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>46306</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>46306</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>46304</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>46306</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>46306</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>46308</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“苏州税稽处〔2026〕164号”,新值“苏州税稽处〔2026〕162号”未静默覆盖。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“苏州税稽处〔2026〕164号”,新值“苏州税稽处〔2026〕162号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
         <v>46294</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46296</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>46296</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>46286</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>46286</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>46280</v>
       </c>
       <c r="AA65" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>46280</v>
       </c>
       <c r="AA67" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>46280</v>
       </c>
       <c r="AA68" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>46280</v>
       </c>
       <c r="AA69" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>46280</v>
       </c>
       <c r="AA70" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>46280</v>
       </c>
       <c r="AA71" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>46254</v>
       </c>
       <c r="AA112" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>46254</v>
       </c>
       <c r="AA113" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB113" s="2" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>46246</v>
       </c>
       <c r="AA137" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>46234</v>
       </c>
       <c r="AA163" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB163" s="2" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>46238</v>
       </c>
       <c r="AA164" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB164" s="2" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>46238</v>
       </c>
       <c r="AA165" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>46254</v>
       </c>
       <c r="AA171" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>46258</v>
       </c>
       <c r="AA222" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>46254</v>
       </c>
       <c r="AA223" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB223" s="2" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>46258</v>
       </c>
       <c r="AA232" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>46308</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>46308</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>46308</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46308</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>46308</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>46234</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>46258</v>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>46254</v>
       </c>
       <c r="AA64" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>46258</v>
       </c>
       <c r="AA70" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
@@ -41315,7 +41315,7 @@
         <v>46306</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>46306</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>46304</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>46306</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>46306</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>46308</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
       </c>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>字段“决定书文号”存在冲突:保留原值“苏州税稽处〔2026〕164号”,新值“苏州税稽处〔2026〕162号”未静默覆盖。</t>
+          <t>字段“决定书文号”存在冲突:保留原值“苏州税稽处〔2026〕164号”,新值“苏州税稽处〔2026〕162号”未静默覆盖。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -44317,7 +44317,7 @@
         <v>46294</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>46296</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>46296</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -45899,7 +45899,7 @@
         <v>46286</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
@@ -46021,7 +46021,7 @@
         <v>46286</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>46280</v>
       </c>
       <c r="AA47" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>46280</v>
       </c>
       <c r="AA49" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>46280</v>
       </c>
       <c r="AA50" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>46280</v>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
@@ -47217,7 +47217,7 @@
         <v>46280</v>
       </c>
       <c r="AA52" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>46280</v>
       </c>
       <c r="AA53" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
@@ -51727,7 +51727,7 @@
         <v>46254</v>
       </c>
       <c r="AA89" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>46254</v>
       </c>
       <c r="AA90" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
@@ -54535,7 +54535,7 @@
         <v>46246</v>
       </c>
       <c r="AA112" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>46238</v>
       </c>
       <c r="AA127" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
@@ -56507,7 +56507,7 @@
         <v>46238</v>
       </c>
       <c r="AA128" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB128" s="2" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>46254</v>
       </c>
       <c r="AA131" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
@@ -61658,7 +61658,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -62935,7 +62935,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -63258,7 +63258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M188"/>
+  <dimension ref="A1:M189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -72666,8 +72666,57 @@
         </is>
       </c>
     </row>
+    <row r="189" ht="54" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T17:27:56+08:00</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 至 2026-10-14</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n">
+        <v>525</v>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G189" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I189" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /qzsswj/xxgk/sjxxgk/qtgg_23603/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinata...</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问79页，访问失败418页，持久化待复核409个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M188"/>
+  <autoFilter ref="A1:M189"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$190</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -27098,7 +27098,7 @@
         <v>46229</v>
       </c>
       <c r="AA213" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>46254</v>
       </c>
       <c r="AA221" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
@@ -59783,7 +59783,7 @@
         <v>46229</v>
       </c>
       <c r="AA155" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB155" s="2" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>46254</v>
       </c>
       <c r="AA160" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
@@ -61902,7 +61902,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -63258,7 +63258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M189"/>
+  <dimension ref="A1:M190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -72715,8 +72715,57 @@
         </is>
       </c>
     </row>
+    <row r="190" ht="54" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T17:57:30+08:00</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 至 2026-10-14</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="n">
+        <v>511</v>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G190" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I190" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/qzsswj/xxgk/sjxxgk/qtgg_23603/: ConnectionError: HTTPSConnectionPool(host='fuji...</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问78页，访问失败415页，持久化待复核406个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M189"/>
+  <autoFilter ref="A1:M190"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -797,7 +797,7 @@
         <v>46308</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>46308</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46308</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>46308</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46308</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>46306</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>46306</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>46304</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>46306</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>46306</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>46308</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>46294</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46296</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>46296</v>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>46286</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>46286</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>46280</v>
       </c>
       <c r="AA65" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>46280</v>
       </c>
       <c r="AA67" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>46280</v>
       </c>
       <c r="AA68" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>46280</v>
       </c>
       <c r="AA69" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>46280</v>
       </c>
       <c r="AA70" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>46280</v>
       </c>
       <c r="AA71" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>46254</v>
       </c>
       <c r="AA112" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>46254</v>
       </c>
       <c r="AA113" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB113" s="2" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>46246</v>
       </c>
       <c r="AA137" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>46234</v>
       </c>
       <c r="AA163" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB163" s="2" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>46238</v>
       </c>
       <c r="AA164" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB164" s="2" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>46238</v>
       </c>
       <c r="AA165" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>46254</v>
       </c>
       <c r="AA171" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>46229</v>
       </c>
       <c r="AA213" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>46254</v>
       </c>
       <c r="AA221" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>46258</v>
       </c>
       <c r="AA222" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>46254</v>
       </c>
       <c r="AA223" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB223" s="2" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>46258</v>
       </c>
       <c r="AA232" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>46308</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>46308</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>46308</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46308</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>46308</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>46234</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>46258</v>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>46254</v>
       </c>
       <c r="AA64" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>46258</v>
       </c>
       <c r="AA70" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
@@ -41315,7 +41315,7 @@
         <v>46306</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>46306</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>46304</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>46306</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>46306</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>46308</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>46294</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         <v>46296</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>46296</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
@@ -45899,7 +45899,7 @@
         <v>46286</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
@@ -46021,7 +46021,7 @@
         <v>46286</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>46280</v>
       </c>
       <c r="AA47" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>46280</v>
       </c>
       <c r="AA49" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>46280</v>
       </c>
       <c r="AA50" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>46280</v>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
@@ -47217,7 +47217,7 @@
         <v>46280</v>
       </c>
       <c r="AA52" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>46280</v>
       </c>
       <c r="AA53" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
@@ -51727,7 +51727,7 @@
         <v>46254</v>
       </c>
       <c r="AA89" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>46254</v>
       </c>
       <c r="AA90" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
@@ -54535,7 +54535,7 @@
         <v>46246</v>
       </c>
       <c r="AA112" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>46238</v>
       </c>
       <c r="AA127" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
@@ -56507,7 +56507,7 @@
         <v>46238</v>
       </c>
       <c r="AA128" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB128" s="2" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>46254</v>
       </c>
       <c r="AA131" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
@@ -59783,7 +59783,7 @@
         <v>46229</v>
       </c>
       <c r="AA155" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB155" s="2" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>46254</v>
       </c>
       <c r="AA160" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
@@ -61658,7 +61658,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -61902,7 +61902,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -62935,7 +62935,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -63258,7 +63258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M190"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -72764,8 +72764,57 @@
         </is>
       </c>
     </row>
+    <row r="191" ht="54" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T17:05:57+08:00</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 至 2026-10-15</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="n">
+        <v>531</v>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G191" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I191" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问82页，访问失败430页，持久化待复核421个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M190"/>
+  <autoFilter ref="A1:M191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -63258,7 +63258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M191"/>
+  <dimension ref="A1:M192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -72813,8 +72813,57 @@
         </is>
       </c>
     </row>
+    <row r="192" ht="54" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T17:36:49+08:00</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 至 2026-10-15</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>489</v>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I192" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/pingtanswj/zfxxgkzl/zfxxgkml/qtgg/: ConnectionError: HTTPSConnectionPool(host='...</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问55页，访问失败431页，持久化待复核422个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M191"/>
+  <autoFilter ref="A1:M192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$168</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$195</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -781,7 +781,7 @@
         <v>46311</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         <v>46311</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>46311</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>46311</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1185,7 +1185,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1269,7 +1273,7 @@
         <v>46311</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1303,7 +1307,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1399,7 +1407,7 @@
         <v>46308</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1549,7 @@
         <v>46308</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1776,7 +1784,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>我局于2025年6月16日起,对你2020年1月1日-2020年12月31日期间的涉税情况进行检查,确认你有如下违法事实,并作出如下处罚决定: 根据《税务处理决定书》(鄂税三稽处〔2026〕8号)认定你存在以下违法事实: 经查,你于2020年提供装修服务取得收入163,804.00元,未进行纳税申报。 根据《中华人民共和国税收征收管理法》(2015年4月24日发布的主席令第二十三号修订)第六十四条第二款:“纳税人不进行纳税申报,不缴或者少缴应纳税款的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款。 根据《内蒙古自治区国家税务局内蒙古自治区地方税务局关于发布〈内蒙古自治区税务行政处罚裁量基准〉的公告》(内蒙古自治区国家税务局内蒙古自治区地方税务局公告2017年第8号):“三、违反纳税申报管理类(三)纳税人不进行纳税申报,不缴或者少缴应纳税款的。 《中华人民共和国税收征收管理法》第六十四条第二款,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款。 1.不缴或者少缴税款100万元以下的,处百分之五十以上一倍以下罚款; ”之规定,决定对你个人不进行纳税申报造成少缴税款2,129.45元处以0.5倍罚款,即1,064.73元。</t>
+          <t>我局于2025年6月16日起,对你(地址:内蒙古鄂尔多斯市伊金霍洛旗纳林陶亥镇道劳岱村沟门社034号)2020年1月1日-2020年12月31日期间的涉税情况进行检查,违法事实及处理决定如下: 经查,你于2020年提供装修服务取得收入163,804.00元,未进行纳税申报。 ”之规定,对你少缴的个人所得税税款,按日加收滞纳税款万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1784,13 +1792,15 @@
           <t>个人所得税</t>
         </is>
       </c>
-      <c r="R10" s="3" t="n"/>
+      <c r="R10" s="3" t="n">
+        <v>2129.45</v>
+      </c>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
       <c r="U10" s="3" t="n"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>综上所述,对你共处罚款1,064.73元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>你在2020年应税收入为163,804.00元,应纳税额=163,804.00*1.3%=2,129.45元,应补缴个人所得税2,129.45元。 综上,你在2020年应税收入为163,804.00元,应补缴个人所得税2,129.45元,并就上述税款按日加收万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="W10" s="4" t="n">
@@ -1804,7 +1814,7 @@
         <v>46308</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1847,7 +1857,7 @@
         <is>
           <t>Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202610/t20261013_898073.html”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202610/t20261013_898073.html”未静默覆盖。 字段“附件链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202610/P020261013417006903908.docx”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202610/P020261013417006903908.docx”未静默覆盖。 字段“页面标题”存在冲突:保留原值“国家税务总局内蒙古自治区税务局-
 旗县局通知公告”,新值“国家税务总局内蒙古自治区税务局-
-通知公告”未静默覆盖。</t>
+通知公告”未静默覆盖。 字段“主要违法事实”已根据官方附件重新解析。 字段“处理或处罚结果”已根据官方附件重新解析。 字段“附件链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202610/P020261013417006903908.docx”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202610/P020261013557090721134.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1955,7 @@
         <v>46308</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2440,7 +2450,7 @@
         <v>46304</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2802,7 +2812,7 @@
         <v>46308</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -5854,7 +5864,7 @@
         <v>46294</v>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
@@ -6472,7 +6482,7 @@
         <v>46296</v>
       </c>
       <c r="AA48" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
@@ -6594,7 +6604,7 @@
         <v>46296</v>
       </c>
       <c r="AA49" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
@@ -8084,7 +8094,7 @@
         <v>46286</v>
       </c>
       <c r="AA61" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
@@ -8206,7 +8216,7 @@
         <v>46286</v>
       </c>
       <c r="AA62" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
@@ -9226,7 +9236,7 @@
         <v>46280</v>
       </c>
       <c r="AA70" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
@@ -9458,7 +9468,7 @@
         <v>46280</v>
       </c>
       <c r="AA72" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
@@ -9576,7 +9586,7 @@
         <v>46280</v>
       </c>
       <c r="AA73" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
@@ -9690,7 +9700,7 @@
         <v>46280</v>
       </c>
       <c r="AA74" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
@@ -9808,7 +9818,7 @@
         <v>46280</v>
       </c>
       <c r="AA75" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
@@ -9926,7 +9936,7 @@
         <v>46280</v>
       </c>
       <c r="AA76" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
@@ -14938,7 +14948,7 @@
         <v>46254</v>
       </c>
       <c r="AA117" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
@@ -15064,7 +15074,7 @@
         <v>46254</v>
       </c>
       <c r="AA118" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
@@ -18004,7 +18014,7 @@
         <v>46246</v>
       </c>
       <c r="AA142" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
@@ -21342,7 +21352,7 @@
         <v>46234</v>
       </c>
       <c r="AA168" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
@@ -21464,7 +21474,7 @@
         <v>46238</v>
       </c>
       <c r="AA169" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB169" s="2" t="inlineStr">
         <is>
@@ -21590,7 +21600,7 @@
         <v>46238</v>
       </c>
       <c r="AA170" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
@@ -22368,7 +22378,7 @@
         <v>46254</v>
       </c>
       <c r="AA176" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
@@ -27704,7 +27714,7 @@
         <v>46229</v>
       </c>
       <c r="AA218" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
@@ -28732,7 +28742,7 @@
         <v>46254</v>
       </c>
       <c r="AA226" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
@@ -28866,7 +28876,7 @@
         <v>46258</v>
       </c>
       <c r="AA227" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB227" s="2" t="inlineStr">
         <is>
@@ -29008,7 +29018,7 @@
         <v>46254</v>
       </c>
       <c r="AA228" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
@@ -30210,7 +30220,7 @@
         <v>46258</v>
       </c>
       <c r="AA237" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB237" s="2" t="inlineStr">
         <is>
@@ -31589,7 +31599,7 @@
         <v>46308</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -31731,7 +31741,7 @@
         <v>46308</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -31966,7 +31976,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>我局于2025年6月16日起,对你2020年1月1日-2020年12月31日期间的涉税情况进行检查,确认你有如下违法事实,并作出如下处罚决定: 根据《税务处理决定书》(鄂税三稽处〔2026〕8号)认定你存在以下违法事实: 经查,你于2020年提供装修服务取得收入163,804.00元,未进行纳税申报。 根据《中华人民共和国税收征收管理法》(2015年4月24日发布的主席令第二十三号修订)第六十四条第二款:“纳税人不进行纳税申报,不缴或者少缴应纳税款的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款。 根据《内蒙古自治区国家税务局内蒙古自治区地方税务局关于发布〈内蒙古自治区税务行政处罚裁量基准〉的公告》(内蒙古自治区国家税务局内蒙古自治区地方税务局公告2017年第8号):“三、违反纳税申报管理类(三)纳税人不进行纳税申报,不缴或者少缴应纳税款的。 《中华人民共和国税收征收管理法》第六十四条第二款,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款。 1.不缴或者少缴税款100万元以下的,处百分之五十以上一倍以下罚款; ”之规定,决定对你个人不进行纳税申报造成少缴税款2,129.45元处以0.5倍罚款,即1,064.73元。</t>
+          <t>我局于2025年6月16日起,对你(地址:内蒙古鄂尔多斯市伊金霍洛旗纳林陶亥镇道劳岱村沟门社034号)2020年1月1日-2020年12月31日期间的涉税情况进行检查,违法事实及处理决定如下: 经查,你于2020年提供装修服务取得收入163,804.00元,未进行纳税申报。 ”之规定,对你少缴的个人所得税税款,按日加收滞纳税款万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -31974,13 +31984,15 @@
           <t>个人所得税</t>
         </is>
       </c>
-      <c r="R5" s="3" t="n"/>
+      <c r="R5" s="3" t="n">
+        <v>2129.45</v>
+      </c>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>综上所述,对你共处罚款1,064.73元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
+          <t>你在2020年应税收入为163,804.00元,应纳税额=163,804.00*1.3%=2,129.45元,应补缴个人所得税2,129.45元。 综上,你在2020年应税收入为163,804.00元,应补缴个人所得税2,129.45元,并就上述税款按日加收万分之五的滞纳金。</t>
         </is>
       </c>
       <c r="W5" s="4" t="n">
@@ -31994,7 +32006,7 @@
         <v>46308</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -32037,7 +32049,7 @@
         <is>
           <t>Excel 与 CSV 历史数据已合并核对。 字段“官方原文链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202610/t20261013_898073.html”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202610/t20261013_898073.html”未静默覆盖。 字段“附件链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202610/P020261013417006903908.docx”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/tzgghhht/202610/P020261013417006903908.docx”未静默覆盖。 字段“页面标题”存在冲突:保留原值“国家税务总局内蒙古自治区税务局-
 旗县局通知公告”,新值“国家税务总局内蒙古自治区税务局-
-通知公告”未静默覆盖。</t>
+通知公告”未静默覆盖。 字段“主要违法事实”已根据官方附件重新解析。 字段“处理或处罚结果”已根据官方附件重新解析。 字段“附件链接”存在冲突:保留原值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202610/P020261013417006903908.docx”,新值“https://neimenggu.chinatax.gov.cn/sjpd/eeds/xjtzgghhht/202610/P020261013557090721134.docx”未静默覆盖。</t>
         </is>
       </c>
     </row>
@@ -32135,7 +32147,7 @@
         <v>46308</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -36348,7 +36360,7 @@
         <v>46234</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -39726,7 +39738,7 @@
         <v>46258</v>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
@@ -39868,7 +39880,7 @@
         <v>46254</v>
       </c>
       <c r="AA64" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
@@ -40692,7 +40704,7 @@
         <v>46258</v>
       </c>
       <c r="AA70" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
@@ -41811,7 +41823,7 @@
         <v>46311</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -41851,7 +41863,7 @@
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。</t>
+          <t>官方附件可下载,但尚未提取到可核实的案情或金额,按文号线索收录。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -41933,7 +41945,7 @@
         <v>46311</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -42055,7 +42067,7 @@
         <v>46311</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -42181,7 +42193,7 @@
         <v>46311</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -42215,7 +42227,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -42299,7 +42315,7 @@
         <v>46311</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -42333,7 +42349,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -42783,7 +42803,7 @@
         <v>46304</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -43145,7 +43165,7 @@
         <v>46308</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -45537,7 +45557,7 @@
         <v>46294</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -46155,7 +46175,7 @@
         <v>46296</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -46277,7 +46297,7 @@
         <v>46296</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
@@ -47119,7 +47139,7 @@
         <v>46286</v>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
@@ -47241,7 +47261,7 @@
         <v>46286</v>
       </c>
       <c r="AA47" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
@@ -47855,7 +47875,7 @@
         <v>46280</v>
       </c>
       <c r="AA52" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
@@ -48087,7 +48107,7 @@
         <v>46280</v>
       </c>
       <c r="AA54" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
@@ -48205,7 +48225,7 @@
         <v>46280</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -48319,7 +48339,7 @@
         <v>46280</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -48437,7 +48457,7 @@
         <v>46280</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -48555,7 +48575,7 @@
         <v>46280</v>
       </c>
       <c r="AA58" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
@@ -52947,7 +52967,7 @@
         <v>46254</v>
       </c>
       <c r="AA94" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
@@ -53073,7 +53093,7 @@
         <v>46254</v>
       </c>
       <c r="AA95" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
@@ -55755,7 +55775,7 @@
         <v>46246</v>
       </c>
       <c r="AA117" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
@@ -57601,7 +57621,7 @@
         <v>46238</v>
       </c>
       <c r="AA132" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB132" s="2" t="inlineStr">
         <is>
@@ -57727,7 +57747,7 @@
         <v>46238</v>
       </c>
       <c r="AA133" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB133" s="2" t="inlineStr">
         <is>
@@ -58083,7 +58103,7 @@
         <v>46254</v>
       </c>
       <c r="AA136" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
@@ -61003,7 +61023,7 @@
         <v>46229</v>
       </c>
       <c r="AA160" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
@@ -61625,7 +61645,7 @@
         <v>46254</v>
       </c>
       <c r="AA165" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
@@ -62886,7 +62906,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -63012,7 +63032,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -63130,7 +63150,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -64163,7 +64183,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -64289,7 +64309,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -64407,7 +64427,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -64486,7 +64506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M194"/>
+  <dimension ref="A1:M195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -74196,8 +74216,57 @@
         </is>
       </c>
     </row>
+    <row r="195" ht="54" customHeight="1">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17T16:30:27+08:00</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10 至 2026-10-17</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="n">
+        <v>526</v>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G195" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I195" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/pingtanswj/zfxxgkzl/zfxxgkml/qtgg/: ConnectionError: HTTPSConnectionPool(host='...</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问74页，访问失败437页，持久化待复核428个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M194"/>
+  <autoFilter ref="A1:M195"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$168</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -781,7 +781,7 @@
         <v>46311</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>46311</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>46311</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>46311</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>46311</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>46308</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>46308</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46308</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>46308</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>46304</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46308</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>处理文书中的处罚结果串值已根据官方附件清除。</t>
+          <t>处理文书中的处罚结果串值已根据官方附件清除。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -6126,7 +6130,7 @@
         <v>46294</v>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
@@ -6744,7 +6748,7 @@
         <v>46296</v>
       </c>
       <c r="AA50" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
@@ -6866,7 +6870,7 @@
         <v>46296</v>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
@@ -8356,7 +8360,7 @@
         <v>46286</v>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
@@ -8478,7 +8482,7 @@
         <v>46286</v>
       </c>
       <c r="AA64" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
@@ -9498,7 +9502,7 @@
         <v>46280</v>
       </c>
       <c r="AA72" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
@@ -9730,7 +9734,7 @@
         <v>46280</v>
       </c>
       <c r="AA74" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
@@ -9848,7 +9852,7 @@
         <v>46280</v>
       </c>
       <c r="AA75" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
@@ -9962,7 +9966,7 @@
         <v>46280</v>
       </c>
       <c r="AA76" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
@@ -10080,7 +10084,7 @@
         <v>46280</v>
       </c>
       <c r="AA77" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
@@ -10198,7 +10202,7 @@
         <v>46280</v>
       </c>
       <c r="AA78" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
@@ -15210,7 +15214,7 @@
         <v>46254</v>
       </c>
       <c r="AA119" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
@@ -15336,7 +15340,7 @@
         <v>46254</v>
       </c>
       <c r="AA120" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
@@ -18276,7 +18280,7 @@
         <v>46246</v>
       </c>
       <c r="AA144" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
@@ -21614,7 +21618,7 @@
         <v>46234</v>
       </c>
       <c r="AA170" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
@@ -21736,7 +21740,7 @@
         <v>46238</v>
       </c>
       <c r="AA171" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
@@ -21862,7 +21866,7 @@
         <v>46238</v>
       </c>
       <c r="AA172" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
@@ -22640,7 +22644,7 @@
         <v>46254</v>
       </c>
       <c r="AA178" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
@@ -27976,7 +27980,7 @@
         <v>46229</v>
       </c>
       <c r="AA220" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
@@ -29004,7 +29008,7 @@
         <v>46254</v>
       </c>
       <c r="AA228" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
@@ -29138,7 +29142,7 @@
         <v>46258</v>
       </c>
       <c r="AA229" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
@@ -29280,7 +29284,7 @@
         <v>46254</v>
       </c>
       <c r="AA230" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
@@ -30482,7 +30486,7 @@
         <v>46258</v>
       </c>
       <c r="AA239" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB239" s="2" t="inlineStr">
         <is>
@@ -31863,7 +31867,7 @@
         <v>46308</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -32005,7 +32009,7 @@
         <v>46308</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -32270,7 +32274,7 @@
         <v>46308</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -32411,7 +32415,7 @@
         <v>46308</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -32584,7 +32588,7 @@
       </c>
       <c r="AJ7" s="2" t="inlineStr">
         <is>
-          <t>处理文书中的处罚结果串值已根据官方附件清除。</t>
+          <t>处理文书中的处罚结果串值已根据官方附件清除。 Excel 与 CSV 历史数据已合并核对。</t>
         </is>
       </c>
     </row>
@@ -32718,7 +32722,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -36886,7 +36894,7 @@
         <v>46234</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
@@ -40264,7 +40272,7 @@
         <v>46258</v>
       </c>
       <c r="AA65" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
@@ -40406,7 +40414,7 @@
         <v>46254</v>
       </c>
       <c r="AA66" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
@@ -41230,7 +41238,7 @@
         <v>46258</v>
       </c>
       <c r="AA72" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
@@ -42351,7 +42359,7 @@
         <v>46311</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -42473,7 +42481,7 @@
         <v>46311</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -42595,7 +42603,7 @@
         <v>46311</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -42721,7 +42729,7 @@
         <v>46311</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -42843,7 +42851,7 @@
         <v>46311</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -43331,7 +43339,7 @@
         <v>46304</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -43693,7 +43701,7 @@
         <v>46308</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
@@ -46085,7 +46093,7 @@
         <v>46294</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
@@ -46703,7 +46711,7 @@
         <v>46296</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
@@ -46825,7 +46833,7 @@
         <v>46296</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
@@ -47667,7 +47675,7 @@
         <v>46286</v>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
@@ -47789,7 +47797,7 @@
         <v>46286</v>
       </c>
       <c r="AA47" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
@@ -48403,7 +48411,7 @@
         <v>46280</v>
       </c>
       <c r="AA52" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
@@ -48635,7 +48643,7 @@
         <v>46280</v>
       </c>
       <c r="AA54" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
@@ -48753,7 +48761,7 @@
         <v>46280</v>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
@@ -48867,7 +48875,7 @@
         <v>46280</v>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
@@ -48985,7 +48993,7 @@
         <v>46280</v>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
@@ -49103,7 +49111,7 @@
         <v>46280</v>
       </c>
       <c r="AA58" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
@@ -53495,7 +53503,7 @@
         <v>46254</v>
       </c>
       <c r="AA94" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
@@ -53621,7 +53629,7 @@
         <v>46254</v>
       </c>
       <c r="AA95" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
@@ -56303,7 +56311,7 @@
         <v>46246</v>
       </c>
       <c r="AA117" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
@@ -58149,7 +58157,7 @@
         <v>46238</v>
       </c>
       <c r="AA132" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB132" s="2" t="inlineStr">
         <is>
@@ -58275,7 +58283,7 @@
         <v>46238</v>
       </c>
       <c r="AA133" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB133" s="2" t="inlineStr">
         <is>
@@ -58631,7 +58639,7 @@
         <v>46254</v>
       </c>
       <c r="AA136" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
@@ -61551,7 +61559,7 @@
         <v>46229</v>
       </c>
       <c r="AA160" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
@@ -62173,7 +62181,7 @@
         <v>46254</v>
       </c>
       <c r="AA165" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
@@ -63434,7 +63442,7 @@
         <v>46238</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -63560,7 +63568,7 @@
         <v>46238</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
@@ -63678,7 +63686,7 @@
         <v>46229</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
@@ -64711,7 +64719,7 @@
         <v>46238</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -64837,7 +64845,7 @@
         <v>46238</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
@@ -64955,7 +64963,7 @@
         <v>46229</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
@@ -65034,7 +65042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M196"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -74846,8 +74854,57 @@
         </is>
       </c>
     </row>
+    <row r="197" ht="54" customHeight="1">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18T16:48:15+08:00</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 至 2026-10-18</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n">
+        <v>531</v>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H197" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I197" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/pingtanswj/zfxxgkzl/zfxxgkml/qtgg/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /pingtanswj/zfxxgkzl/zfxxgkml/qtgg/ (Caused by NewConnectionError("HTTPSConnection(host='fujian...</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问76页，访问失败439页，持久化待复核430个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M196"/>
+  <autoFilter ref="A1:M197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$168</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$198</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -65042,7 +65042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M197"/>
+  <dimension ref="A1:M198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -74903,8 +74903,57 @@
         </is>
       </c>
     </row>
+    <row r="198" ht="54" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18T17:19:43+08:00</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 至 2026-10-18</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="n">
+        <v>506</v>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G198" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I198" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinatax.gov.cn', port=443): Max retries exceeded with url: /fzsswj/xxgk/gsgg/qtl/ (Caused by NewConnectionError("HTTPSConnection(host='fujian.chinatax.gov.cn', port=44...</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问64页，访问失败438页，持久化待复核429个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M197"/>
+  <autoFilter ref="A1:M198"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/全国税务处理及行政处罚决定书汇总.xlsx
+++ b/data/全国税务处理及行政处罚决定书汇总.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公告送达及文号线索'!$A$1:$AJ$170</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待核验记录'!$A$1:$AJ$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'失效链接'!$A$1:$AJ$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'每日运行日志'!$A$1:$M$200</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1709,7 +1709,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1827,7 +1831,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -2020,7 +2028,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>我局于2025年6月16日起,对你(地址:内蒙古鄂尔多斯市伊金霍洛旗纳林陶亥镇道劳岱村沟门社034号)2020年1月1日-2020年12月31日期间的涉税情况进行检查,违法事实及处理决定如下: 经查,你于2020年提供装修服务取得收入163,804.00元,未进行纳税申报。 ”之规定,对你少缴的个人所得税税款,按日加收滞纳税款万分之五的滞纳金。</t>
+          <t>我局于2025年6月16日起,对你2020年1月1日-2020年12月31日期间的涉税情况进行检查,确认你有如下违法事实,并作出如下处罚决定: 根据《税务处理决定书》(鄂税三稽处〔2026〕8号)认定你存在以下违法事实: 经查,你于2020年提供装修服务取得收入163,804.00元,未进行纳税申报。 根据《中华人民共和国税收征收管理法》(2015年4月24日发布的主席令第二十三号修订)第六十四条第二款:“纳税人不进行纳税申报,不缴或者少缴应纳税款的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款。 根据《内蒙古自治区国家税务局内蒙古自治区地方税务局关于发布〈内蒙古自治区税务行政处罚裁量基准〉的公告》(内蒙古自治区国家税务局内蒙古自治区地方税务局公告2017年第8号):“三、违反纳税申报管理类(三)纳税人不进行纳税申报,不缴或者少缴应纳税款的。 《中华人民共和国税收征收管理法》第六十四条第二款,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款。 1.不缴或者少缴税款100万元以下的,处百分之五十以上一倍以下罚款; ”之规定,决定对你个人不进行纳税申报造成少缴税款2,129.45元处以0.5倍罚款,即1,064.73元。</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2036,7 +2044,7 @@
       <c r="U12" s="3" t="n"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>你在2020年应税收入为163,804.00元,应纳税额=163,804.00*1.3%=2,129.45元,应补缴个人所得税2,129.45元。 综上,你在2020年应税收入为163,804.00元,应补缴个人所得税2,129.45元,并就上述税款按日加收万分之五的滞纳金。</t>
+          <t>综上所述,对你共处罚款1,064.73元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
         </is>
       </c>
       <c r="W12" s="4" t="n">
@@ -3178,7 +3186,7 @@
         <v>46312</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
@@ -3314,7 +3322,7 @@
         <v>46312</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
@@ -32482,7 +32490,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>我局于2025年6月16日起,对你(地址:内蒙古鄂尔多斯市伊金霍洛旗纳林陶亥镇道劳岱村沟门社034号)2020年1月1日-2020年12月31日期间的涉税情况进行检查,违法事实及处理决定如下: 经查,你于2020年提供装修服务取得收入163,804.00元,未进行纳税申报。 ”之规定,对你少缴的个人所得税税款,按日加收滞纳税款万分之五的滞纳金。</t>
+          <t>我局于2025年6月16日起,对你2020年1月1日-2020年12月31日期间的涉税情况进行检查,确认你有如下违法事实,并作出如下处罚决定: 根据《税务处理决定书》(鄂税三稽处〔2026〕8号)认定你存在以下违法事实: 经查,你于2020年提供装修服务取得收入163,804.00元,未进行纳税申报。 根据《中华人民共和国税收征收管理法》(2015年4月24日发布的主席令第二十三号修订)第六十四条第二款:“纳税人不进行纳税申报,不缴或者少缴应纳税款的,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款。 根据《内蒙古自治区国家税务局内蒙古自治区地方税务局关于发布〈内蒙古自治区税务行政处罚裁量基准〉的公告》(内蒙古自治区国家税务局内蒙古自治区地方税务局公告2017年第8号):“三、违反纳税申报管理类(三)纳税人不进行纳税申报,不缴或者少缴应纳税款的。 《中华人民共和国税收征收管理法》第六十四条第二款,由税务机关追缴其不缴或者少缴的税款、滞纳金,并处不缴或者少缴的税款百分之五十以上五倍以下的罚款。 1.不缴或者少缴税款100万元以下的,处百分之五十以上一倍以下罚款; ”之规定,决定对你个人不进行纳税申报造成少缴税款2,129.45元处以0.5倍罚款,即1,064.73元。</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -32498,7 +32506,7 @@
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>你在2020年应税收入为163,804.00元,应纳税额=163,804.00*1.3%=2,129.45元,应补缴个人所得税2,129.45元。 综上,你在2020年应税收入为163,804.00元,应补缴个人所得税2,129.45元,并就上述税款按日加收万分之五的滞纳金。</t>
+          <t>综上所述,对你共处罚款1,064.73元。 到期不缴纳罚款,我局可依照《中华人民共和国行政处罚法》第七十二条第一款第(一)项规定,每日按罚款数额的百分之三加处罚款。</t>
         </is>
       </c>
       <c r="W5" s="4" t="n">
@@ -32790,7 +32798,7 @@
         <v>46312</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -32926,7 +32934,7 @@
         <v>46312</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -43245,7 +43253,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -43363,7 +43375,11 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>Excel 与 CSV 历史数据已合并核对。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -65518,7 +65534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M199"/>
+  <dimension ref="A1:M200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -75481,8 +75497,57 @@
         </is>
       </c>
     </row>
+    <row r="200" ht="54" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19T18:20:29+08:00</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 至 2026-10-19</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="n">
+        <v>509</v>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I200" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>discover_official_index: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/: HTTPError: 403 Client Error: Forbidden for url: http://qinghai.chinatax.gov.cn/hxz/sjtzgg/ | discover_official_index: https://fujian.chinatax.gov.cn/fzsswj/xxgk/gsgg/qtl/: ConnectionError: HTTPSConnectionPool(host='fujian.chinat...</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>本次已核验来源新增0份文书；检索覆盖不完整，不能据此认定其他日期没有新文书。本轮可访问60页，访问失败447页，持久化待复核438个链接。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M199"/>
+  <autoFilter ref="A1:M200"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
